--- a/inventory/ae-cryptography-asset-inventory.xlsx
+++ b/inventory/ae-cryptography-asset-inventory.xlsx
@@ -430,7 +430,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M91"/>
+  <dimension ref="A1:M111"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.6640625" defaultRowHeight="16"/>
   <cols>
     <col width="30" bestFit="1" customWidth="1" style="2" min="1" max="1"/>
@@ -514,12 +514,12 @@
     <row r="2" ht="23" customHeight="1">
       <c r="A2" s="5" t="inlineStr">
         <is>
-          <t>acvp-server-1.1.0.41</t>
+          <t>acvp-server-1.1.0.42</t>
         </is>
       </c>
       <c r="B2" s="13" t="inlineStr">
         <is>
-          <t>c</t>
+          <t>x</t>
         </is>
       </c>
       <c r="C2" s="10" t="inlineStr">
@@ -529,7 +529,7 @@
       </c>
       <c r="D2" s="3" t="inlineStr">
         <is>
-          <t>1.1.0.41</t>
+          <t>1.1.0.42</t>
         </is>
       </c>
       <c r="E2" s="3" t="inlineStr">
@@ -539,7 +539,7 @@
       </c>
       <c r="F2" s="5" t="inlineStr">
         <is>
-          <t>https://github.com/usnistgov/ACVP-Server/archive/refs/tags/v1.1.0.41.tar.gz</t>
+          <t>https://github.com/usnistgov/ACVP-Server/archive/refs/tags/v1.1.0.42.tar.gz</t>
         </is>
       </c>
       <c r="G2" s="5" t="inlineStr">
@@ -549,7 +549,7 @@
       </c>
       <c r="H2" s="5" t="inlineStr">
         <is>
-          <t>v1.1.0.41 (2025)</t>
+          <t>v1.1.0.42 (2026-04-16)</t>
         </is>
       </c>
       <c r="I2" s="5" t="n"/>
@@ -631,7 +631,11 @@
           <t>ascon-c</t>
         </is>
       </c>
-      <c r="B4" s="13" t="n"/>
+      <c r="B4" s="13" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="C4" s="5" t="inlineStr">
         <is>
           <t>CC0-1.0</t>
@@ -683,22 +687,18 @@
     <row r="5" ht="23" customHeight="1">
       <c r="A5" s="5" t="inlineStr">
         <is>
-          <t>aws-lc-1.72.0</t>
-        </is>
-      </c>
-      <c r="B5" s="13" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
-      <c r="C5" s="5" t="inlineStr">
+          <t>aws-lc-4.0.0</t>
+        </is>
+      </c>
+      <c r="B5" s="13" t="n"/>
+      <c r="C5" s="10" t="inlineStr">
         <is>
           <t>Apache-2.0 AND ISC</t>
         </is>
       </c>
       <c r="D5" s="3" t="inlineStr">
         <is>
-          <t>1.72.0</t>
+          <t>4.0.0</t>
         </is>
       </c>
       <c r="E5" s="3" t="inlineStr">
@@ -708,7 +708,7 @@
       </c>
       <c r="F5" s="5" t="inlineStr">
         <is>
-          <t>https://github.com/aws/aws-lc/archive/refs/tags/v1.72.0.tar.gz</t>
+          <t>https://github.com/aws/aws-lc/archive/refs/tags/v4.0.0.tar.gz</t>
         </is>
       </c>
       <c r="G5" s="5" t="inlineStr">
@@ -718,7 +718,7 @@
       </c>
       <c r="H5" s="5" t="inlineStr">
         <is>
-          <t>v1.70.0</t>
+          <t>v4.0.0</t>
         </is>
       </c>
       <c r="I5" s="5" t="inlineStr">
@@ -728,10 +728,14 @@
       </c>
       <c r="J5" s="5" t="inlineStr">
         <is>
-          <t>AES-*, ChaCha20-Poly1305, SHA-*, HMAC-*, AES-CMAC, RSAES-OAEP-*, ECDH-*, ECDSA-*, EdDSA-*, RSASSA-PSS-*, HKDF-*, PBKDF2-*, ML-KEM-*, ML-DSA-*, CTR_DRBG-AES-256, HMAC_DRBG-SHA-256</t>
-        </is>
-      </c>
-      <c r="K5" s="5" t="n"/>
+          <t>AES-*, ChaCha20-Poly1305, SHA-*, HMAC-*, AES-CMAC, RSAES-OAEP-*, ECDH-*, ECDSA-*, EdDSA-*, RSASSA-PSS-*, HKDF-*, PBKDF2-*, ML-KEM-*, ML-DSA-*, CTR_DRBG-AES-256, HMAC_DRBG-SHA-256, ML-KEM-[512|768|1024], ML-DSA-[44|65|87]-*</t>
+        </is>
+      </c>
+      <c r="K5" s="5" t="inlineStr">
+        <is>
+          <t>Previous major line.</t>
+        </is>
+      </c>
       <c r="L5" s="5" t="inlineStr">
         <is>
           <t>RSA: expired 2000; ECC: Certicom/BlackBerry largely expired 2017–2022; ML-KEM: NIST patent licenses secured; ML-DSA: no known patents; AES, ChaCha20, SHA, HMAC: no known patents. Apache-2.0 license includes patent grant.</t>
@@ -746,22 +750,22 @@
     <row r="6" ht="23" customHeight="1">
       <c r="A6" s="5" t="inlineStr">
         <is>
-          <t>aws-lc-kdf</t>
+          <t>aws-lc-5.0.0</t>
         </is>
       </c>
       <c r="B6" s="13" t="inlineStr">
         <is>
-          <t>(x)</t>
+          <t>x</t>
         </is>
       </c>
       <c r="C6" s="5" t="inlineStr">
         <is>
-          <t>Apache-2.0</t>
+          <t>Apache-2.0 AND ISC</t>
         </is>
       </c>
       <c r="D6" s="3" t="inlineStr">
         <is>
-          <t>1.71.0</t>
+          <t>5.0.0</t>
         </is>
       </c>
       <c r="E6" s="3" t="inlineStr">
@@ -771,29 +775,33 @@
       </c>
       <c r="F6" s="5" t="inlineStr">
         <is>
-          <t>https://github.com/aws/aws-lc/archive/refs/tags/v1.71.0.tar.gz</t>
+          <t>https://github.com/aws/aws-lc/archive/refs/tags/v5.0.0.tar.gz</t>
         </is>
       </c>
       <c r="G6" s="5" t="inlineStr">
         <is>
-          <t>AWS-LC — CatKDF and KeyCombine (NIST SP 800-56Cr2)</t>
+          <t>AWS-LC — AWS BoringSSL fork (C); ML-KEM, ML-DSA; FIPS 140-3 validated</t>
         </is>
       </c>
       <c r="H6" s="5" t="inlineStr">
         <is>
-          <t>Stable release</t>
-        </is>
-      </c>
-      <c r="I6" s="5" t="n"/>
+          <t>v5.0.0 (2026-05-29)</t>
+        </is>
+      </c>
+      <c r="I6" s="5" t="inlineStr">
+        <is>
+          <t>stable</t>
+        </is>
+      </c>
       <c r="J6" s="5" t="inlineStr">
         <is>
-          <t>CatKDF, KeyCombine</t>
+          <t>AES-*, ChaCha20-Poly1305, SHA-*, HMAC-*, AES-CMAC, RSAES-OAEP-*, ECDH-*, ECDSA-*, EdDSA-*, RSASSA-PSS-*, HKDF-*, PBKDF2-*, ML-KEM-*, ML-DSA-*, CTR_DRBG-AES-256, HMAC_DRBG-SHA-256, ML-KEM-[512|768|1024], ML-DSA-[44|65|87]-*</t>
         </is>
       </c>
       <c r="K6" s="5" t="n"/>
       <c r="L6" s="5" t="inlineStr">
         <is>
-          <t>No known patents.</t>
+          <t>RSA: expired 2000; ECC: Certicom/BlackBerry largely expired 2017–2022; ML-KEM: NIST patent licenses secured; ML-DSA: no known patents; AES, ChaCha20, SHA, HMAC: no known patents. Apache-2.0 license includes patent grant.</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
@@ -805,58 +813,54 @@
     <row r="7" ht="23" customHeight="1">
       <c r="A7" s="5" t="inlineStr">
         <is>
-          <t>bc-csharp-2.6.2</t>
+          <t>aws-lc-kdf</t>
         </is>
       </c>
       <c r="B7" s="13" t="inlineStr">
         <is>
-          <t>x</t>
+          <t>(x)</t>
         </is>
       </c>
       <c r="C7" s="5" t="inlineStr">
         <is>
-          <t>MIT</t>
+          <t>Apache-2.0</t>
         </is>
       </c>
       <c r="D7" s="3" t="inlineStr">
         <is>
-          <t>2.6.2</t>
+          <t>5.0.0</t>
         </is>
       </c>
       <c r="E7" s="3" t="inlineStr">
         <is>
-          <t>https://github.com/bcgit/bc-csharp</t>
+          <t>https://github.com/aws/aws-lc</t>
         </is>
       </c>
       <c r="F7" s="5" t="inlineStr">
         <is>
-          <t>https://github.com/bcgit/bc-csharp/archive/refs/tags/release-2.6.2.tar.gz</t>
+          <t>https://github.com/aws/aws-lc/archive/refs/tags/v5.0.0.tar.gz</t>
         </is>
       </c>
       <c r="G7" s="5" t="inlineStr">
         <is>
-          <t>Bouncy Castle C# (.NET) — mirrors Java PQC support; ML-KEM, ML-DSA, SLH-DSA</t>
+          <t>AWS-LC — CatKDF and KeyCombine (NIST SP 800-56Cr2)</t>
         </is>
       </c>
       <c r="H7" s="5" t="inlineStr">
         <is>
-          <t>release-2.6.2</t>
-        </is>
-      </c>
-      <c r="I7" s="5" t="inlineStr">
-        <is>
-          <t>stable</t>
-        </is>
-      </c>
+          <t>v5.0.0 (2026-05-29)</t>
+        </is>
+      </c>
+      <c r="I7" s="5" t="n"/>
       <c r="J7" s="5" t="inlineStr">
         <is>
-          <t>AES-[128|192|256]-[GCM|CCM|CBC|CTR|OFB|CFB128|XTS|KW], ChaCha20-Poly1305, SHA-[256|384|512], SHA3-[256|384|512], HMAC-[SHA-256|SHA-384|SHA-512], AES-[128|192|256]-CMAC, RSAES-OAEP-[2048|3072|4096]-*, ECDH-[P-256|P-384|P-521], ECDH-[brainpoolP256r1|brainpoolP384r1|brainpoolP512r1], ECDH-[Curve25519|X25519], ECDH-[Curve448|X448], ECDSA-[P-256|P-384|P-521]-*, ECDSA-[brainpoolP256r1|brainpoolP384r1|brainpoolP512r1]-*, EdDSA-[Ed25519|Ed448], RSASSA-PSS-[2048|3072|4096]-*, LMS-*, XMSS-*, HKDF-[SHA-256|SHA-384|SHA-512], PBKDF2-HMAC-[SHA-256|SHA-384|SHA-512]-*, bcrypt-*, ML-KEM-[512|768|1024], ML-DSA-[44|65|87]-*, SLH-DSA-*</t>
+          <t>CatKDF, KeyCombine</t>
         </is>
       </c>
       <c r="K7" s="5" t="n"/>
       <c r="L7" s="5" t="inlineStr">
         <is>
-          <t>RSA: expired 2000; DH: expired 1997; ECC: Certicom/BlackBerry largely expired 2017–2022; ML-KEM: NIST patent licenses secured; FN-DSA: NTRU patents in public domain; AES, SHA, HMAC: no known patents. MIT license.</t>
+          <t>No known patents.</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
@@ -868,7 +872,7 @@
     <row r="8" ht="23" customHeight="1">
       <c r="A8" s="5" t="inlineStr">
         <is>
-          <t>bc-java-1.83</t>
+          <t>aws-lc-rs-1.17.0</t>
         </is>
       </c>
       <c r="B8" s="13" t="inlineStr">
@@ -876,34 +880,34 @@
           <t>x</t>
         </is>
       </c>
-      <c r="C8" s="5" t="inlineStr">
-        <is>
-          <t>MIT</t>
+      <c r="C8" s="10" t="inlineStr">
+        <is>
+          <t>ISC AND (Apache-2.0 OR ISC)</t>
         </is>
       </c>
       <c r="D8" s="3" t="inlineStr">
         <is>
-          <t>1.83</t>
+          <t>1.17.0</t>
         </is>
       </c>
       <c r="E8" s="3" t="inlineStr">
         <is>
-          <t>https://github.com/bcgit/bc-java</t>
+          <t>https://github.com/aws/aws-lc-rs</t>
         </is>
       </c>
       <c r="F8" s="5" t="inlineStr">
         <is>
-          <t>https://github.com/bcgit/bc-java/archive/refs/tags/r1rv83.tar.gz</t>
+          <t>https://github.com/aws/aws-lc-rs/archive/refs/tags/v1.17.0.tar.gz</t>
         </is>
       </c>
       <c r="G8" s="5" t="inlineStr">
         <is>
-          <t>Bouncy Castle Java — comprehensive crypto library (Java); ML-KEM, ML-DSA, SLH-DSA, FN-DSA, HQC, composite signatures</t>
+          <t>aws-lc-rs — Rust crypto library (ring-compatible API) backed by AWS-LC (C/asm)</t>
         </is>
       </c>
       <c r="H8" s="5" t="inlineStr">
         <is>
-          <t>r1rv83 (1.83)</t>
+          <t>v1.17.0 (2026-05-13)</t>
         </is>
       </c>
       <c r="I8" s="5" t="inlineStr">
@@ -913,15 +917,15 @@
       </c>
       <c r="J8" s="5" t="inlineStr">
         <is>
-          <t>AES-[128|192|256]-[GCM|CCM|GCM-SIV|CBC|CTR|OFB|CFB128|XTS|KW], ChaCha20-Poly1305, SHA-[256|384|512], SHA3-[256|384|512], SHAKE128, SHAKE256, HMAC-[SHA-256|SHA-384|SHA-512], AES-[128|192|256]-CMAC, RSAES-OAEP-[2048|3072|4096]-*, ECDH-[P-256|P-384|P-521], ECDH-[brainpoolP256r1|brainpoolP384r1|brainpoolP512r1], ECDH-[Curve25519|X25519], ECDH-[Curve448|X448], FFDH-*, ECDSA-[P-256|P-384|P-521]-*, ECDSA-[brainpoolP256r1|brainpoolP384r1|brainpoolP512r1]-*, EdDSA-[Ed25519|Ed448], RSASSA-PSS-[2048|3072|4096]-*, LMS-*, XMSS-*, HKDF-[SHA-256|SHA-384|SHA-512], PBKDF2-HMAC-[SHA-256|SHA-384|SHA-512]-*, Argon2id-*, scrypt-*, bcrypt-*, ML-KEM-[512|768|1024], ML-DSA-[44|65|87]-*, SLH-DSA-*, FN-DSA-[512|1024], HQC-[128|192|256]</t>
-        </is>
-      </c>
-      <c r="K8" s="5" t="n"/>
-      <c r="L8" s="5" t="inlineStr">
-        <is>
-          <t>RSA: expired 2000; DH: expired 1997; ECC: Certicom/BlackBerry largely expired 2017–2022; ML-KEM: NIST patent licenses secured; FN-DSA: NTRU patents in public domain (Security Innovation, 2017); AES, SHA, HMAC: no known patents. MIT license (no explicit patent grant).</t>
-        </is>
-      </c>
+          <t>AES-[128|256]-GCM, ChaCha20-Poly1305, AES-[128|192|256]-[CBC|CTR], SHA-*, HMAC-*, HKDF, PBKDF2-*, RSASSA-PSS-*, RSAES-OAEP-*, ECDSA-[P-256|P-384|P-521]-*, EdDSA-Ed25519, ECDH-[P-256|P-384|X25519], ML-KEM-[512|768|1024], ML-DSA-[44|65|87]-*</t>
+        </is>
+      </c>
+      <c r="K8" s="5" t="inlineStr">
+        <is>
+          <t>Rust safe-API wrapper over AWS-LC; default crypto backend for rustls.</t>
+        </is>
+      </c>
+      <c r="L8" s="5" t="n"/>
       <c r="M8" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve"> </t>
@@ -931,12 +935,12 @@
     <row r="9" ht="23" customHeight="1">
       <c r="A9" s="5" t="inlineStr">
         <is>
-          <t>bc-java-dlies-1.83</t>
+          <t>bc-csharp-2.6.2</t>
         </is>
       </c>
       <c r="B9" s="13" t="inlineStr">
         <is>
-          <t>(x)</t>
+          <t>x</t>
         </is>
       </c>
       <c r="C9" s="5" t="inlineStr">
@@ -946,39 +950,43 @@
       </c>
       <c r="D9" s="3" t="inlineStr">
         <is>
-          <t>1.83</t>
+          <t>2.6.2</t>
         </is>
       </c>
       <c r="E9" s="3" t="inlineStr">
         <is>
-          <t>https://github.com/bcgit/bc-java</t>
+          <t>https://github.com/bcgit/bc-csharp</t>
         </is>
       </c>
       <c r="F9" s="5" t="inlineStr">
         <is>
-          <t>https://github.com/bcgit/bc-java/archive/refs/tags/r1rv83.tar.gz</t>
+          <t>https://github.com/bcgit/bc-csharp/archive/refs/tags/release-2.6.2.tar.gz</t>
         </is>
       </c>
       <c r="G9" s="5" t="inlineStr">
         <is>
-          <t>Bouncy Castle DLIES implementation</t>
+          <t>Bouncy Castle C# (.NET) — mirrors Java PQC support; ML-KEM, ML-DSA, SLH-DSA</t>
         </is>
       </c>
       <c r="H9" s="5" t="inlineStr">
         <is>
-          <t>Stable release</t>
-        </is>
-      </c>
-      <c r="I9" s="5" t="n"/>
+          <t>release-2.6.2</t>
+        </is>
+      </c>
+      <c r="I9" s="5" t="inlineStr">
+        <is>
+          <t>stable</t>
+        </is>
+      </c>
       <c r="J9" s="5" t="inlineStr">
         <is>
-          <t>DLIES, ECIES</t>
+          <t>AES-[128|192|256]-[GCM|CCM|CBC|CTR|OFB|CFB128|XTS|KW], ChaCha20-Poly1305, SHA-[256|384|512], SHA3-[256|384|512], HMAC-[SHA-256|SHA-384|SHA-512], AES-[128|192|256]-CMAC, RSAES-OAEP-[2048|3072|4096]-*, ECDH-[P-256|P-384|P-521], ECDH-[brainpoolP256r1|brainpoolP384r1|brainpoolP512r1], ECDH-[Curve25519|X25519], ECDH-[Curve448|X448], ECDSA-[P-256|P-384|P-521]-*, ECDSA-[brainpoolP256r1|brainpoolP384r1|brainpoolP512r1]-*, EdDSA-[Ed25519|Ed448], RSASSA-PSS-[2048|3072|4096]-*, LMS-*, XMSS-*, HKDF-[SHA-256|SHA-384|SHA-512], PBKDF2-HMAC-[SHA-256|SHA-384|SHA-512]-*, bcrypt-*, ML-KEM-[512|768|1024], ML-DSA-[44|65|87]-*, SLH-DSA-*</t>
         </is>
       </c>
       <c r="K9" s="5" t="n"/>
       <c r="L9" s="5" t="inlineStr">
         <is>
-          <t>No known patents.</t>
+          <t>RSA: expired 2000; DH: expired 1997; ECC: Certicom/BlackBerry largely expired 2017–2022; ML-KEM: NIST patent licenses secured; FN-DSA: NTRU patents in public domain; AES, SHA, HMAC: no known patents. MIT license.</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
@@ -990,7 +998,7 @@
     <row r="10" ht="23" customHeight="1">
       <c r="A10" s="5" t="inlineStr">
         <is>
-          <t>blake3-1.8.4</t>
+          <t>bc-java-1.83</t>
         </is>
       </c>
       <c r="B10" s="13" t="inlineStr">
@@ -1000,44 +1008,48 @@
       </c>
       <c r="C10" s="5" t="inlineStr">
         <is>
-          <t>CC0-1.0 OR Apache-2.0</t>
+          <t>MIT</t>
         </is>
       </c>
       <c r="D10" s="3" t="inlineStr">
         <is>
-          <t>1.8.4</t>
+          <t>1.83</t>
         </is>
       </c>
       <c r="E10" s="3" t="inlineStr">
         <is>
-          <t>https://github.com/BLAKE3-team/BLAKE3</t>
+          <t>https://github.com/bcgit/bc-java</t>
         </is>
       </c>
       <c r="F10" s="5" t="inlineStr">
         <is>
-          <t>https://github.com/BLAKE3-team/BLAKE3/archive/refs/tags/1.8.4.tar.gz</t>
+          <t>https://github.com/bcgit/bc-java/archive/refs/tags/r1rv83.tar.gz</t>
         </is>
       </c>
       <c r="G10" s="5" t="inlineStr">
         <is>
-          <t>BLAKE3 reference implementation (Rust + C)</t>
+          <t>Bouncy Castle Java — comprehensive crypto library (Java); ML-KEM, ML-DSA, SLH-DSA, FN-DSA, HQC, composite signatures</t>
         </is>
       </c>
       <c r="H10" s="5" t="inlineStr">
         <is>
-          <t>Stable release</t>
-        </is>
-      </c>
-      <c r="I10" s="5" t="n"/>
+          <t>r1rv83 (1.83)</t>
+        </is>
+      </c>
+      <c r="I10" s="5" t="inlineStr">
+        <is>
+          <t>stable</t>
+        </is>
+      </c>
       <c r="J10" s="5" t="inlineStr">
         <is>
-          <t>BLAKE3</t>
+          <t>AES-[128|192|256]-[GCM|CCM|GCM-SIV|CBC|CTR|OFB|CFB128|XTS|KW], ChaCha20-Poly1305, SHA-[256|384|512], SHA3-[256|384|512], SHAKE128, SHAKE256, HMAC-[SHA-256|SHA-384|SHA-512], AES-[128|192|256]-CMAC, RSAES-OAEP-[2048|3072|4096]-*, ECDH-[P-256|P-384|P-521], ECDH-[brainpoolP256r1|brainpoolP384r1|brainpoolP512r1], ECDH-[Curve25519|X25519], ECDH-[Curve448|X448], FFDH-*, ECDSA-[P-256|P-384|P-521]-*, ECDSA-[brainpoolP256r1|brainpoolP384r1|brainpoolP512r1]-*, EdDSA-[Ed25519|Ed448], RSASSA-PSS-[2048|3072|4096]-*, LMS-*, XMSS-*, HKDF-[SHA-256|SHA-384|SHA-512], PBKDF2-HMAC-[SHA-256|SHA-384|SHA-512]-*, Argon2id-*, scrypt-*, bcrypt-*, ML-KEM-[512|768|1024], ML-DSA-[44|65|87]-*, SLH-DSA-*, FN-DSA-[512|1024], HQC-[128|192|256]</t>
         </is>
       </c>
       <c r="K10" s="5" t="n"/>
       <c r="L10" s="5" t="inlineStr">
         <is>
-          <t>No known patents.</t>
+          <t>RSA: expired 2000; DH: expired 1997; ECC: Certicom/BlackBerry largely expired 2017–2022; ML-KEM: NIST patent licenses secured; FN-DSA: NTRU patents in public domain (Security Innovation, 2017); AES, SHA, HMAC: no known patents. MIT license (no explicit patent grant).</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
@@ -1049,37 +1061,37 @@
     <row r="11" ht="23" customHeight="1">
       <c r="A11" s="5" t="inlineStr">
         <is>
-          <t>blst-0.3.13</t>
+          <t>bc-java-dlies-1.83</t>
         </is>
       </c>
       <c r="B11" s="13" t="inlineStr">
         <is>
-          <t>x</t>
+          <t>(x)</t>
         </is>
       </c>
       <c r="C11" s="5" t="inlineStr">
         <is>
-          <t>Apache-2.0</t>
+          <t>MIT</t>
         </is>
       </c>
       <c r="D11" s="3" t="inlineStr">
         <is>
-          <t>0.3.13</t>
+          <t>1.83</t>
         </is>
       </c>
       <c r="E11" s="3" t="inlineStr">
         <is>
-          <t>https://github.com/supranational/blst</t>
+          <t>https://github.com/bcgit/bc-java</t>
         </is>
       </c>
       <c r="F11" s="5" t="inlineStr">
         <is>
-          <t>https://github.com/supranational/blst/archive/refs/tags/v0.3.13.tar.gz</t>
+          <t>https://github.com/bcgit/bc-java/archive/refs/tags/r1rv83.tar.gz</t>
         </is>
       </c>
       <c r="G11" s="5" t="inlineStr">
         <is>
-          <t>BLS12-381 signature library (Supranational)</t>
+          <t>Bouncy Castle DLIES implementation</t>
         </is>
       </c>
       <c r="H11" s="5" t="inlineStr">
@@ -1090,7 +1102,7 @@
       <c r="I11" s="5" t="n"/>
       <c r="J11" s="5" t="inlineStr">
         <is>
-          <t>BLS-BLS12-381</t>
+          <t>DLIES, ECIES</t>
         </is>
       </c>
       <c r="K11" s="5" t="n"/>
@@ -1108,50 +1120,54 @@
     <row r="12" ht="23" customHeight="1">
       <c r="A12" s="5" t="inlineStr">
         <is>
-          <t>boringssl</t>
-        </is>
-      </c>
-      <c r="B12" s="13" t="n"/>
+          <t>blake3-1.8.5</t>
+        </is>
+      </c>
+      <c r="B12" s="13" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="C12" s="5" t="inlineStr">
         <is>
-          <t>OpenSSL AND ISC</t>
-        </is>
-      </c>
-      <c r="D12" s="11" t="inlineStr">
-        <is>
-          <t>UNRELEASED</t>
+          <t>CC0-1.0 OR Apache-2.0</t>
+        </is>
+      </c>
+      <c r="D12" s="3" t="inlineStr">
+        <is>
+          <t>1.8.5</t>
         </is>
       </c>
       <c r="E12" s="3" t="inlineStr">
         <is>
-          <t>https://github.com/google/boringssl</t>
+          <t>https://github.com/BLAKE3-team/BLAKE3</t>
         </is>
       </c>
       <c r="F12" s="5" t="inlineStr">
         <is>
-          <t>https://github.com/google/boringssl/archive/refs/tags/0.20260211.0.tar.gz</t>
+          <t>https://github.com/BLAKE3-team/BLAKE3/archive/refs/tags/1.8.5.tar.gz</t>
         </is>
       </c>
       <c r="G12" s="5" t="inlineStr">
         <is>
-          <t>BoringSSL — Google OpenSSL fork (C); ML-KEM; rolling snapshots, used by Chrome/Android/gRPC</t>
+          <t>BLAKE3 reference implementation (Rust + C)</t>
         </is>
       </c>
       <c r="H12" s="5" t="inlineStr">
         <is>
-          <t>0.20260211.0 (rolling snapshot)</t>
+          <t>1.8.5 (2026-04-25)</t>
         </is>
       </c>
       <c r="I12" s="5" t="n"/>
       <c r="J12" s="5" t="inlineStr">
         <is>
-          <t>AES-[128|256]-[GCM|CBC|CTR|CCM|XTS], ChaCha20-Poly1305, SHA-[256|384|512], HMAC-[SHA-256|SHA-384|SHA-512], AES-[128|256]-CMAC, RSAES-OAEP-[2048|3072|4096]-*, ECDH-[P-256|P-384|P-521], ECDH-[Curve25519|X25519], ECDSA-[P-256|P-384|P-521]-*, EdDSA-Ed25519, RSASSA-PSS-[2048|3072|4096]-*, HKDF-[SHA-256|SHA-384|SHA-512], ML-KEM-[512|768|1024]</t>
+          <t>BLAKE3</t>
         </is>
       </c>
       <c r="K12" s="5" t="n"/>
       <c r="L12" s="5" t="inlineStr">
         <is>
-          <t>RSA: expired 2000; ECC: Certicom/BlackBerry largely expired 2017–2022; ML-KEM: NIST patent licenses secured; AES, ChaCha20, SHA, HMAC: no known patents. Hybrid OpenSSL+ISC license; no explicit patent grant.</t>
+          <t>No known patents.</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
@@ -1163,7 +1179,7 @@
     <row r="13" ht="23" customHeight="1">
       <c r="A13" s="5" t="inlineStr">
         <is>
-          <t>botan-3.11.1</t>
+          <t>blst-0.3.16</t>
         </is>
       </c>
       <c r="B13" s="13" t="inlineStr">
@@ -1173,52 +1189,44 @@
       </c>
       <c r="C13" s="5" t="inlineStr">
         <is>
-          <t>BSD-2-Clause</t>
+          <t>Apache-2.0</t>
         </is>
       </c>
       <c r="D13" s="3" t="inlineStr">
         <is>
-          <t>3.11.1</t>
+          <t>0.3.16</t>
         </is>
       </c>
       <c r="E13" s="3" t="inlineStr">
         <is>
-          <t>https://github.com/randombit/botan</t>
+          <t>https://github.com/supranational/blst</t>
         </is>
       </c>
       <c r="F13" s="5" t="inlineStr">
         <is>
-          <t>https://github.com/randombit/botan/archive/refs/tags/3.11.1.zip</t>
+          <t>https://github.com/supranational/blst/archive/refs/tags/v0.3.16.tar.gz</t>
         </is>
       </c>
       <c r="G13" s="5" t="inlineStr">
         <is>
-          <t>BSI-commissioned cryptographic library (Rohde &amp; Schwarz Cybersecurity). BSI formally recommends this version for security-sensitive applications. Supports all BSI TR-02102-1 PQC algorithms (FrodoKEM, Classic McEliece, ML-KEM, ML-DSA, SLH-DSA, XMSS, HSS/LMS). TLS 1.3 hybrid PQ key exchange. RSCS1 variant includes BSI-specific patches (compliant ECDH). Native APIs: C++, C, Python.</t>
+          <t>BLS12-381 signature library (Supranational)</t>
         </is>
       </c>
       <c r="H13" s="5" t="inlineStr">
         <is>
-          <t>BSI recommended</t>
-        </is>
-      </c>
-      <c r="I13" s="5" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
+          <t>v0.3.16 (2025-09-19)</t>
+        </is>
+      </c>
+      <c r="I13" s="5" t="n"/>
       <c r="J13" s="5" t="inlineStr">
         <is>
-          <t>AES-[128|192|256]-*, SHA-[256|384|512], SHA3-*, HMAC-*, ECDSA-*, EdDSA-*, RSASSA-PSS-*, ECDH-*, ML-KEM-[512|768|1024], ML-DSA-[44|65|87]-*, SLH-DSA-*, FrodoKEM-[640|976|1344], ClassicMcEliece-*, XMSS-*, LMS-*, Argon2id-*, bcrypt-*, scrypt-*, ChaCha20-Poly1305</t>
-        </is>
-      </c>
-      <c r="K13" s="5" t="inlineStr">
-        <is>
-          <t>https://www.bsi.bund.de/SharedDocs/Downloads/DE/BSI/Krypto/Projektzusammenfassung_Botan.pdf?__blob=publicationFile&amp;v=1</t>
-        </is>
-      </c>
+          <t>BLS-BLS12-381</t>
+        </is>
+      </c>
+      <c r="K13" s="5" t="n"/>
       <c r="L13" s="5" t="inlineStr">
         <is>
-          <t>No known patents for Botan implementation. ML-KEM/ML-DSA/SLH-DSA: NIST patent licenses secured. FrodoKEM: no known patents. Classic McEliece: believed patent-free. XMSS/LMS: no known patents. NTRU patents (Security Innovation) placed in public domain March 2017.</t>
+          <t>No known patents.</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
@@ -1230,62 +1238,50 @@
     <row r="14" ht="23" customHeight="1">
       <c r="A14" s="5" t="inlineStr">
         <is>
-          <t>botan-3.7.1-RSCS1</t>
-        </is>
-      </c>
-      <c r="B14" s="13" t="inlineStr">
-        <is>
-          <t>(x)</t>
-        </is>
-      </c>
+          <t>boringssl</t>
+        </is>
+      </c>
+      <c r="B14" s="13" t="n"/>
       <c r="C14" s="5" t="inlineStr">
         <is>
-          <t>BSD-2-Clause</t>
-        </is>
-      </c>
-      <c r="D14" s="3" t="inlineStr">
-        <is>
-          <t>3.7.1-RSCS1</t>
+          <t>OpenSSL AND ISC</t>
+        </is>
+      </c>
+      <c r="D14" s="11" t="inlineStr">
+        <is>
+          <t>UNRELEASED</t>
         </is>
       </c>
       <c r="E14" s="3" t="inlineStr">
         <is>
-          <t>https://github.com/Rohde-Schwarz/botan</t>
+          <t>https://github.com/google/boringssl</t>
         </is>
       </c>
       <c r="F14" s="5" t="inlineStr">
         <is>
-          <t>https://github.com/Rohde-Schwarz/botan/releases/download/3.7.1-RSCS1/botan-3.7.1-RSCS1.zip</t>
+          <t>https://github.com/google/boringssl/archive/refs/tags/0.20260211.0.tar.gz</t>
         </is>
       </c>
       <c r="G14" s="5" t="inlineStr">
         <is>
-          <t>BSI-commissioned cryptographic library (Rohde &amp; Schwarz Cybersecurity). BSI formally recommends this version for security-sensitive applications. Supports all BSI TR-02102-1 PQC algorithms (FrodoKEM, Classic McEliece, ML-KEM, ML-DSA, SLH-DSA, XMSS, HSS/LMS). TLS 1.3 hybrid PQ key exchange. RSCS1 variant includes BSI-specific patches (compliant ECDH). Native APIs: C++, C, Python.</t>
+          <t>BoringSSL — Google OpenSSL fork (C); ML-KEM; rolling snapshots, used by Chrome/Android/gRPC</t>
         </is>
       </c>
       <c r="H14" s="5" t="inlineStr">
         <is>
-          <t>BSI recommended</t>
-        </is>
-      </c>
-      <c r="I14" s="5" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
+          <t>0.20260211.0 (rolling snapshot)</t>
+        </is>
+      </c>
+      <c r="I14" s="5" t="n"/>
       <c r="J14" s="5" t="inlineStr">
         <is>
-          <t>AES-[128|192|256]-*, SHA-[256|384|512], SHA3-*, HMAC-*, ECDSA-*, EdDSA-*, RSASSA-PSS-*, ECDH-*, ML-KEM-[512|768|1024], ML-DSA-[44|65|87]-*, SLH-DSA-*, FrodoKEM-[640|976|1344], ClassicMcEliece-*, XMSS-*, LMS-*, Argon2id-*, bcrypt-*, scrypt-*, ChaCha20-Poly1305</t>
-        </is>
-      </c>
-      <c r="K14" s="5" t="inlineStr">
-        <is>
-          <t>https://www.bsi.bund.de/SharedDocs/Downloads/DE/BSI/Krypto/Projektzusammenfassung_Botan.pdf?__blob=publicationFile&amp;v=1</t>
-        </is>
-      </c>
+          <t>AES-[128|256]-[GCM|CBC|CTR|CCM|XTS], ChaCha20-Poly1305, SHA-[256|384|512], HMAC-[SHA-256|SHA-384|SHA-512], AES-[128|256]-CMAC, RSAES-OAEP-[2048|3072|4096]-*, ECDH-[P-256|P-384|P-521], ECDH-[Curve25519|X25519], ECDSA-[P-256|P-384|P-521]-*, EdDSA-Ed25519, RSASSA-PSS-[2048|3072|4096]-*, HKDF-[SHA-256|SHA-384|SHA-512], ML-KEM-[512|768|1024]</t>
+        </is>
+      </c>
+      <c r="K14" s="5" t="n"/>
       <c r="L14" s="5" t="inlineStr">
         <is>
-          <t>No known patents for Botan implementation. ML-KEM/ML-DSA/SLH-DSA: NIST patent licenses secured. FrodoKEM: no known patents. Classic McEliece: believed patent-free. XMSS/LMS: no known patents. NTRU patents (Security Innovation) placed in public domain March 2017.</t>
+          <t>RSA: expired 2000; ECC: Certicom/BlackBerry largely expired 2017–2022; ML-KEM: NIST patent licenses secured; AES, ChaCha20, SHA, HMAC: no known patents. Hybrid OpenSSL+ISC license; no explicit patent grant.</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
@@ -1297,7 +1293,7 @@
     <row r="15" ht="23" customHeight="1">
       <c r="A15" s="5" t="inlineStr">
         <is>
-          <t>circl-1.6.3</t>
+          <t>botan-3.12.0</t>
         </is>
       </c>
       <c r="B15" s="13" t="inlineStr">
@@ -1307,48 +1303,52 @@
       </c>
       <c r="C15" s="5" t="inlineStr">
         <is>
-          <t>BSD-3-Clause</t>
+          <t>BSD-2-Clause</t>
         </is>
       </c>
       <c r="D15" s="3" t="inlineStr">
         <is>
-          <t>1.6.3</t>
+          <t>3.12.0</t>
         </is>
       </c>
       <c r="E15" s="3" t="inlineStr">
         <is>
-          <t>https://github.com/cloudflare/circl</t>
+          <t>https://github.com/randombit/botan</t>
         </is>
       </c>
       <c r="F15" s="5" t="inlineStr">
         <is>
-          <t>https://github.com/cloudflare/circl/archive/refs/tags/v1.6.3.tar.gz</t>
+          <t>https://github.com/randombit/botan/archive/refs/tags/3.12.0.zip</t>
         </is>
       </c>
       <c r="G15" s="5" t="inlineStr">
         <is>
-          <t>Cloudflare CIRCL — Go crypto library; ML-KEM, ML-DSA, SLH-DSA, FrodoKEM, hybrid KEMs; used in Cloudflare production TLS</t>
+          <t>BSI-commissioned cryptographic library (Rohde &amp; Schwarz Cybersecurity). BSI formally recommends this version for security-sensitive applications. Supports all BSI TR-02102-1 PQC algorithms (FrodoKEM, Classic McEliece, ML-KEM, ML-DSA, SLH-DSA, XMSS, HSS/LMS). TLS 1.3 hybrid PQ key exchange. RSCS1 variant includes BSI-specific patches (compliant ECDH). Native APIs: C++, C, Python.</t>
         </is>
       </c>
       <c r="H15" s="5" t="inlineStr">
         <is>
-          <t>v1.6.3</t>
+          <t>3.12.0 (2026-05-07)</t>
         </is>
       </c>
       <c r="I15" s="5" t="inlineStr">
         <is>
-          <t>stable</t>
+          <t>active</t>
         </is>
       </c>
       <c r="J15" s="5" t="inlineStr">
         <is>
-          <t>ML-KEM-[512|768|1024], ML-DSA-[44|65|87]-*, SLH-DSA-*, FrodoKEM-*, ECDH-[P-256|P-384|P-521], ECDH-[Curve25519|X25519], ECDH-[Curve448|X448], EdDSA-[Ed25519|Ed448], ECDSA-[P-256|P-384|P-521]-*, HKDF-[SHA-256|SHA-384|SHA-512]</t>
-        </is>
-      </c>
-      <c r="K15" s="5" t="n"/>
+          <t>AES-[128|192|256]-*, SHA-[256|384|512], SHA3-*, HMAC-*, ECDSA-*, EdDSA-*, RSASSA-PSS-*, ECDH-*, ML-KEM-[512|768|1024], ML-DSA-[44|65|87]-*, SLH-DSA-*, FrodoKEM-[640|976|1344], ClassicMcEliece-*, XMSS-*, LMS-*, Argon2id-*, bcrypt-*, scrypt-*, ChaCha20-Poly1305, GOSTR3411-2012, GOSTR3410, GOST-28147, Grasshopper, GMAC</t>
+        </is>
+      </c>
+      <c r="K15" s="5" t="inlineStr">
+        <is>
+          <t>https://www.bsi.bund.de/SharedDocs/Downloads/DE/BSI/Krypto/Projektzusammenfassung_Botan.pdf?__blob=publicationFile&amp;v=1</t>
+        </is>
+      </c>
       <c r="L15" s="5" t="inlineStr">
         <is>
-          <t>ML-KEM: NIST patent licenses secured; ML-DSA, SLH-DSA: no known patents; ECC (ECDH, EdDSA, ECDSA): Certicom/BlackBerry largely expired; FrodoKEM: no known patents. BSD-3-Clause.</t>
+          <t>No known patents for Botan implementation. ML-KEM/ML-DSA/SLH-DSA: NIST patent licenses secured. FrodoKEM: no known patents. Classic McEliece: believed patent-free. XMSS/LMS: no known patents. NTRU patents (Security Innovation) placed in public domain March 2017.</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
@@ -1360,50 +1360,62 @@
     <row r="16" ht="23" customHeight="1">
       <c r="A16" s="5" t="inlineStr">
         <is>
-          <t>cross-implementation</t>
-        </is>
-      </c>
-      <c r="B16" s="13" t="n"/>
-      <c r="C16" s="10" t="inlineStr">
-        <is>
-          <t>UNKNOWN</t>
-        </is>
-      </c>
-      <c r="D16" s="11" t="inlineStr">
-        <is>
-          <t>2.2</t>
+          <t>botan-3.7.1-RSCS1</t>
+        </is>
+      </c>
+      <c r="B16" s="13" t="inlineStr">
+        <is>
+          <t>(x)</t>
+        </is>
+      </c>
+      <c r="C16" s="5" t="inlineStr">
+        <is>
+          <t>BSD-2-Clause</t>
+        </is>
+      </c>
+      <c r="D16" s="3" t="inlineStr">
+        <is>
+          <t>3.7.1-RSCS1</t>
         </is>
       </c>
       <c r="E16" s="3" t="inlineStr">
         <is>
-          <t>https://github.com/CROSS-signature/CROSS-implementation</t>
+          <t>https://github.com/Rohde-Schwarz/botan</t>
         </is>
       </c>
       <c r="F16" s="5" t="inlineStr">
         <is>
-          <t>https://github.com/CROSS-signature/CROSS-implementation/archive/refs/heads/main.tar.gz</t>
+          <t>https://github.com/Rohde-Schwarz/botan/releases/download/3.7.1-RSCS1/botan-3.7.1-RSCS1.zip</t>
         </is>
       </c>
       <c r="G16" s="5" t="inlineStr">
         <is>
-          <t>CROSS — Codes and Restricted Objects Signature Scheme</t>
+          <t>BSI-commissioned cryptographic library (Rohde &amp; Schwarz Cybersecurity). BSI formally recommends this version for security-sensitive applications. Supports all BSI TR-02102-1 PQC algorithms (FrodoKEM, Classic McEliece, ML-KEM, ML-DSA, SLH-DSA, XMSS, HSS/LMS). TLS 1.3 hybrid PQ key exchange. RSCS1 variant includes BSI-specific patches (compliant ECDH). Native APIs: C++, C, Python.</t>
         </is>
       </c>
       <c r="H16" s="5" t="inlineStr">
         <is>
-          <t>v2.2</t>
-        </is>
-      </c>
-      <c r="I16" s="5" t="n"/>
+          <t>BSI recommended</t>
+        </is>
+      </c>
+      <c r="I16" s="5" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
       <c r="J16" s="5" t="inlineStr">
         <is>
-          <t>CROSS-*</t>
-        </is>
-      </c>
-      <c r="K16" s="5" t="n"/>
+          <t>AES-[128|192|256]-*, SHA-[256|384|512], SHA3-*, HMAC-*, ECDSA-*, EdDSA-*, RSASSA-PSS-*, ECDH-*, ML-KEM-[512|768|1024], ML-DSA-[44|65|87]-*, SLH-DSA-*, FrodoKEM-[640|976|1344], ClassicMcEliece-*, XMSS-*, LMS-*, Argon2id-*, bcrypt-*, scrypt-*, ChaCha20-Poly1305</t>
+        </is>
+      </c>
+      <c r="K16" s="5" t="inlineStr">
+        <is>
+          <t>https://www.bsi.bund.de/SharedDocs/Downloads/DE/BSI/Krypto/Projektzusammenfassung_Botan.pdf?__blob=publicationFile&amp;v=1</t>
+        </is>
+      </c>
       <c r="L16" s="5" t="inlineStr">
         <is>
-          <t>No known patents (NIST Round 2 submission requirement: patent-free).</t>
+          <t>No known patents for Botan implementation. ML-KEM/ML-DSA/SLH-DSA: NIST patent licenses secured. FrodoKEM: no known patents. Classic McEliece: believed patent-free. XMSS/LMS: no known patents. NTRU patents (Security Innovation) placed in public domain March 2017.</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
@@ -1415,7 +1427,7 @@
     <row r="17" ht="23" customHeight="1">
       <c r="A17" s="5" t="inlineStr">
         <is>
-          <t>cryptopp-8.9.0</t>
+          <t>circl-1.6.3</t>
         </is>
       </c>
       <c r="B17" s="13" t="inlineStr">
@@ -1425,32 +1437,32 @@
       </c>
       <c r="C17" s="5" t="inlineStr">
         <is>
-          <t>BSL-1.0</t>
+          <t>BSD-3-Clause</t>
         </is>
       </c>
       <c r="D17" s="3" t="inlineStr">
         <is>
-          <t>8.9.0</t>
+          <t>1.6.3</t>
         </is>
       </c>
       <c r="E17" s="3" t="inlineStr">
         <is>
-          <t>https://github.com/weidai11/cryptopp</t>
+          <t>https://github.com/cloudflare/circl</t>
         </is>
       </c>
       <c r="F17" s="5" t="inlineStr">
         <is>
-          <t>https://github.com/weidai11/cryptopp/archive/refs/tags/CRYPTOPP_8_9_0.tar.gz</t>
+          <t>https://github.com/cloudflare/circl/archive/refs/tags/v1.6.3.tar.gz</t>
         </is>
       </c>
       <c r="G17" s="5" t="inlineStr">
         <is>
-          <t>Crypto++ — C++ crypto library; no PQC in 8.9.0 (Oct 2023, last official release)</t>
+          <t>Cloudflare CIRCL — Go crypto library; ML-KEM, ML-DSA, SLH-DSA, FrodoKEM, hybrid KEMs; used in Cloudflare production TLS</t>
         </is>
       </c>
       <c r="H17" s="5" t="inlineStr">
         <is>
-          <t>CRYPTOPP_8_9_0</t>
+          <t>v1.6.3</t>
         </is>
       </c>
       <c r="I17" s="5" t="inlineStr">
@@ -1460,13 +1472,13 @@
       </c>
       <c r="J17" s="5" t="inlineStr">
         <is>
-          <t>AES-[128|192|256]-[GCM|CCM|CBC|CTR|OFB|CFB128|XTS|ECB], ChaCha20-*, SHA-[256|384|512], SHA3-[256|384|512], HMAC-[SHA-256|SHA-384|SHA-512], AES-[128|192|256]-CMAC, RSAES-OAEP-[2048|3072|4096]-*, ECDH-[P-256|P-384|P-521], ECDSA-[P-256|P-384|P-521]-*, RSASSA-PSS-[2048|3072|4096]-*, HKDF-[SHA-256|SHA-384|SHA-512], PBKDF2-HMAC-[SHA-256|SHA-384|SHA-512]-*</t>
+          <t>ML-KEM-[512|768|1024], ML-DSA-[44|65|87]-*, SLH-DSA-*, FrodoKEM-*, ECDH-[P-256|P-384|P-521], ECDH-[Curve25519|X25519], ECDH-[Curve448|X448], EdDSA-[Ed25519|Ed448], ECDSA-[P-256|P-384|P-521]-*, HKDF-[SHA-256|SHA-384|SHA-512]</t>
         </is>
       </c>
       <c r="K17" s="5" t="n"/>
       <c r="L17" s="5" t="inlineStr">
         <is>
-          <t>RSA: expired 2000; DH: expired 1997; ECC: Certicom/BlackBerry largely expired 2017–2022; AES, ChaCha20, SHA, HMAC: no known patents. BSL-1.0 (no explicit patent grant).</t>
+          <t>ML-KEM: NIST patent licenses secured; ML-DSA, SLH-DSA: no known patents; ECC (ECDH, EdDSA, ECDSA): Certicom/BlackBerry largely expired; FrodoKEM: no known patents. BSD-3-Clause.</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
@@ -1478,56 +1490,56 @@
     <row r="18" ht="23" customHeight="1">
       <c r="A18" s="5" t="inlineStr">
         <is>
-          <t>crystals-go</t>
+          <t>conscrypt-1.4.2</t>
         </is>
       </c>
       <c r="B18" s="13" t="n"/>
-      <c r="C18" s="5" t="inlineStr">
+      <c r="C18" s="10" t="inlineStr">
         <is>
           <t>Apache-2.0</t>
         </is>
       </c>
-      <c r="D18" s="11" t="inlineStr">
-        <is>
-          <t>UNRELEASED</t>
+      <c r="D18" s="3" t="inlineStr">
+        <is>
+          <t>1.4.2</t>
         </is>
       </c>
       <c r="E18" s="3" t="inlineStr">
         <is>
-          <t>https://github.com/kudelskisecurity/crystals-go</t>
+          <t>https://github.com/google/conscrypt</t>
         </is>
       </c>
       <c r="F18" s="5" t="inlineStr">
         <is>
-          <t>https://github.com/kudelskisecurity/crystals-go/archive/refs/heads/main.tar.gz</t>
+          <t>https://github.com/google/conscrypt/archive/refs/tags/1.4.2.tar.gz</t>
         </is>
       </c>
       <c r="G18" s="5" t="inlineStr">
         <is>
-          <t>crystals-go — Go CRYSTALS impl ⚠ ARCHIVED — KyberSlash patch applied, then retired</t>
+          <t>Conscrypt — Java JCA/JSSE security provider backed by BoringSSL (Java + JNI)</t>
         </is>
       </c>
       <c r="H18" s="5" t="inlineStr">
         <is>
-          <t>Archived 2023 (unmaintained)</t>
+          <t>1.4.2</t>
         </is>
       </c>
       <c r="I18" s="5" t="inlineStr">
         <is>
-          <t>retired</t>
+          <t>previous</t>
         </is>
       </c>
       <c r="J18" s="5" t="inlineStr">
         <is>
-          <t>ML-KEM-[512|768|1024], ML-DSA-[44|65|87]-*</t>
-        </is>
-      </c>
-      <c r="K18" s="5" t="n"/>
-      <c r="L18" s="5" t="inlineStr">
-        <is>
-          <t>ML-KEM: NIST patent licenses secured. No library-level patents.</t>
-        </is>
-      </c>
+          <t>AES-[128|192|256]-[GCM|CBC], ChaCha20-Poly1305, ECDH-*, RSAES-OAEP-*, RSASSA-PSS-*, ECDSA-*, EdDSA-Ed25519, HMAC-[SHA-256|SHA-512]</t>
+        </is>
+      </c>
+      <c r="K18" s="5" t="inlineStr">
+        <is>
+          <t>Previous major line (1.x; superseded). Wraps BoringSSL.</t>
+        </is>
+      </c>
+      <c r="L18" s="5" t="n"/>
       <c r="M18" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve"> </t>
@@ -1537,52 +1549,60 @@
     <row r="19" ht="23" customHeight="1">
       <c r="A19" s="5" t="inlineStr">
         <is>
-          <t>dilithium</t>
-        </is>
-      </c>
-      <c r="B19" s="13" t="n"/>
-      <c r="C19" s="5" t="inlineStr">
-        <is>
-          <t>CC0-1.0 OR Apache-2.0</t>
-        </is>
-      </c>
-      <c r="D19" s="11" t="inlineStr">
-        <is>
-          <t>3.1</t>
+          <t>conscrypt-2.5.3</t>
+        </is>
+      </c>
+      <c r="B19" s="13" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="C19" s="10" t="inlineStr">
+        <is>
+          <t>Apache-2.0</t>
+        </is>
+      </c>
+      <c r="D19" s="3" t="inlineStr">
+        <is>
+          <t>2.5.3</t>
         </is>
       </c>
       <c r="E19" s="3" t="inlineStr">
         <is>
-          <t>https://github.com/pq-crystals/dilithium</t>
+          <t>https://github.com/google/conscrypt</t>
         </is>
       </c>
       <c r="F19" s="5" t="inlineStr">
         <is>
-          <t>https://github.com/pq-crystals/dilithium/archive/refs/heads/master.tar.gz</t>
+          <t>https://github.com/google/conscrypt/archive/refs/tags/2.5.3.tar.gz</t>
         </is>
       </c>
       <c r="G19" s="5" t="inlineStr">
         <is>
-          <t>Dilithium / ML-DSA (CRYSTALS reference C + AVX2)</t>
+          <t>Conscrypt — Java JCA/JSSE security provider backed by BoringSSL (Java + JNI)</t>
         </is>
       </c>
       <c r="H19" s="5" t="inlineStr">
         <is>
-          <t>v3.1 (pre-FIPS 204; superseded by ML-DSA)</t>
-        </is>
-      </c>
-      <c r="I19" s="5" t="n"/>
+          <t>2.5.3 (release date: verify)</t>
+        </is>
+      </c>
+      <c r="I19" s="5" t="inlineStr">
+        <is>
+          <t>stable</t>
+        </is>
+      </c>
       <c r="J19" s="5" t="inlineStr">
         <is>
-          <t>ML-DSA-[44|65|87]-*, HashML-DSA-[44|65|87]-*</t>
-        </is>
-      </c>
-      <c r="K19" s="5" t="n"/>
-      <c r="L19" s="5" t="inlineStr">
-        <is>
-          <t>No known patents.</t>
-        </is>
-      </c>
+          <t>AES-[128|192|256]-[GCM|CBC], ChaCha20-Poly1305, ECDH-*, RSAES-OAEP-*, RSASSA-PSS-*, ECDSA-*, EdDSA-Ed25519, ML-DSA-65, HMAC-[SHA-256|SHA-512]</t>
+        </is>
+      </c>
+      <c r="K19" s="5" t="inlineStr">
+        <is>
+          <t>Wraps BoringSSL; used in Android and gRPC.</t>
+        </is>
+      </c>
+      <c r="L19" s="5" t="n"/>
       <c r="M19" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve"> </t>
@@ -1592,10 +1612,14 @@
     <row r="20" ht="23" customHeight="1">
       <c r="A20" s="5" t="inlineStr">
         <is>
-          <t>draft-kwiatkowski-tls-ecdhe-mlkem</t>
-        </is>
-      </c>
-      <c r="B20" s="13" t="n"/>
+          <t>cross-implementation</t>
+        </is>
+      </c>
+      <c r="B20" s="13" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="C20" s="10" t="inlineStr">
         <is>
           <t>UNKNOWN</t>
@@ -1603,39 +1627,39 @@
       </c>
       <c r="D20" s="11" t="inlineStr">
         <is>
-          <t>draft-03</t>
+          <t>2.2</t>
         </is>
       </c>
       <c r="E20" s="3" t="inlineStr">
         <is>
-          <t>https://github.com/post-quantum-cryptography/draft-kwiatkowski-tls-ecdhe-mlkem</t>
+          <t>https://github.com/CROSS-signature/CROSS-implementation</t>
         </is>
       </c>
       <c r="F20" s="5" t="inlineStr">
         <is>
-          <t>https://github.com/post-quantum-cryptography/draft-kwiatkowski-tls-ecdhe-mlkem/archive/refs/heads/main.tar.gz</t>
+          <t>https://github.com/CROSS-signature/CROSS-implementation/archive/refs/heads/main.tar.gz</t>
         </is>
       </c>
       <c r="G20" s="5" t="inlineStr">
         <is>
-          <t>post-quantum-cryptography/draft-kwiatkowski-tls-ecdhe-mlkem — TLS hybrid KEM draft</t>
+          <t>CROSS — Codes and Restricted Objects Signature Scheme</t>
         </is>
       </c>
       <c r="H20" s="5" t="inlineStr">
         <is>
-          <t>draft-kwiatkowski-tls-ecdhe-mlkem-03</t>
+          <t>v2.2</t>
         </is>
       </c>
       <c r="I20" s="5" t="n"/>
       <c r="J20" s="5" t="inlineStr">
         <is>
-          <t>ML-KEM-768, ECDH-[Curve25519|X25519]</t>
+          <t>CROSS-*</t>
         </is>
       </c>
       <c r="K20" s="5" t="n"/>
       <c r="L20" s="5" t="inlineStr">
         <is>
-          <t>Protocol draft. ML-KEM: NIST patent licenses secured. ECC: Certicom/BlackBerry portfolio largely expired.</t>
+          <t>No known patents (NIST Round 2 submission requirement: patent-free).</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
@@ -1647,7 +1671,7 @@
     <row r="21" ht="23" customHeight="1">
       <c r="A21" s="5" t="inlineStr">
         <is>
-          <t>faest-avx-2.0.1</t>
+          <t>cryptopp-8.9.0</t>
         </is>
       </c>
       <c r="B21" s="13" t="inlineStr">
@@ -1657,44 +1681,48 @@
       </c>
       <c r="C21" s="5" t="inlineStr">
         <is>
-          <t>MIT</t>
+          <t>BSL-1.0</t>
         </is>
       </c>
       <c r="D21" s="3" t="inlineStr">
         <is>
-          <t>2.0.1</t>
+          <t>8.9.0</t>
         </is>
       </c>
       <c r="E21" s="3" t="inlineStr">
         <is>
-          <t>https://github.com/faest-sign/faest-avx</t>
+          <t>https://github.com/weidai11/cryptopp</t>
         </is>
       </c>
       <c r="F21" s="5" t="inlineStr">
         <is>
-          <t>https://github.com/faest-sign/faest-avx/archive/refs/tags/v2.0.1.tar.gz</t>
+          <t>https://github.com/weidai11/cryptopp/archive/refs/tags/CRYPTOPP_8_9_0.tar.gz</t>
         </is>
       </c>
       <c r="G21" s="5" t="inlineStr">
         <is>
-          <t>FAEST-avx — FAEST AVX2 optimised C++ implementation</t>
+          <t>Crypto++ — C++ crypto library; no PQC in 8.9.0 (Oct 2023, last official release)</t>
         </is>
       </c>
       <c r="H21" s="5" t="inlineStr">
         <is>
-          <t>v2.0.1</t>
-        </is>
-      </c>
-      <c r="I21" s="5" t="n"/>
+          <t>CRYPTOPP_8_9_0</t>
+        </is>
+      </c>
+      <c r="I21" s="5" t="inlineStr">
+        <is>
+          <t>stable</t>
+        </is>
+      </c>
       <c r="J21" s="5" t="inlineStr">
         <is>
-          <t>FAEST-[128s|128f|192s|192f|256s|256f]</t>
+          <t>AES-[128|192|256]-[GCM|CCM|CBC|CTR|OFB|CFB128|XTS|ECB], ChaCha20-*, SHA-[256|384|512], SHA3-[256|384|512], HMAC-[SHA-256|SHA-384|SHA-512], AES-[128|192|256]-CMAC, RSAES-OAEP-[2048|3072|4096]-*, ECDH-[P-256|P-384|P-521], ECDSA-[P-256|P-384|P-521]-*, RSASSA-PSS-[2048|3072|4096]-*, HKDF-[SHA-256|SHA-384|SHA-512], PBKDF2-HMAC-[SHA-256|SHA-384|SHA-512]-*, SEED, ARIA, Camellia, Serpent-*, Twofish-*, Threefish-*, Rabbit</t>
         </is>
       </c>
       <c r="K21" s="5" t="n"/>
       <c r="L21" s="5" t="inlineStr">
         <is>
-          <t>No known patents (NIST Round 2 submission requirement: patent-free).</t>
+          <t>RSA: expired 2000; DH: expired 1997; ECC: Certicom/BlackBerry largely expired 2017–2022; AES, ChaCha20, SHA, HMAC: no known patents. BSL-1.0 (no explicit patent grant).</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
@@ -1706,50 +1734,54 @@
     <row r="22" ht="23" customHeight="1">
       <c r="A22" s="5" t="inlineStr">
         <is>
-          <t>faest-ref</t>
+          <t>crystals-go</t>
         </is>
       </c>
       <c r="B22" s="13" t="n"/>
       <c r="C22" s="5" t="inlineStr">
         <is>
-          <t>MIT</t>
+          <t>Apache-2.0</t>
         </is>
       </c>
       <c r="D22" s="11" t="inlineStr">
         <is>
-          <t>2.0.4</t>
+          <t>UNRELEASED</t>
         </is>
       </c>
       <c r="E22" s="3" t="inlineStr">
         <is>
-          <t>https://github.com/faest-sign/faest-ref</t>
+          <t>https://github.com/kudelskisecurity/crystals-go</t>
         </is>
       </c>
       <c r="F22" s="5" t="inlineStr">
         <is>
-          <t>https://github.com/faest-sign/faest-ref/archive/refs/heads/main.tar.gz</t>
+          <t>https://github.com/kudelskisecurity/crystals-go/archive/refs/heads/main.tar.gz</t>
         </is>
       </c>
       <c r="G22" s="5" t="inlineStr">
         <is>
-          <t>FAEST-ref — FAEST reference C implementation (VOLEitH, AES-based)</t>
+          <t>crystals-go — Go CRYSTALS impl ⚠ ARCHIVED — KyberSlash patch applied, then retired</t>
         </is>
       </c>
       <c r="H22" s="5" t="inlineStr">
         <is>
-          <t>v2.0.4</t>
-        </is>
-      </c>
-      <c r="I22" s="5" t="n"/>
+          <t>Archived 2023 (unmaintained)</t>
+        </is>
+      </c>
+      <c r="I22" s="5" t="inlineStr">
+        <is>
+          <t>retired</t>
+        </is>
+      </c>
       <c r="J22" s="5" t="inlineStr">
         <is>
-          <t>FAEST-[128s|128f|192s|192f|256s|256f]</t>
+          <t>ML-KEM-[512|768|1024], ML-DSA-[44|65|87]-*</t>
         </is>
       </c>
       <c r="K22" s="5" t="n"/>
       <c r="L22" s="5" t="inlineStr">
         <is>
-          <t>No known patents (NIST Round 2 submission requirement: patent-free).</t>
+          <t>ML-KEM: NIST patent licenses secured. No library-level patents.</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
@@ -1761,50 +1793,50 @@
     <row r="23" ht="23" customHeight="1">
       <c r="A23" s="5" t="inlineStr">
         <is>
-          <t>falcon</t>
+          <t>dilithium</t>
         </is>
       </c>
       <c r="B23" s="13" t="n"/>
       <c r="C23" s="5" t="inlineStr">
         <is>
-          <t>MIT</t>
+          <t>CC0-1.0 OR Apache-2.0</t>
         </is>
       </c>
       <c r="D23" s="11" t="inlineStr">
         <is>
-          <t>UNRELEASED</t>
+          <t>3.1</t>
         </is>
       </c>
       <c r="E23" s="3" t="inlineStr">
         <is>
-          <t>https://falcon-sign.info/</t>
+          <t>https://github.com/pq-crystals/dilithium</t>
         </is>
       </c>
       <c r="F23" s="5" t="inlineStr">
         <is>
-          <t>https://falcon-sign.info/Falcon-impl-20211101.zip</t>
+          <t>https://github.com/pq-crystals/dilithium/archive/refs/heads/master.tar.gz</t>
         </is>
       </c>
       <c r="G23" s="5" t="inlineStr">
         <is>
-          <t>Falcon / FN-DSA official C reference (falcon-sign.info)</t>
+          <t>Dilithium / ML-DSA (CRYSTALS reference C + AVX2)</t>
         </is>
       </c>
       <c r="H23" s="5" t="inlineStr">
         <is>
-          <t>No formal releases — Round 3.1 zip on official site</t>
+          <t>v3.1 (pre-FIPS 204; superseded by ML-DSA)</t>
         </is>
       </c>
       <c r="I23" s="5" t="n"/>
       <c r="J23" s="5" t="inlineStr">
         <is>
-          <t>FN-DSA-[512|1024]</t>
+          <t>ML-DSA-[44|65|87]-*, HashML-DSA-[44|65|87]-*</t>
         </is>
       </c>
       <c r="K23" s="5" t="n"/>
       <c r="L23" s="5" t="inlineStr">
         <is>
-          <t>NTRU-related patents (Security Innovation, formerly NTRU Cryptosystems): placed in public domain March 2017. NIST requirements for FIPS 206 ensure patent freedom.</t>
+          <t>No known patents.</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
@@ -1816,52 +1848,60 @@
     <row r="24" ht="23" customHeight="1">
       <c r="A24" s="5" t="inlineStr">
         <is>
-          <t>falcon-py</t>
-        </is>
-      </c>
-      <c r="B24" s="13" t="n"/>
-      <c r="C24" s="5" t="inlineStr">
+          <t>dotnet-runtime-10.0.9</t>
+        </is>
+      </c>
+      <c r="B24" s="13" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="C24" s="10" t="inlineStr">
         <is>
           <t>MIT</t>
         </is>
       </c>
-      <c r="D24" s="11" t="inlineStr">
-        <is>
-          <t>UNRELEASED</t>
+      <c r="D24" s="3" t="inlineStr">
+        <is>
+          <t>10.0.9</t>
         </is>
       </c>
       <c r="E24" s="3" t="inlineStr">
         <is>
-          <t>https://github.com/tprest/falcon.py</t>
+          <t>https://github.com/dotnet/runtime</t>
         </is>
       </c>
       <c r="F24" s="5" t="inlineStr">
         <is>
-          <t>https://github.com/tprest/falcon.py/archive/refs/heads/master.tar.gz</t>
+          <t>https://github.com/dotnet/runtime/archive/refs/tags/v10.0.9.tar.gz</t>
         </is>
       </c>
       <c r="G24" s="5" t="inlineStr">
         <is>
-          <t>Falcon Python reference (Thomas Prest)</t>
+          <t>.NET runtime and base class libraries (System.Security.Cryptography); C# with native interop</t>
         </is>
       </c>
       <c r="H24" s="5" t="inlineStr">
         <is>
-          <t>No formal releases — rolling</t>
-        </is>
-      </c>
-      <c r="I24" s="5" t="n"/>
+          <t>v10.0.9 (2026-06-09); .NET 10 LTS</t>
+        </is>
+      </c>
+      <c r="I24" s="5" t="inlineStr">
+        <is>
+          <t>lts</t>
+        </is>
+      </c>
       <c r="J24" s="5" t="inlineStr">
         <is>
-          <t>FN-DSA-[512|1024]</t>
-        </is>
-      </c>
-      <c r="K24" s="5" t="n"/>
-      <c r="L24" s="5" t="inlineStr">
-        <is>
-          <t>NTRU-related patents (Security Innovation): placed in public domain March 2017.</t>
-        </is>
-      </c>
+          <t>AES-[128|192|256]-[GCM|CCM|CBC|CTR], ChaCha20-Poly1305, 3DES, SHA-[1|256|384|512], SHA3-*, MD5, HMAC-*, RSAES-OAEP-*, RSASSA-PSS-*, RSASSA-PKCS1-*, ECDSA-*, ECDH-*, DSA, PBKDF2-*, HKDF</t>
+        </is>
+      </c>
+      <c r="K24" s="5" t="inlineStr">
+        <is>
+          <t>Managed layer routing most primitives to the OS provider (CNG on Windows, OpenSSL on Linux/macOS).</t>
+        </is>
+      </c>
+      <c r="L24" s="5" t="n"/>
       <c r="M24" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve"> </t>
@@ -1871,52 +1911,56 @@
     <row r="25" ht="23" customHeight="1">
       <c r="A25" s="5" t="inlineStr">
         <is>
-          <t>glibc-getentropy</t>
+          <t>dotnet-runtime-9.0.17</t>
         </is>
       </c>
       <c r="B25" s="13" t="n"/>
-      <c r="C25" s="5" t="inlineStr">
-        <is>
-          <t>LGPL-2.1-or-later</t>
-        </is>
-      </c>
-      <c r="D25" s="11" t="inlineStr">
-        <is>
-          <t>N/A</t>
+      <c r="C25" s="10" t="inlineStr">
+        <is>
+          <t>MIT</t>
+        </is>
+      </c>
+      <c r="D25" s="3" t="inlineStr">
+        <is>
+          <t>9.0.17</t>
         </is>
       </c>
       <c r="E25" s="3" t="inlineStr">
         <is>
-          <t>https://sourceware.org/glibc/</t>
-        </is>
-      </c>
-      <c r="F25" s="7" t="inlineStr">
-        <is>
-          <t>https://github.com/bminor/glibc/blob/master/sysdeps/unix/sysv/linux/getentropy.c</t>
+          <t>https://github.com/dotnet/runtime</t>
+        </is>
+      </c>
+      <c r="F25" s="5" t="inlineStr">
+        <is>
+          <t>https://github.com/dotnet/runtime/archive/refs/tags/v9.0.17.tar.gz</t>
         </is>
       </c>
       <c r="G25" s="5" t="inlineStr">
         <is>
-          <t>glibc getentropy() — POSIX entropy interface (GNU C Library)</t>
+          <t>.NET runtime and base class libraries (System.Security.Cryptography); C# with native interop</t>
         </is>
       </c>
       <c r="H25" s="5" t="inlineStr">
         <is>
-          <t>OS library facility</t>
-        </is>
-      </c>
-      <c r="I25" s="5" t="n"/>
+          <t>v9.0.17 (2026-06-09); .NET 9 STS</t>
+        </is>
+      </c>
+      <c r="I25" s="5" t="inlineStr">
+        <is>
+          <t>previous</t>
+        </is>
+      </c>
       <c r="J25" s="5" t="inlineStr">
         <is>
-          <t>getentropy</t>
-        </is>
-      </c>
-      <c r="K25" s="5" t="n"/>
-      <c r="L25" s="5" t="inlineStr">
-        <is>
-          <t>No known patents.</t>
-        </is>
-      </c>
+          <t>AES-[128|192|256]-[GCM|CCM|CBC|CTR], ChaCha20-Poly1305, 3DES, SHA-[1|256|384|512], SHA3-*, MD5, HMAC-*, RSAES-OAEP-*, RSASSA-PSS-*, RSASSA-PKCS1-*, ECDSA-*, ECDH-*, DSA, PBKDF2-*, HKDF</t>
+        </is>
+      </c>
+      <c r="K25" s="5" t="inlineStr">
+        <is>
+          <t>Previous major line (.NET 9 STS).</t>
+        </is>
+      </c>
+      <c r="L25" s="5" t="n"/>
       <c r="M25" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve"> </t>
@@ -1926,58 +1970,50 @@
     <row r="26" ht="23" customHeight="1">
       <c r="A26" s="5" t="inlineStr">
         <is>
-          <t>gmssl-3.1.1</t>
-        </is>
-      </c>
-      <c r="B26" s="13" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
-      <c r="C26" s="5" t="inlineStr">
-        <is>
-          <t>Apache-2.0</t>
-        </is>
-      </c>
-      <c r="D26" s="3" t="inlineStr">
-        <is>
-          <t>3.1.1</t>
+          <t>draft-kwiatkowski-tls-ecdhe-mlkem</t>
+        </is>
+      </c>
+      <c r="B26" s="13" t="n"/>
+      <c r="C26" s="10" t="inlineStr">
+        <is>
+          <t>UNKNOWN</t>
+        </is>
+      </c>
+      <c r="D26" s="11" t="inlineStr">
+        <is>
+          <t>draft-03</t>
         </is>
       </c>
       <c r="E26" s="3" t="inlineStr">
         <is>
-          <t>https://github.com/guanzhi/GmSSL</t>
+          <t>https://github.com/post-quantum-cryptography/draft-kwiatkowski-tls-ecdhe-mlkem</t>
         </is>
       </c>
       <c r="F26" s="5" t="inlineStr">
         <is>
-          <t>https://github.com/guanzhi/GmSSL/archive/refs/tags/v3.1.1.tar.gz</t>
+          <t>https://github.com/post-quantum-cryptography/draft-kwiatkowski-tls-ecdhe-mlkem/archive/refs/heads/main.tar.gz</t>
         </is>
       </c>
       <c r="G26" s="5" t="inlineStr">
         <is>
-          <t>GmSSL — Chinese national cryptographic standards library (C); SM2/SM3/SM4/SM9/ZUC/SM9-KEM</t>
+          <t>post-quantum-cryptography/draft-kwiatkowski-tls-ecdhe-mlkem — TLS hybrid KEM draft</t>
         </is>
       </c>
       <c r="H26" s="5" t="inlineStr">
         <is>
-          <t>v3.1.1 — 2024; stable release</t>
-        </is>
-      </c>
-      <c r="I26" s="5" t="inlineStr">
-        <is>
-          <t>stable</t>
-        </is>
-      </c>
+          <t>draft-kwiatkowski-tls-ecdhe-mlkem-03</t>
+        </is>
+      </c>
+      <c r="I26" s="5" t="n"/>
       <c r="J26" s="5" t="inlineStr">
         <is>
-          <t>SM9-(SIG|SIGNATURE), SM9-(KEM|KEYENCAPSULATION|KEY-ENCAPSULATION), SM9-(ENC|ENCRYPTION|PKE|PUBLICKEY-ENCRYPTION|PUBLIC-KEY-ENCRYPTION), SM9-(KEX|KEYEXCHANGE|KEY-EXCHANGE|KEYAGREE|KEY-AGREE|KEYAGREEMENT|KEY-AGREEMENT), SM2-*, SM3, SM4-[ECB|CBC|CTR|GCM|CCM]-*</t>
+          <t>ML-KEM-768, ECDH-[Curve25519|X25519]</t>
         </is>
       </c>
       <c r="K26" s="5" t="n"/>
       <c r="L26" s="5" t="inlineStr">
         <is>
-          <t>No known patents for GmSSL implementation. SM9 standard owned by State Cryptography Administration of China.</t>
+          <t>Protocol draft. ML-KEM: NIST patent licenses secured. ECC: Certicom/BlackBerry portfolio largely expired.</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
@@ -1989,7 +2025,7 @@
     <row r="27" ht="23" customHeight="1">
       <c r="A27" s="5" t="inlineStr">
         <is>
-          <t>gnutls-3.8.12</t>
+          <t>faest-avx-2.0.1</t>
         </is>
       </c>
       <c r="B27" s="13" t="inlineStr">
@@ -1999,48 +2035,44 @@
       </c>
       <c r="C27" s="5" t="inlineStr">
         <is>
-          <t>LGPL-2.1-or-later</t>
+          <t>MIT</t>
         </is>
       </c>
       <c r="D27" s="3" t="inlineStr">
         <is>
-          <t>3.8.12</t>
+          <t>2.0.1</t>
         </is>
       </c>
       <c r="E27" s="3" t="inlineStr">
         <is>
-          <t>https://gitlab.com/gnutls/gnutls</t>
+          <t>https://github.com/faest-sign/faest-avx</t>
         </is>
       </c>
       <c r="F27" s="5" t="inlineStr">
         <is>
-          <t>https://www.gnupg.org/ftp/gcrypt/gnutls/v3.8/gnutls-3.8.12.tar.xz</t>
+          <t>https://github.com/faest-sign/faest-avx/archive/refs/tags/v2.0.1.tar.gz</t>
         </is>
       </c>
       <c r="G27" s="5" t="inlineStr">
         <is>
-          <t>GnuTLS — TLS/crypto library (C); experimental ML-KEM via --with-liboqs or --with-leancrypto; hybrid X25519+ML-KEM-768 TLS</t>
+          <t>FAEST-avx — FAEST AVX2 optimised C++ implementation</t>
         </is>
       </c>
       <c r="H27" s="5" t="inlineStr">
         <is>
-          <t>3.8.12 (2026-02-09)</t>
-        </is>
-      </c>
-      <c r="I27" s="5" t="inlineStr">
-        <is>
-          <t>stable</t>
-        </is>
-      </c>
+          <t>v2.0.1</t>
+        </is>
+      </c>
+      <c r="I27" s="5" t="n"/>
       <c r="J27" s="5" t="inlineStr">
         <is>
-          <t>AES-[128|192|256]-[GCM|CCM|CBC|CTR|XTS], ChaCha20-Poly1305, SHA-[256|384|512], SHA3-[256|384|512], HMAC-[SHA-256|SHA-384|SHA-512], AES-[128|192|256]-CMAC, RSAES-OAEP-[2048|3072|4096]-*, ECDH-[P-256|P-384|P-521], ECDH-[brainpoolP256r1|brainpoolP384r1|brainpoolP512r1], ECDH-[Curve25519|X25519], ECDH-[Curve448|X448], ECDSA-[P-256|P-384|P-521]-*, EdDSA-[Ed25519|Ed448], RSASSA-PSS-[2048|3072|4096]-*, HKDF-[SHA-256|SHA-384|SHA-512], PBKDF2-HMAC-[SHA-256|SHA-384|SHA-512]-*, ML-KEM-768</t>
+          <t>FAEST-[128s|128f|192s|192f|256s|256f]</t>
         </is>
       </c>
       <c r="K27" s="5" t="n"/>
       <c r="L27" s="5" t="inlineStr">
         <is>
-          <t>RSA: expired 2000; DH: expired 1997; ECC: Certicom/BlackBerry largely expired 2017–2022; ML-KEM: NIST patent licenses secured (via liboqs/leancrypto); AES, ChaCha20, SHA, HMAC: no known patents. LGPL-2.1-or-later.</t>
+          <t>No known patents (NIST Round 2 submission requirement: patent-free).</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
@@ -2052,58 +2084,50 @@
     <row r="28" ht="23" customHeight="1">
       <c r="A28" s="5" t="inlineStr">
         <is>
-          <t>go-1.26.2</t>
-        </is>
-      </c>
-      <c r="B28" s="13" t="inlineStr">
-        <is>
-          <t xml:space="preserve">(c) </t>
-        </is>
-      </c>
+          <t>faest-ref</t>
+        </is>
+      </c>
+      <c r="B28" s="13" t="n"/>
       <c r="C28" s="5" t="inlineStr">
         <is>
-          <t>BSD-3-Clause</t>
-        </is>
-      </c>
-      <c r="D28" s="3" t="inlineStr">
-        <is>
-          <t>1.26.2</t>
+          <t>MIT</t>
+        </is>
+      </c>
+      <c r="D28" s="11" t="inlineStr">
+        <is>
+          <t>2.0.4</t>
         </is>
       </c>
       <c r="E28" s="3" t="inlineStr">
         <is>
-          <t>https://github.com/golang/go</t>
+          <t>https://github.com/faest-sign/faest-ref</t>
         </is>
       </c>
       <c r="F28" s="5" t="inlineStr">
         <is>
-          <t>https://github.com/golang/go/archive/refs/tags/go1.26.2.tar.gz</t>
+          <t>https://github.com/faest-sign/faest-ref/archive/refs/heads/main.tar.gz</t>
         </is>
       </c>
       <c r="G28" s="5" t="inlineStr">
         <is>
-          <t>Go standard library — crypto/* packages (Go); X25519MLKEM768 hybrid TLS default since 1.24; ML-DSA in 1.26+</t>
+          <t>FAEST-ref — FAEST reference C implementation (VOLEitH, AES-based)</t>
         </is>
       </c>
       <c r="H28" s="5" t="inlineStr">
         <is>
-          <t>go1.26.1 (2026-03-05)</t>
-        </is>
-      </c>
-      <c r="I28" s="5" t="inlineStr">
-        <is>
-          <t>stable</t>
-        </is>
-      </c>
+          <t>v2.0.4</t>
+        </is>
+      </c>
+      <c r="I28" s="5" t="n"/>
       <c r="J28" s="5" t="inlineStr">
         <is>
-          <t>AES-[128|192|256]-[GCM|CBC|CTR|CCM|GCM-SIV|XTS], ChaCha20-Poly1305, SHA-[256|384|512], SHA3-[256|384|512], HMAC-[SHA-256|SHA-384|SHA-512], ECDH-[P-256|P-384|P-521], ECDH-[Curve25519|X25519], ECDH-[Curve448|X448], EdDSA-[Ed25519|Ed448], ECDSA-[P-256|P-384|P-521]-*, RSASSA-PSS-[2048|3072|4096]-*, RSAES-OAEP-[2048|3072|4096]-*, HKDF-[SHA-256|SHA-384|SHA-512], PBKDF2-HMAC-[SHA-256|SHA-384|SHA-512]-*, ML-KEM-768, ML-DSA-[44|65|87]-*</t>
+          <t>FAEST-[128s|128f|192s|192f|256s|256f]</t>
         </is>
       </c>
       <c r="K28" s="5" t="n"/>
       <c r="L28" s="5" t="inlineStr">
         <is>
-          <t>AES, ChaCha20, SHA, HMAC: no known patents; ECC: Certicom/BlackBerry largely expired; ML-KEM: NIST patent licenses secured; ML-DSA: no known patents. BSD-3-Clause.</t>
+          <t>No known patents (NIST Round 2 submission requirement: patent-free).</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
@@ -2115,7 +2139,7 @@
     <row r="29" ht="23" customHeight="1">
       <c r="A29" s="5" t="inlineStr">
         <is>
-          <t>hawk-sign</t>
+          <t>falcon</t>
         </is>
       </c>
       <c r="B29" s="13" t="n"/>
@@ -2131,34 +2155,34 @@
       </c>
       <c r="E29" s="3" t="inlineStr">
         <is>
-          <t>https://github.com/ludopulles/hawk-sign</t>
+          <t>https://falcon-sign.info/</t>
         </is>
       </c>
       <c r="F29" s="5" t="inlineStr">
         <is>
-          <t>https://github.com/ludopulles/hawk-sign/archive/refs/heads/main.tar.gz</t>
+          <t>https://falcon-sign.info/Falcon-impl-20211101.zip</t>
         </is>
       </c>
       <c r="G29" s="5" t="inlineStr">
         <is>
-          <t>HAWK — Lattice Isomorphism Problem signature (Ducas, Postlethwaite, Pulles…)</t>
+          <t>Falcon / FN-DSA official C reference (falcon-sign.info)</t>
         </is>
       </c>
       <c r="H29" s="5" t="inlineStr">
         <is>
-          <t>No formal releases; tag: asiacryptsubmission</t>
+          <t>No formal releases — Round 3.1 zip on official site</t>
         </is>
       </c>
       <c r="I29" s="5" t="n"/>
       <c r="J29" s="5" t="inlineStr">
         <is>
-          <t>HAWK-[512|1024]</t>
+          <t>FN-DSA-[512|1024]</t>
         </is>
       </c>
       <c r="K29" s="5" t="n"/>
       <c r="L29" s="5" t="inlineStr">
         <is>
-          <t>No known patents (NIST Round 2 submission requirement: patent-free). Note: HAWK uses lattice structures related to NTRU; core NTRU patents (Security Innovation) placed in public domain March 2017. HAWK-specific IP not yet assessed by NIST.</t>
+          <t>NTRU-related patents (Security Innovation, formerly NTRU Cryptosystems): placed in public domain March 2017. NIST requirements for FIPS 206 ensure patent freedom.</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
@@ -2170,54 +2194,50 @@
     <row r="30" ht="23" customHeight="1">
       <c r="A30" s="5" t="inlineStr">
         <is>
-          <t>hqc-5.0.0</t>
-        </is>
-      </c>
-      <c r="B30" s="13" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
-      <c r="C30" s="3" t="inlineStr">
-        <is>
-          <t>CC0-1.0</t>
-        </is>
-      </c>
-      <c r="D30" s="3" t="inlineStr">
-        <is>
-          <t>5.0.0</t>
+          <t>falcon-py</t>
+        </is>
+      </c>
+      <c r="B30" s="13" t="n"/>
+      <c r="C30" s="5" t="inlineStr">
+        <is>
+          <t>MIT</t>
+        </is>
+      </c>
+      <c r="D30" s="11" t="inlineStr">
+        <is>
+          <t>UNRELEASED</t>
         </is>
       </c>
       <c r="E30" s="3" t="inlineStr">
         <is>
-          <t>https://gitlab.com/pqc-hqc/hqc</t>
-        </is>
-      </c>
-      <c r="F30" s="3" t="inlineStr">
-        <is>
-          <t>https://gitlab.com/pqc-hqc/hqc/-/archive/v5.0.0/hqc-v5.0.0.zip</t>
+          <t>https://github.com/tprest/falcon.py</t>
+        </is>
+      </c>
+      <c r="F30" s="5" t="inlineStr">
+        <is>
+          <t>https://github.com/tprest/falcon.py/archive/refs/heads/master.tar.gz</t>
         </is>
       </c>
       <c r="G30" s="5" t="inlineStr">
         <is>
-          <t>HQC official reference implementation (GitLab)</t>
+          <t>Falcon Python reference (Thomas Prest)</t>
         </is>
       </c>
       <c r="H30" s="5" t="inlineStr">
         <is>
-          <t>v5.0.0 (Round 4 update, 2025)</t>
+          <t>No formal releases — rolling</t>
         </is>
       </c>
       <c r="I30" s="5" t="n"/>
       <c r="J30" s="5" t="inlineStr">
         <is>
-          <t>HQC-[128|192|256]</t>
+          <t>FN-DSA-[512|1024]</t>
         </is>
       </c>
       <c r="K30" s="5" t="n"/>
       <c r="L30" s="5" t="inlineStr">
         <is>
-          <t>No known patents (confirmed patent-free by submitters; required for NIST selection, March 2025).</t>
+          <t>NTRU-related patents (Security Innovation): placed in public domain March 2017.</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
@@ -2229,44 +2249,44 @@
     <row r="31" ht="23" customHeight="1">
       <c r="A31" s="5" t="inlineStr">
         <is>
-          <t>hqc-py</t>
+          <t>glibc-getentropy</t>
         </is>
       </c>
       <c r="B31" s="13" t="n"/>
       <c r="C31" s="5" t="inlineStr">
         <is>
-          <t>MIT</t>
+          <t>LGPL-2.1-or-later</t>
         </is>
       </c>
       <c r="D31" s="11" t="inlineStr">
         <is>
-          <t>UNRELEASED</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="E31" s="3" t="inlineStr">
         <is>
-          <t>https://github.com/mjosaarinen/hqc-py</t>
-        </is>
-      </c>
-      <c r="F31" s="5" t="inlineStr">
-        <is>
-          <t>https://github.com/mjosaarinen/hqc-py/archive/refs/heads/main.tar.gz</t>
+          <t>https://sourceware.org/glibc/</t>
+        </is>
+      </c>
+      <c r="F31" s="7" t="inlineStr">
+        <is>
+          <t>https://github.com/bminor/glibc/blob/master/sysdeps/unix/sysv/linux/getentropy.c</t>
         </is>
       </c>
       <c r="G31" s="5" t="inlineStr">
         <is>
-          <t>hqc-py — Python reference, Markku-Juhani Saarinen (v5.0.0 test vectors)</t>
+          <t>glibc getentropy() — POSIX entropy interface (GNU C Library)</t>
         </is>
       </c>
       <c r="H31" s="5" t="inlineStr">
         <is>
-          <t>No formal releases — rolling</t>
+          <t>OS library facility</t>
         </is>
       </c>
       <c r="I31" s="5" t="n"/>
       <c r="J31" s="5" t="inlineStr">
         <is>
-          <t>HQC-[128|192|256]</t>
+          <t>getentropy</t>
         </is>
       </c>
       <c r="K31" s="5" t="n"/>
@@ -2284,50 +2304,58 @@
     <row r="32" ht="23" customHeight="1">
       <c r="A32" s="5" t="inlineStr">
         <is>
-          <t>kat</t>
-        </is>
-      </c>
-      <c r="B32" s="13" t="n"/>
-      <c r="C32" s="10" t="inlineStr">
-        <is>
-          <t>UNKNOWN</t>
-        </is>
-      </c>
-      <c r="D32" s="11" t="inlineStr">
-        <is>
-          <t>0.0.4</t>
+          <t>gmssl-3.1.1</t>
+        </is>
+      </c>
+      <c r="B32" s="13" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="C32" s="5" t="inlineStr">
+        <is>
+          <t>Apache-2.0</t>
+        </is>
+      </c>
+      <c r="D32" s="3" t="inlineStr">
+        <is>
+          <t>3.1.1</t>
         </is>
       </c>
       <c r="E32" s="3" t="inlineStr">
         <is>
-          <t>https://github.com/post-quantum-cryptography/KAT</t>
+          <t>https://github.com/guanzhi/GmSSL</t>
         </is>
       </c>
       <c r="F32" s="5" t="inlineStr">
         <is>
-          <t>https://github.com/post-quantum-cryptography/KAT/archive/refs/heads/main.tar.gz</t>
+          <t>https://github.com/guanzhi/GmSSL/archive/refs/tags/v3.1.1.tar.gz</t>
         </is>
       </c>
       <c r="G32" s="5" t="inlineStr">
         <is>
-          <t>post-quantum-cryptography/KAT — XMSS and LMS KAT vectors</t>
+          <t>GmSSL — Chinese national cryptographic standards library (C); SM2/SM3/SM4/SM9/ZUC/SM9-KEM</t>
         </is>
       </c>
       <c r="H32" s="5" t="inlineStr">
         <is>
-          <t>v0.0.4</t>
-        </is>
-      </c>
-      <c r="I32" s="5" t="n"/>
+          <t>v3.1.1 — 2024; stable release</t>
+        </is>
+      </c>
+      <c r="I32" s="5" t="inlineStr">
+        <is>
+          <t>stable</t>
+        </is>
+      </c>
       <c r="J32" s="5" t="inlineStr">
         <is>
-          <t>XMSS-*, LMS-*</t>
+          <t>SM9-(SIG|SIGNATURE), SM9-(KEM|KEYENCAPSULATION|KEY-ENCAPSULATION), SM9-(ENC|ENCRYPTION|PKE|PUBLICKEY-ENCRYPTION|PUBLIC-KEY-ENCRYPTION), SM9-(KEX|KEYEXCHANGE|KEY-EXCHANGE|KEYAGREE|KEY-AGREE|KEYAGREEMENT|KEY-AGREEMENT), SM2-*, SM3, SM4-[ECB|CBC|CTR|GCM|CCM]-*</t>
         </is>
       </c>
       <c r="K32" s="5" t="n"/>
       <c r="L32" s="5" t="inlineStr">
         <is>
-          <t>Test vector repository only. No known patents.</t>
+          <t>No known patents for GmSSL implementation. SM9 standard owned by State Cryptography Administration of China.</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
@@ -2339,46 +2367,58 @@
     <row r="33" ht="23" customHeight="1">
       <c r="A33" s="5" t="inlineStr">
         <is>
-          <t>kernel-pmu</t>
-        </is>
-      </c>
-      <c r="B33" s="13" t="n"/>
-      <c r="C33" s="10" t="inlineStr">
-        <is>
-          <t>UNKNOWN</t>
-        </is>
-      </c>
-      <c r="D33" s="11" t="inlineStr">
-        <is>
-          <t>UNRELEASED</t>
+          <t>gnutls-3.8.13</t>
+        </is>
+      </c>
+      <c r="B33" s="13" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="C33" s="5" t="inlineStr">
+        <is>
+          <t>LGPL-2.1-or-later</t>
+        </is>
+      </c>
+      <c r="D33" s="3" t="inlineStr">
+        <is>
+          <t>3.8.13</t>
         </is>
       </c>
       <c r="E33" s="3" t="inlineStr">
         <is>
-          <t>https://github.com/XKCP/Kernel-PMU</t>
+          <t>https://gitlab.com/gnutls/gnutls</t>
         </is>
       </c>
       <c r="F33" s="5" t="inlineStr">
         <is>
-          <t>https://github.com/XKCP/Kernel-PMU/archive/refs/heads/master.zip</t>
+          <t>https://www.gnupg.org/ftp/gcrypt/gnutls/v3.8/gnutls-3.8.13.tar.xz</t>
         </is>
       </c>
       <c r="G33" s="5" t="inlineStr">
         <is>
-          <t>XKCP/Kernel-PMU — PMU side-channel tooling (cited in KyberSlash thread)</t>
+          <t>GnuTLS — TLS/crypto library (C); experimental ML-KEM via --with-liboqs or --with-leancrypto; hybrid X25519+ML-KEM-768 TLS</t>
         </is>
       </c>
       <c r="H33" s="5" t="inlineStr">
         <is>
-          <t>No formal releases</t>
-        </is>
-      </c>
-      <c r="I33" s="5" t="n"/>
-      <c r="J33" s="5" t="n"/>
+          <t>3.8.13 (2026-04-29)</t>
+        </is>
+      </c>
+      <c r="I33" s="5" t="inlineStr">
+        <is>
+          <t>stable</t>
+        </is>
+      </c>
+      <c r="J33" s="5" t="inlineStr">
+        <is>
+          <t>AES-[128|192|256]-[GCM|CCM|CBC|CTR|XTS], ChaCha20-Poly1305, SHA-[256|384|512], SHA3-[256|384|512], HMAC-[SHA-256|SHA-384|SHA-512], AES-[128|192|256]-CMAC, RSAES-OAEP-[2048|3072|4096]-*, ECDH-[P-256|P-384|P-521], ECDH-[brainpoolP256r1|brainpoolP384r1|brainpoolP512r1], ECDH-[Curve25519|X25519], ECDH-[Curve448|X448], ECDSA-[P-256|P-384|P-521]-*, EdDSA-[Ed25519|Ed448], RSASSA-PSS-[2048|3072|4096]-*, HKDF-[SHA-256|SHA-384|SHA-512], PBKDF2-HMAC-[SHA-256|SHA-384|SHA-512]-*, ML-KEM-768</t>
+        </is>
+      </c>
       <c r="K33" s="5" t="n"/>
       <c r="L33" s="5" t="inlineStr">
         <is>
-          <t>Side-channel research tooling only. No known patents.</t>
+          <t>RSA: expired 2000; DH: expired 1997; ECC: Certicom/BlackBerry largely expired 2017–2022; ML-KEM: NIST patent licenses secured (via liboqs/leancrypto); AES, ChaCha20, SHA, HMAC: no known patents. LGPL-2.1-or-later.</t>
         </is>
       </c>
       <c r="M33" s="2" t="inlineStr">
@@ -2390,50 +2430,58 @@
     <row r="34" ht="23" customHeight="1">
       <c r="A34" s="5" t="inlineStr">
         <is>
-          <t>kyber</t>
+          <t>go-1.25.9</t>
         </is>
       </c>
       <c r="B34" s="13" t="n"/>
-      <c r="C34" s="5" t="inlineStr">
-        <is>
-          <t>CC0-1.0 OR Apache-2.0</t>
-        </is>
-      </c>
-      <c r="D34" s="11" t="inlineStr">
-        <is>
-          <t>3.0</t>
+      <c r="C34" s="10" t="inlineStr">
+        <is>
+          <t>BSD-3-Clause</t>
+        </is>
+      </c>
+      <c r="D34" s="3" t="inlineStr">
+        <is>
+          <t>1.25.9</t>
         </is>
       </c>
       <c r="E34" s="3" t="inlineStr">
         <is>
-          <t>https://github.com/pq-crystals/kyber</t>
+          <t>https://github.com/golang/go</t>
         </is>
       </c>
       <c r="F34" s="5" t="inlineStr">
         <is>
-          <t>https://github.com/pq-crystals/kyber/archive/refs/heads/master.tar.gz</t>
+          <t>https://github.com/golang/go/archive/refs/tags/go1.25.9.tar.gz</t>
         </is>
       </c>
       <c r="G34" s="5" t="inlineStr">
         <is>
-          <t>Kyber / ML-KEM (CRYSTALS reference C + AVX2)</t>
+          <t>Go standard library — crypto/* packages (Go); X25519MLKEM768 hybrid TLS default since 1.24; ML-DSA in 1.26+</t>
         </is>
       </c>
       <c r="H34" s="5" t="inlineStr">
         <is>
-          <t>v3.0 (pre-FIPS 203; superseded by ML-KEM)</t>
-        </is>
-      </c>
-      <c r="I34" s="5" t="n"/>
+          <t>go1.25.9 (2026-06-02)</t>
+        </is>
+      </c>
+      <c r="I34" s="5" t="inlineStr">
+        <is>
+          <t>previous</t>
+        </is>
+      </c>
       <c r="J34" s="5" t="inlineStr">
         <is>
-          <t>ML-KEM-[512|768|1024]</t>
-        </is>
-      </c>
-      <c r="K34" s="5" t="n"/>
+          <t>AES-[128|192|256]-[GCM|CBC|CTR|CCM|GCM-SIV|XTS], ChaCha20-Poly1305, SHA-[256|384|512], SHA3-[256|384|512], HMAC-[SHA-256|SHA-384|SHA-512], ECDH-[P-256|P-384|P-521], ECDH-[Curve25519|X25519], ECDH-[Curve448|X448], EdDSA-[Ed25519|Ed448], ECDSA-[P-256|P-384|P-521]-*, RSASSA-PSS-[2048|3072|4096]-*, RSAES-OAEP-[2048|3072|4096]-*, HKDF-[SHA-256|SHA-384|SHA-512], PBKDF2-HMAC-[SHA-256|SHA-384|SHA-512]-*, ML-KEM-768, ML-DSA-[44|65|87]-*</t>
+        </is>
+      </c>
+      <c r="K34" s="5" t="inlineStr">
+        <is>
+          <t>Previous Go release line (still supported).</t>
+        </is>
+      </c>
       <c r="L34" s="5" t="inlineStr">
         <is>
-          <t>ML-KEM: NIST secured patent license agreements making implementations freely available (see FIPS 203 patent summary). No known unencumbered patents.</t>
+          <t>AES, ChaCha20, SHA, HMAC: no known patents; ECC: Certicom/BlackBerry largely expired; ML-KEM: NIST patent licenses secured; ML-DSA: no known patents. BSD-3-Clause.</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
@@ -2445,7 +2493,7 @@
     <row r="35" ht="23" customHeight="1">
       <c r="A35" s="5" t="inlineStr">
         <is>
-          <t>less-2.1.0</t>
+          <t>go-1.26.4</t>
         </is>
       </c>
       <c r="B35" s="13" t="inlineStr">
@@ -2453,46 +2501,50 @@
           <t>x</t>
         </is>
       </c>
-      <c r="C35" s="10" t="inlineStr">
-        <is>
-          <t>UNKNOWN</t>
+      <c r="C35" s="5" t="inlineStr">
+        <is>
+          <t>BSD-3-Clause</t>
         </is>
       </c>
       <c r="D35" s="3" t="inlineStr">
         <is>
-          <t>2.1.0</t>
+          <t>1.26.4</t>
         </is>
       </c>
       <c r="E35" s="3" t="inlineStr">
         <is>
-          <t>https://github.com/less-sig/LESS</t>
+          <t>https://github.com/golang/go</t>
         </is>
       </c>
       <c r="F35" s="5" t="inlineStr">
         <is>
-          <t>https://github.com/less-sig/LESS/archive/refs/tags/v2.1.0.zip</t>
+          <t>https://github.com/golang/go/archive/refs/tags/go1.26.4.tar.gz</t>
         </is>
       </c>
       <c r="G35" s="5" t="inlineStr">
         <is>
-          <t>LESS — Linear Equivalence Signature Scheme</t>
+          <t>Go standard library — crypto/* packages (Go); X25519MLKEM768 hybrid TLS default since 1.24; ML-DSA in 1.26+</t>
         </is>
       </c>
       <c r="H35" s="5" t="inlineStr">
         <is>
-          <t>Round 2 submission (not sure which version)</t>
-        </is>
-      </c>
-      <c r="I35" s="5" t="n"/>
+          <t>go1.26.4 (2026-06-02)</t>
+        </is>
+      </c>
+      <c r="I35" s="5" t="inlineStr">
+        <is>
+          <t>stable</t>
+        </is>
+      </c>
       <c r="J35" s="5" t="inlineStr">
         <is>
-          <t>LESS-*</t>
+          <t>AES-[128|192|256]-[GCM|CBC|CTR|CCM|GCM-SIV|XTS], ChaCha20-Poly1305, SHA-[256|384|512], SHA3-[256|384|512], HMAC-[SHA-256|SHA-384|SHA-512], ECDH-[P-256|P-384|P-521], ECDH-[Curve25519|X25519], ECDH-[Curve448|X448], EdDSA-[Ed25519|Ed448], ECDSA-[P-256|P-384|P-521]-*, RSASSA-PSS-[2048|3072|4096]-*, RSAES-OAEP-[2048|3072|4096]-*, HKDF-[SHA-256|SHA-384|SHA-512], PBKDF2-HMAC-[SHA-256|SHA-384|SHA-512]-*, ML-KEM-768, ML-DSA-[44|65|87]-*</t>
         </is>
       </c>
       <c r="K35" s="5" t="n"/>
       <c r="L35" s="5" t="inlineStr">
         <is>
-          <t>No known patents (NIST Round 2 submission requirement: patent-free).</t>
+          <t>AES, ChaCha20, SHA, HMAC: no known patents; ECC: Certicom/BlackBerry largely expired; ML-KEM: NIST patent licenses secured; ML-DSA: no known patents. BSD-3-Clause.</t>
         </is>
       </c>
       <c r="M35" s="2" t="inlineStr">
@@ -2504,56 +2556,60 @@
     <row r="36" ht="23" customHeight="1">
       <c r="A36" s="5" t="inlineStr">
         <is>
-          <t>libargon2</t>
+          <t>golang-x-crypto-0.53.0</t>
         </is>
       </c>
       <c r="B36" s="13" t="inlineStr">
         <is>
-          <t>c</t>
-        </is>
-      </c>
-      <c r="C36" s="5" t="inlineStr">
-        <is>
-          <t>CC0-1.0 OR Apache-2.0</t>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="C36" s="10" t="inlineStr">
+        <is>
+          <t>BSD-3-Clause</t>
         </is>
       </c>
       <c r="D36" s="3" t="inlineStr">
         <is>
-          <t>20190702</t>
+          <t>0.53.0</t>
         </is>
       </c>
       <c r="E36" s="3" t="inlineStr">
         <is>
-          <t>https://github.com/P-H-C/phc-winner-argon2</t>
+          <t>https://github.com/golang/crypto</t>
         </is>
       </c>
       <c r="F36" s="5" t="inlineStr">
         <is>
-          <t>https://github.com/P-H-C/phc-winner-argon2/archive/refs/tags/20190702.tar.gz</t>
+          <t>https://github.com/golang/crypto/archive/refs/tags/v0.53.0.tar.gz</t>
         </is>
       </c>
       <c r="G36" s="5" t="inlineStr">
         <is>
-          <t>Argon2 reference C implementation (PHC winner)</t>
+          <t>golang.org/x/crypto — official Go supplementary crypto (pure-Go primitives beyond the standard library)</t>
         </is>
       </c>
       <c r="H36" s="5" t="inlineStr">
         <is>
-          <t>Stable release (July 2019)</t>
-        </is>
-      </c>
-      <c r="I36" s="5" t="n"/>
+          <t>v0.53.0 (2026-06-08)</t>
+        </is>
+      </c>
+      <c r="I36" s="5" t="inlineStr">
+        <is>
+          <t>stable</t>
+        </is>
+      </c>
       <c r="J36" s="5" t="inlineStr">
         <is>
-          <t>Argon2i-*, Argon2d-*, Argon2id-*</t>
-        </is>
-      </c>
-      <c r="K36" s="5" t="n"/>
-      <c r="L36" s="5" t="inlineStr">
-        <is>
-          <t>No known patents.</t>
-        </is>
-      </c>
+          <t>ChaCha20, XChaCha20, ChaCha20-Poly1305, ECDH-[Curve25519|X25519], Blowfish-*, Twofish-*, CAST5-*, TEA, XTEA, AES-[128|192|256]-XTS, Salsa20, BLAKE2b-*, BLAKE2s-*, SHA3-*, SHAKE128, SHAKE256, Argon2id-*, scrypt-*, PBKDF2-*, HKDF, bcrypt-*, EdDSA-Ed25519, SSH-KDF</t>
+        </is>
+      </c>
+      <c r="K36" s="5" t="inlineStr">
+        <is>
+          <t>Complements the Go standard library (go-1.26.4); some packages later graduated into stdlib.</t>
+        </is>
+      </c>
+      <c r="L36" s="5" t="n"/>
       <c r="M36" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve"> </t>
@@ -2563,7 +2619,7 @@
     <row r="37" ht="23" customHeight="1">
       <c r="A37" s="5" t="inlineStr">
         <is>
-          <t>libgcrypt-1.12.2</t>
+          <t>gost-engine-3.0.3</t>
         </is>
       </c>
       <c r="B37" s="13" t="inlineStr">
@@ -2571,34 +2627,34 @@
           <t>x</t>
         </is>
       </c>
-      <c r="C37" s="5" t="inlineStr">
-        <is>
-          <t>LGPL-2.1-or-later</t>
+      <c r="C37" s="10" t="inlineStr">
+        <is>
+          <t>Apache-2.0</t>
         </is>
       </c>
       <c r="D37" s="3" t="inlineStr">
         <is>
-          <t>1.12.2</t>
+          <t>3.0.3</t>
         </is>
       </c>
       <c r="E37" s="3" t="inlineStr">
         <is>
-          <t>https://github.com/gpg/libgcrypt</t>
+          <t>https://github.com/gost-engine/engine</t>
         </is>
       </c>
       <c r="F37" s="5" t="inlineStr">
         <is>
-          <t>https://gnupg.org/ftp/gcrypt/libgcrypt/libgcrypt-1.12.2.tar.bz2</t>
+          <t>https://github.com/gost-engine/engine/archive/refs/tags/v3.0.3.tar.gz</t>
         </is>
       </c>
       <c r="G37" s="5" t="inlineStr">
         <is>
-          <t>libgcrypt — GnuPG crypto library (C); classical algorithms only; no PQC</t>
+          <t>gost-engine — OpenSSL engine/provider implementing the Russian GOST cryptographic suite (C)</t>
         </is>
       </c>
       <c r="H37" s="5" t="inlineStr">
         <is>
-          <t>libgcrypt-1.12.1 (2026-02-20)</t>
+          <t>v3.0.3 (2023-11-17)</t>
         </is>
       </c>
       <c r="I37" s="5" t="inlineStr">
@@ -2608,15 +2664,15 @@
       </c>
       <c r="J37" s="5" t="inlineStr">
         <is>
-          <t>AES-[128|192|256]-[GCM|CCM|CBC|CTR|OFB|CFB128], ChaCha20-Poly1305, SHA-[256|384|512], SHA3-[256|384|512], HMAC-[SHA-256|SHA-384|SHA-512], AES-[128|192|256]-CMAC, RSAES-OAEP-[2048|3072|4096]-*, ECDH-[P-256|P-384|P-521], ECDH-[brainpoolP256r1|brainpoolP384r1|brainpoolP512r1], ECDH-[Curve25519|X25519], ECDSA-[P-256|P-384|P-521]-*, EdDSA-[Ed25519|Ed448], RSASSA-PSS-[2048|3072|4096]-*, HKDF-[SHA-256|SHA-384|SHA-512], PBKDF2-HMAC-[SHA-256|SHA-384|SHA-512]-*</t>
-        </is>
-      </c>
-      <c r="K37" s="5" t="n"/>
-      <c r="L37" s="5" t="inlineStr">
-        <is>
-          <t>RSA: expired 2000; DH: expired 1997; ECC: Certicom/BlackBerry largely expired 2017–2022; AES, ChaCha20, SHA, HMAC: no known patents. LGPL-2.1-or-later.</t>
-        </is>
-      </c>
+          <t>Magma, Grasshopper, GOSTR3410-2012, GOSTR3411-2012, GOST-28147, GOST-28147-MAC</t>
+        </is>
+      </c>
+      <c r="K37" s="5" t="inlineStr">
+        <is>
+          <t>The production implementation of GOST R 34.12-2015 (Magma 64-bit + Kuznyechik/Grasshopper 128-bit), Streebog (GOST R 34.11-2012), and GOST R 34.10-2012. Loaded as an OpenSSL 1.1/3.x engine.</t>
+        </is>
+      </c>
+      <c r="L37" s="5" t="n"/>
       <c r="M37" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve"> </t>
@@ -2626,56 +2682,56 @@
     <row r="38" ht="23" customHeight="1">
       <c r="A38" s="5" t="inlineStr">
         <is>
-          <t>liboqs-0.15.0</t>
-        </is>
-      </c>
-      <c r="B38" s="13" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
-      <c r="C38" s="5" t="inlineStr">
-        <is>
-          <t>MIT (+ third-party components)</t>
+          <t>hacl-star</t>
+        </is>
+      </c>
+      <c r="B38" s="13" t="n"/>
+      <c r="C38" s="10" t="inlineStr">
+        <is>
+          <t>Apache-2.0</t>
         </is>
       </c>
       <c r="D38" s="3" t="inlineStr">
         <is>
-          <t>0.15.0</t>
+          <t>UNRELEASED</t>
         </is>
       </c>
       <c r="E38" s="3" t="inlineStr">
         <is>
-          <t>https://github.com/open-quantum-safe/liboqs</t>
+          <t>https://github.com/hacl-star/hacl-star</t>
         </is>
       </c>
       <c r="F38" s="5" t="inlineStr">
         <is>
-          <t>https://github.com/open-quantum-safe/liboqs/archive/refs/tags/0.15.0.tar.gz</t>
+          <t>https://github.com/cryspen/hacl-packages/archive/refs/tags/ocaml-v0.7.2.tar.gz</t>
         </is>
       </c>
       <c r="G38" s="5" t="inlineStr">
         <is>
-          <t>liboqs — Open Quantum Safe C library (ML-KEM, ML-DSA, SLH-DSA, HQC, MAYO, CROSS, UOV, SNOVA…)</t>
+          <t>HACL* / EverCrypt — formally verified crypto library in F* compiled to C (EverCrypt provider with ValeCrypt asm)</t>
         </is>
       </c>
       <c r="H38" s="5" t="inlineStr">
         <is>
-          <t>v0.15.0 (2025-11-14)</t>
-        </is>
-      </c>
-      <c r="I38" s="5" t="n"/>
+          <t>No formal library release; packaging cryspen/hacl-packages ocaml-v0.7.2 (2025-09-25)</t>
+        </is>
+      </c>
+      <c r="I38" s="5" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
       <c r="J38" s="5" t="inlineStr">
         <is>
-          <t>ML-KEM-[512|768|1024], ML-DSA-[44|65|87]-*, SLH-DSA-*, FN-DSA-[512|1024], HQC-[128|192|256], MAYO-*, CROSS-*, UOV-*, SNOVA-*</t>
-        </is>
-      </c>
-      <c r="K38" s="5" t="n"/>
-      <c r="L38" s="5" t="inlineStr">
-        <is>
-          <t>ML-KEM: NIST patent licenses secured; FN-DSA: NTRU patents placed in public domain (Security Innovation, 2017); RSA: US 4,405,829 expired 2000; ECC: Certicom/BlackBerry portfolio largely expired 2017–2022. No library-level patents.</t>
-        </is>
-      </c>
+          <t>ECDH-[Curve25519|X25519], EdDSA-Ed25519, AES-[128|256]-GCM, ChaCha20-Poly1305, Poly1305, SHA-[256|384|512], SHA3-*, HMAC-*, HKDF</t>
+        </is>
+      </c>
+      <c r="K38" s="5" t="inlineStr">
+        <is>
+          <t>Formally verified C consumed by NSS/Firefox, CPython, and the Linux kernel (curve25519). Releases moved to cryspen/hacl-packages.</t>
+        </is>
+      </c>
+      <c r="L38" s="5" t="n"/>
       <c r="M38" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve"> </t>
@@ -2685,54 +2741,50 @@
     <row r="39" ht="23" customHeight="1">
       <c r="A39" s="5" t="inlineStr">
         <is>
-          <t>libosmocore-1.14.0</t>
-        </is>
-      </c>
-      <c r="B39" s="13" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
+          <t>hawk-sign</t>
+        </is>
+      </c>
+      <c r="B39" s="13" t="n"/>
       <c r="C39" s="5" t="inlineStr">
         <is>
-          <t>GPL-2.0-or-later</t>
-        </is>
-      </c>
-      <c r="D39" s="3" t="inlineStr">
-        <is>
-          <t>1.14.0</t>
+          <t>MIT</t>
+        </is>
+      </c>
+      <c r="D39" s="11" t="inlineStr">
+        <is>
+          <t>UNRELEASED</t>
         </is>
       </c>
       <c r="E39" s="3" t="inlineStr">
         <is>
-          <t>https://gitea.osmocom.org/osmocom/libosmocore</t>
+          <t>https://github.com/ludopulles/hawk-sign</t>
         </is>
       </c>
       <c r="F39" s="5" t="inlineStr">
         <is>
-          <t>https://downloads.osmocom.org/releases/libosmocore/libosmocore-1.14.0.tar.bz2</t>
+          <t>https://github.com/ludopulles/hawk-sign/archive/refs/heads/main.tar.gz</t>
         </is>
       </c>
       <c r="G39" s="5" t="inlineStr">
         <is>
-          <t>libosmocore — Osmocom GSM/3GPP utility library (C); MILENAGE, A5/1, A5/2, GEA algorithms</t>
+          <t>HAWK — Lattice Isomorphism Problem signature (Ducas, Postlethwaite, Pulles…)</t>
         </is>
       </c>
       <c r="H39" s="5" t="inlineStr">
         <is>
-          <t>Rolling releases; actively maintained by Osmocom project</t>
+          <t>No formal releases; tag: asiacryptsubmission</t>
         </is>
       </c>
       <c r="I39" s="5" t="n"/>
       <c r="J39" s="5" t="inlineStr">
         <is>
-          <t>MILENAGE, A5/1, A5/2, GEA-[0|1|2|3|4|5]-*</t>
+          <t>HAWK-[512|1024]</t>
         </is>
       </c>
       <c r="K39" s="5" t="n"/>
       <c r="L39" s="5" t="inlineStr">
         <is>
-          <t>A5/1 and A5/2 were proprietary algorithms; original IP owned by 3GPP/ETSI. Practically treated as public knowledge since 1999 leak. No licensing restrictions on open-source implementations.</t>
+          <t>No known patents (NIST Round 2 submission requirement: patent-free). Note: HAWK uses lattice structures related to NTRU; core NTRU patents (Security Innovation) placed in public domain March 2017. HAWK-specific IP not yet assessed by NIST.</t>
         </is>
       </c>
       <c r="M39" s="2" t="inlineStr">
@@ -2744,7 +2796,7 @@
     <row r="40" ht="23" customHeight="1">
       <c r="A40" s="5" t="inlineStr">
         <is>
-          <t>libsodium-1.0.22</t>
+          <t>hqc-5.0.0</t>
         </is>
       </c>
       <c r="B40" s="13" t="inlineStr">
@@ -2752,42 +2804,46 @@
           <t>x</t>
         </is>
       </c>
-      <c r="C40" s="5" t="inlineStr">
-        <is>
-          <t>ISC</t>
+      <c r="C40" s="3" t="inlineStr">
+        <is>
+          <t>CC0-1.0</t>
         </is>
       </c>
       <c r="D40" s="3" t="inlineStr">
         <is>
-          <t>1.0.22</t>
+          <t>5.0.0</t>
         </is>
       </c>
       <c r="E40" s="3" t="inlineStr">
         <is>
-          <t>https://github.com/jedisct1/libsodium</t>
-        </is>
-      </c>
-      <c r="F40" s="5" t="inlineStr">
-        <is>
-          <t>https://github.com/jedisct1/libsodium/archive/refs/tags/1.0.22-RELEASE.tar.gz</t>
+          <t>https://gitlab.com/pqc-hqc/hqc</t>
+        </is>
+      </c>
+      <c r="F40" s="3" t="inlineStr">
+        <is>
+          <t>https://gitlab.com/pqc-hqc/hqc/-/archive/v5.0.0/hqc-v5.0.0.zip</t>
         </is>
       </c>
       <c r="G40" s="5" t="inlineStr">
         <is>
-          <t>libsodium — modern crypto primitives (C); X25519, Ed25519, ChaCha20-Poly1305; no PQC</t>
-        </is>
-      </c>
-      <c r="H40" s="5" t="n"/>
+          <t>HQC official reference implementation (GitLab)</t>
+        </is>
+      </c>
+      <c r="H40" s="5" t="inlineStr">
+        <is>
+          <t>v5.0.0 (Round 4 update, 2025)</t>
+        </is>
+      </c>
       <c r="I40" s="5" t="n"/>
       <c r="J40" s="5" t="inlineStr">
         <is>
-          <t>ECDH-[Curve25519|X25519], EdDSA-Ed25519, ChaCha20-Poly1305, HMAC-SHA-512, Argon2id-*, scrypt-*</t>
+          <t>HQC-[128|192|256]</t>
         </is>
       </c>
       <c r="K40" s="5" t="n"/>
       <c r="L40" s="5" t="inlineStr">
         <is>
-          <t>EdDSA/Ed25519, X25519, ChaCha20-Poly1305, Argon2, scrypt: no known patents.</t>
+          <t>No known patents (confirmed patent-free by submitters; required for NIST selection, March 2025).</t>
         </is>
       </c>
       <c r="M40" s="2" t="inlineStr">
@@ -2799,48 +2855,44 @@
     <row r="41" ht="23" customHeight="1">
       <c r="A41" s="5" t="inlineStr">
         <is>
-          <t>libsrtp-2.8.0</t>
-        </is>
-      </c>
-      <c r="B41" s="13" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
+          <t>hqc-py</t>
+        </is>
+      </c>
+      <c r="B41" s="13" t="n"/>
       <c r="C41" s="5" t="inlineStr">
         <is>
-          <t>BSD-3-Clause</t>
-        </is>
-      </c>
-      <c r="D41" s="3" t="inlineStr">
-        <is>
-          <t>2.8.0</t>
+          <t>MIT</t>
+        </is>
+      </c>
+      <c r="D41" s="11" t="inlineStr">
+        <is>
+          <t>UNRELEASED</t>
         </is>
       </c>
       <c r="E41" s="3" t="inlineStr">
         <is>
-          <t>https://github.com/cisco/libsrtp</t>
+          <t>https://github.com/mjosaarinen/hqc-py</t>
         </is>
       </c>
       <c r="F41" s="5" t="inlineStr">
         <is>
-          <t>https://github.com/cisco/libsrtp/archive/refs/tags/v2.8.0.tar.gz</t>
+          <t>https://github.com/mjosaarinen/hqc-py/archive/refs/heads/main.tar.gz</t>
         </is>
       </c>
       <c r="G41" s="5" t="inlineStr">
         <is>
-          <t>Cisco SRTP implementation (RFC 3711)</t>
+          <t>hqc-py — Python reference, Markku-Juhani Saarinen (v5.0.0 test vectors)</t>
         </is>
       </c>
       <c r="H41" s="5" t="inlineStr">
         <is>
-          <t>Stable release</t>
+          <t>No formal releases — rolling</t>
         </is>
       </c>
       <c r="I41" s="5" t="n"/>
       <c r="J41" s="5" t="inlineStr">
         <is>
-          <t>SRTP-*</t>
+          <t>HQC-[128|192|256]</t>
         </is>
       </c>
       <c r="K41" s="5" t="n"/>
@@ -2858,50 +2910,50 @@
     <row r="42" ht="23" customHeight="1">
       <c r="A42" s="5" t="inlineStr">
         <is>
-          <t>linux-dev-random</t>
+          <t>kat</t>
         </is>
       </c>
       <c r="B42" s="13" t="n"/>
-      <c r="C42" s="5" t="inlineStr">
-        <is>
-          <t>GPL-2.0-only</t>
+      <c r="C42" s="10" t="inlineStr">
+        <is>
+          <t>UNKNOWN</t>
         </is>
       </c>
       <c r="D42" s="11" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>0.0.4</t>
         </is>
       </c>
       <c r="E42" s="3" t="inlineStr">
         <is>
-          <t>https://www.kernel.org/</t>
-        </is>
-      </c>
-      <c r="F42" s="8" t="inlineStr">
-        <is>
-          <t>https://github.com/torvalds/linux/blob/master/drivers/char/random.c</t>
+          <t>https://github.com/post-quantum-cryptography/KAT</t>
+        </is>
+      </c>
+      <c r="F42" s="5" t="inlineStr">
+        <is>
+          <t>https://github.com/post-quantum-cryptography/KAT/archive/refs/heads/main.tar.gz</t>
         </is>
       </c>
       <c r="G42" s="5" t="inlineStr">
         <is>
-          <t>Linux kernel /dev/random and /dev/urandom (CSPRNG)</t>
+          <t>post-quantum-cryptography/KAT — XMSS and LMS KAT vectors</t>
         </is>
       </c>
       <c r="H42" s="5" t="inlineStr">
         <is>
-          <t>OS kernel facility</t>
+          <t>v0.0.4</t>
         </is>
       </c>
       <c r="I42" s="5" t="n"/>
       <c r="J42" s="5" t="inlineStr">
         <is>
-          <t>dev-random, dev-urandom</t>
+          <t>XMSS-*, LMS-*</t>
         </is>
       </c>
       <c r="K42" s="5" t="n"/>
       <c r="L42" s="5" t="inlineStr">
         <is>
-          <t>No known patents.</t>
+          <t>Test vector repository only. No known patents.</t>
         </is>
       </c>
       <c r="M42" s="2" t="inlineStr">
@@ -2913,50 +2965,46 @@
     <row r="43" ht="23" customHeight="1">
       <c r="A43" s="5" t="inlineStr">
         <is>
-          <t>linux-getrandom</t>
+          <t>kernel-pmu</t>
         </is>
       </c>
       <c r="B43" s="13" t="n"/>
-      <c r="C43" s="5" t="inlineStr">
-        <is>
-          <t>GPL-2.0-only</t>
+      <c r="C43" s="10" t="inlineStr">
+        <is>
+          <t>UNKNOWN</t>
         </is>
       </c>
       <c r="D43" s="11" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>UNRELEASED</t>
         </is>
       </c>
       <c r="E43" s="3" t="inlineStr">
         <is>
-          <t>https://www.kernel.org/</t>
-        </is>
-      </c>
-      <c r="F43" s="8" t="inlineStr">
-        <is>
-          <t>https://github.com/bminor/glibc/blob/master/sysdeps/unix/sysv/linux/getrandom.c</t>
+          <t>https://github.com/XKCP/Kernel-PMU</t>
+        </is>
+      </c>
+      <c r="F43" s="5" t="inlineStr">
+        <is>
+          <t>https://github.com/XKCP/Kernel-PMU/archive/refs/heads/master.zip</t>
         </is>
       </c>
       <c r="G43" s="5" t="inlineStr">
         <is>
-          <t>Linux kernel getrandom() syscall</t>
+          <t>XKCP/Kernel-PMU — PMU side-channel tooling (cited in KyberSlash thread)</t>
         </is>
       </c>
       <c r="H43" s="5" t="inlineStr">
         <is>
-          <t>OS kernel facility</t>
+          <t>No formal releases</t>
         </is>
       </c>
       <c r="I43" s="5" t="n"/>
-      <c r="J43" s="5" t="inlineStr">
-        <is>
-          <t>getrandom</t>
-        </is>
-      </c>
+      <c r="J43" s="5" t="n"/>
       <c r="K43" s="5" t="n"/>
       <c r="L43" s="5" t="inlineStr">
         <is>
-          <t>No known patents.</t>
+          <t>Side-channel research tooling only. No known patents.</t>
         </is>
       </c>
       <c r="M43" s="2" t="inlineStr">
@@ -2968,50 +3016,50 @@
     <row r="44" ht="23" customHeight="1">
       <c r="A44" s="5" t="inlineStr">
         <is>
-          <t>mayo-c</t>
+          <t>kyber</t>
         </is>
       </c>
       <c r="B44" s="13" t="n"/>
-      <c r="C44" s="3" t="inlineStr">
-        <is>
-          <t>Apache-2.0</t>
+      <c r="C44" s="5" t="inlineStr">
+        <is>
+          <t>CC0-1.0 OR Apache-2.0</t>
         </is>
       </c>
       <c r="D44" s="11" t="inlineStr">
         <is>
-          <t>round2</t>
+          <t>3.0</t>
         </is>
       </c>
       <c r="E44" s="3" t="inlineStr">
         <is>
-          <t>https://github.com/PQCMayo/MAYO-C</t>
-        </is>
-      </c>
-      <c r="F44" s="3" t="inlineStr">
-        <is>
-          <t>https://github.com/PQCMayo/MAYO-C/archive/refs/heads/main.tar.gz</t>
+          <t>https://github.com/pq-crystals/kyber</t>
+        </is>
+      </c>
+      <c r="F44" s="5" t="inlineStr">
+        <is>
+          <t>https://github.com/pq-crystals/kyber/archive/refs/heads/master.tar.gz</t>
         </is>
       </c>
       <c r="G44" s="5" t="inlineStr">
         <is>
-          <t>MAYO-C — official C implementation (multivariate UOV-based)</t>
+          <t>Kyber / ML-KEM (CRYSTALS reference C + AVX2)</t>
         </is>
       </c>
       <c r="H44" s="5" t="inlineStr">
         <is>
-          <t>NIST Round 2 submission</t>
+          <t>v3.0 (pre-FIPS 203; superseded by ML-KEM)</t>
         </is>
       </c>
       <c r="I44" s="5" t="n"/>
       <c r="J44" s="5" t="inlineStr">
         <is>
-          <t>MAYO-[1|2|3|5]</t>
+          <t>ML-KEM-[512|768|1024]</t>
         </is>
       </c>
       <c r="K44" s="5" t="n"/>
       <c r="L44" s="5" t="inlineStr">
         <is>
-          <t>No known patents (NIST Round 2 submission requirement: patent-free).</t>
+          <t>ML-KEM: NIST secured patent license agreements making implementations freely available (see FIPS 203 patent summary). No known unencumbered patents.</t>
         </is>
       </c>
       <c r="M44" s="2" t="inlineStr">
@@ -3023,58 +3071,54 @@
     <row r="45" ht="23" customHeight="1">
       <c r="A45" s="5" t="inlineStr">
         <is>
-          <t>mbedtls-3.6.5</t>
+          <t>less-2.1.0</t>
         </is>
       </c>
       <c r="B45" s="13" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C45" s="3" t="inlineStr">
-        <is>
-          <t>Apache-2.0</t>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="C45" s="10" t="inlineStr">
+        <is>
+          <t>UNKNOWN</t>
         </is>
       </c>
       <c r="D45" s="3" t="inlineStr">
         <is>
-          <t>3.6.5</t>
+          <t>2.1.0</t>
         </is>
       </c>
       <c r="E45" s="3" t="inlineStr">
         <is>
-          <t>https://github.com/Mbed-TLS/mbedtls</t>
-        </is>
-      </c>
-      <c r="F45" s="3" t="inlineStr">
-        <is>
-          <t>https://github.com/Mbed-TLS/mbedtls/archive/refs/tags/mbedtls-3.6.5.tar.gz</t>
+          <t>https://github.com/less-sig/LESS</t>
+        </is>
+      </c>
+      <c r="F45" s="5" t="inlineStr">
+        <is>
+          <t>https://github.com/less-sig/LESS/archive/refs/tags/v2.1.0.zip</t>
         </is>
       </c>
       <c r="G45" s="5" t="inlineStr">
         <is>
-          <t>Mbed-TLS — embedded TLS/crypto (C); LTS 3.6.x branch; no PQC (ML-DSA added in 4.x roadmap Q2 2026)</t>
+          <t>LESS — Linear Equivalence Signature Scheme</t>
         </is>
       </c>
       <c r="H45" s="5" t="inlineStr">
         <is>
-          <t>mbedtls-3.6.5 (LTS)</t>
-        </is>
-      </c>
-      <c r="I45" s="5" t="inlineStr">
-        <is>
-          <t>previous</t>
-        </is>
-      </c>
+          <t>Round 2 submission (not sure which version)</t>
+        </is>
+      </c>
+      <c r="I45" s="5" t="n"/>
       <c r="J45" s="5" t="inlineStr">
         <is>
-          <t>AES-*, ChaCha20-Poly1305, SHA-*, HMAC-*, AES-CMAC, RSAES-OAEP-*, ECDH-*, ECDSA-*, EdDSA-*, RSASSA-PSS-*, HKDF-*, PBKDF2-*</t>
+          <t>LESS-*</t>
         </is>
       </c>
       <c r="K45" s="5" t="n"/>
       <c r="L45" s="5" t="inlineStr">
         <is>
-          <t>RSA: expired 2000; DH: expired 1997; ECC: Certicom/BlackBerry largely expired 2017–2022; AES, ChaCha20, SHA, HMAC: no known patents (no PQC). Apache-2.0 license includes patent grant.</t>
+          <t>No known patents (NIST Round 2 submission requirement: patent-free).</t>
         </is>
       </c>
       <c r="M45" s="2" t="inlineStr">
@@ -3086,7 +3130,7 @@
     <row r="46" ht="23" customHeight="1">
       <c r="A46" s="5" t="inlineStr">
         <is>
-          <t>mbedtls-4.1.0</t>
+          <t>libargon2</t>
         </is>
       </c>
       <c r="B46" s="13" t="inlineStr">
@@ -3094,46 +3138,46 @@
           <t>x</t>
         </is>
       </c>
-      <c r="C46" s="3" t="inlineStr">
-        <is>
-          <t>Apache-2.0</t>
+      <c r="C46" s="5" t="inlineStr">
+        <is>
+          <t>CC0-1.0 OR Apache-2.0</t>
         </is>
       </c>
       <c r="D46" s="3" t="inlineStr">
         <is>
-          <t>4.1.0</t>
+          <t>20190702</t>
         </is>
       </c>
       <c r="E46" s="3" t="inlineStr">
         <is>
-          <t>https://github.com/Mbed-TLS/mbedtls</t>
-        </is>
-      </c>
-      <c r="F46" s="3" t="inlineStr">
-        <is>
-          <t>https://github.com/Mbed-TLS/mbedtls/archive/refs/tags/v4.1.0.tar.gz</t>
+          <t>https://github.com/P-H-C/phc-winner-argon2</t>
+        </is>
+      </c>
+      <c r="F46" s="5" t="inlineStr">
+        <is>
+          <t>https://github.com/P-H-C/phc-winner-argon2/archive/refs/tags/20190702.tar.gz</t>
         </is>
       </c>
       <c r="G46" s="5" t="inlineStr">
         <is>
-          <t>Mbed-TLS — embedded TLS/crypto (C); PQC (ML-DSA) on roadmap Q2 2026; LTS 3.6.x branch parallel</t>
-        </is>
-      </c>
-      <c r="H46" s="5" t="n"/>
-      <c r="I46" s="5" t="inlineStr">
-        <is>
-          <t>stable</t>
-        </is>
-      </c>
+          <t>Argon2 reference C implementation (PHC winner)</t>
+        </is>
+      </c>
+      <c r="H46" s="5" t="inlineStr">
+        <is>
+          <t>Stable release (July 2019)</t>
+        </is>
+      </c>
+      <c r="I46" s="5" t="n"/>
       <c r="J46" s="5" t="inlineStr">
         <is>
-          <t>AES-[128|192|256]-[GCM|CCM|CBC|CTR|OFB|CFB128|XTS], ChaCha20-Poly1305, SHA-[256|384|512], SHA3-[256|384|512], HMAC-[SHA-256|SHA-384|SHA-512], AES-[128|192|256]-CMAC, RSAES-OAEP-[2048|3072|4096]-*, ECDH-[P-256|P-384|P-521], ECDH-[Curve25519|X25519], ECDH-[Curve448|X448], ECDSA-[P-256|P-384|P-521]-*, EdDSA-[Ed25519|Ed448], RSASSA-PSS-[2048|3072|4096]-*, HKDF-[SHA-256|SHA-384|SHA-512], PBKDF2-HMAC-[SHA-256|SHA-384|SHA-512]-*, ML-KEM-[512|768|1024]</t>
+          <t>Argon2i-*, Argon2d-*, Argon2id-*</t>
         </is>
       </c>
       <c r="K46" s="5" t="n"/>
       <c r="L46" s="5" t="inlineStr">
         <is>
-          <t>RSA: expired 2000; DH: expired 1997; ECC: Certicom/BlackBerry largely expired 2017–2022; ML-KEM: NIST patent licenses secured; AES, ChaCha20, SHA, HMAC: no known patents. Apache-2.0 license includes patent grant.</t>
+          <t>No known patents.</t>
         </is>
       </c>
       <c r="M46" s="2" t="inlineStr">
@@ -3145,50 +3189,58 @@
     <row r="47" ht="23" customHeight="1">
       <c r="A47" s="5" t="inlineStr">
         <is>
-          <t>mirith-nist-submission</t>
-        </is>
-      </c>
-      <c r="B47" s="13" t="n"/>
-      <c r="C47" s="3" t="inlineStr">
-        <is>
-          <t>Apache-2.0</t>
-        </is>
-      </c>
-      <c r="D47" s="11" t="inlineStr">
-        <is>
-          <t>1.1.0</t>
+          <t>libgcrypt-1.12.2</t>
+        </is>
+      </c>
+      <c r="B47" s="13" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="C47" s="5" t="inlineStr">
+        <is>
+          <t>LGPL-2.1-or-later</t>
+        </is>
+      </c>
+      <c r="D47" s="3" t="inlineStr">
+        <is>
+          <t>1.12.2</t>
         </is>
       </c>
       <c r="E47" s="3" t="inlineStr">
         <is>
-          <t>https://github.com/Crypto-TII/mirith_nist_submission</t>
-        </is>
-      </c>
-      <c r="F47" s="3" t="inlineStr">
-        <is>
-          <t>https://github.com/Crypto-TII/mirith_nist_submission/archive/refs/heads/main.tar.gz</t>
+          <t>https://github.com/gpg/libgcrypt</t>
+        </is>
+      </c>
+      <c r="F47" s="5" t="inlineStr">
+        <is>
+          <t>https://gnupg.org/ftp/gcrypt/libgcrypt/libgcrypt-1.12.2.tar.bz2</t>
         </is>
       </c>
       <c r="G47" s="5" t="inlineStr">
         <is>
-          <t>Mirath — merger of MIRA + MiRitH (MinRank in the Head)</t>
+          <t>libgcrypt — GnuPG crypto library (C); classical algorithms only; no PQC</t>
         </is>
       </c>
       <c r="H47" s="5" t="inlineStr">
         <is>
-          <t>v1.1.0</t>
-        </is>
-      </c>
-      <c r="I47" s="5" t="n"/>
+          <t>libgcrypt-1.12.1 (2026-02-20)</t>
+        </is>
+      </c>
+      <c r="I47" s="5" t="inlineStr">
+        <is>
+          <t>stable</t>
+        </is>
+      </c>
       <c r="J47" s="5" t="inlineStr">
         <is>
-          <t>Mirath-*</t>
+          <t>AES-[128|192|256]-[GCM|CCM|CBC|CTR|OFB|CFB128], ChaCha20-Poly1305, SHA-[256|384|512], SHA3-[256|384|512], HMAC-[SHA-256|SHA-384|SHA-512], AES-[128|192|256]-CMAC, RSAES-OAEP-[2048|3072|4096]-*, ECDH-[P-256|P-384|P-521], ECDH-[brainpoolP256r1|brainpoolP384r1|brainpoolP512r1], ECDH-[Curve25519|X25519], ECDSA-[P-256|P-384|P-521]-*, EdDSA-[Ed25519|Ed448], RSASSA-PSS-[2048|3072|4096]-*, HKDF-[SHA-256|SHA-384|SHA-512], PBKDF2-HMAC-[SHA-256|SHA-384|SHA-512]-*, GOSTR3411-2012, GOST-28147</t>
         </is>
       </c>
       <c r="K47" s="5" t="n"/>
       <c r="L47" s="5" t="inlineStr">
         <is>
-          <t>No known patents (NIST Round 2 submission requirement: patent-free).</t>
+          <t>RSA: expired 2000; DH: expired 1997; ECC: Certicom/BlackBerry largely expired 2017–2022; AES, ChaCha20, SHA, HMAC: no known patents. LGPL-2.1-or-later.</t>
         </is>
       </c>
       <c r="M47" s="2" t="inlineStr">
@@ -3200,50 +3252,54 @@
     <row r="48" ht="23" customHeight="1">
       <c r="A48" s="5" t="inlineStr">
         <is>
-          <t>mldsa-native</t>
-        </is>
-      </c>
-      <c r="B48" s="13" t="n"/>
-      <c r="C48" s="3" t="inlineStr">
-        <is>
-          <t>Apache-2.0 OR MIT OR ISC</t>
-        </is>
-      </c>
-      <c r="D48" s="11" t="inlineStr">
-        <is>
-          <t>1.0.0-beta</t>
+          <t>liboqs-0.15.0</t>
+        </is>
+      </c>
+      <c r="B48" s="13" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="C48" s="5" t="inlineStr">
+        <is>
+          <t>MIT (+ third-party components)</t>
+        </is>
+      </c>
+      <c r="D48" s="3" t="inlineStr">
+        <is>
+          <t>0.15.0</t>
         </is>
       </c>
       <c r="E48" s="3" t="inlineStr">
         <is>
-          <t>https://github.com/pq-code-package/mldsa-native</t>
-        </is>
-      </c>
-      <c r="F48" s="3" t="inlineStr">
-        <is>
-          <t>https://github.com/pq-code-package/mldsa-native/archive/refs/heads/main.tar.gz</t>
+          <t>https://github.com/open-quantum-safe/liboqs</t>
+        </is>
+      </c>
+      <c r="F48" s="5" t="inlineStr">
+        <is>
+          <t>https://github.com/open-quantum-safe/liboqs/archive/refs/tags/0.15.0.tar.gz</t>
         </is>
       </c>
       <c r="G48" s="5" t="inlineStr">
         <is>
-          <t>mldsa-native — ML-DSA FIPS 204, C90, CBMC-verified (alpha)</t>
+          <t>liboqs — Open Quantum Safe C library (ML-KEM, ML-DSA, SLH-DSA, HQC, MAYO, CROSS, UOV, SNOVA…)</t>
         </is>
       </c>
       <c r="H48" s="5" t="inlineStr">
         <is>
-          <t>v1.0.0-beta</t>
+          <t>v0.15.0 (2025-11-14)</t>
         </is>
       </c>
       <c r="I48" s="5" t="n"/>
       <c r="J48" s="5" t="inlineStr">
         <is>
-          <t>ML-DSA-[44|65|87]-(hedged), HashML-DSA-[44|65|87]</t>
+          <t>ML-KEM-[512|768|1024], ML-DSA-[44|65|87]-*, SLH-DSA-*, FN-DSA-[512|1024], HQC-[128|192|256], MAYO-*, CROSS-*, UOV-*, SNOVA-*</t>
         </is>
       </c>
       <c r="K48" s="5" t="n"/>
       <c r="L48" s="5" t="inlineStr">
         <is>
-          <t>No known patents.</t>
+          <t>ML-KEM: NIST patent licenses secured; FN-DSA: NTRU patents placed in public domain (Security Innovation, 2017); RSA: US 4,405,829 expired 2000; ECC: Certicom/BlackBerry portfolio largely expired 2017–2022. No library-level patents.</t>
         </is>
       </c>
       <c r="M48" s="2" t="inlineStr">
@@ -3255,50 +3311,54 @@
     <row r="49" ht="23" customHeight="1">
       <c r="A49" s="5" t="inlineStr">
         <is>
-          <t>mlkem-libjade</t>
-        </is>
-      </c>
-      <c r="B49" s="13" t="n"/>
-      <c r="C49" s="3" t="inlineStr">
-        <is>
-          <t>Apache-2.0</t>
-        </is>
-      </c>
-      <c r="D49" s="11" t="inlineStr">
-        <is>
-          <t>2025.12.1</t>
+          <t>libosmocore-1.14.0</t>
+        </is>
+      </c>
+      <c r="B49" s="13" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="C49" s="5" t="inlineStr">
+        <is>
+          <t>GPL-2.0-or-later</t>
+        </is>
+      </c>
+      <c r="D49" s="3" t="inlineStr">
+        <is>
+          <t>1.14.0</t>
         </is>
       </c>
       <c r="E49" s="3" t="inlineStr">
         <is>
-          <t>https://github.com/pq-code-package/mlkem-libjade</t>
-        </is>
-      </c>
-      <c r="F49" s="3" t="inlineStr">
-        <is>
-          <t>https://github.com/pq-code-package/mlkem-libjade/archive/refs/heads/main.tar.gz</t>
+          <t>https://gitea.osmocom.org/osmocom/libosmocore</t>
+        </is>
+      </c>
+      <c r="F49" s="5" t="inlineStr">
+        <is>
+          <t>https://downloads.osmocom.org/releases/libosmocore/libosmocore-1.14.0.tar.bz2</t>
         </is>
       </c>
       <c r="G49" s="5" t="inlineStr">
         <is>
-          <t>mlkem-libjade — ML-KEM libjade formally-verified Jasmin</t>
+          <t>libosmocore — Osmocom GSM/3GPP utility library (C); MILENAGE, A5/1, A5/2, GEA algorithms</t>
         </is>
       </c>
       <c r="H49" s="5" t="inlineStr">
         <is>
-          <t>v2025.12.1</t>
+          <t>Rolling releases; actively maintained by Osmocom project</t>
         </is>
       </c>
       <c r="I49" s="5" t="n"/>
       <c r="J49" s="5" t="inlineStr">
         <is>
-          <t>ML-KEM-[512|768|1024]</t>
+          <t>MILENAGE, A5/1, A5/2, GEA-[0|1|2|3|4|5]-*, KASUMI</t>
         </is>
       </c>
       <c r="K49" s="5" t="n"/>
       <c r="L49" s="5" t="inlineStr">
         <is>
-          <t>ML-KEM: NIST secured patent license agreements (freely available). No known unencumbered patents.</t>
+          <t>A5/1 and A5/2 were proprietary algorithms; original IP owned by 3GPP/ETSI. Practically treated as public knowledge since 1999 leak. No licensing restrictions on open-source implementations.</t>
         </is>
       </c>
       <c r="M49" s="2" t="inlineStr">
@@ -3310,7 +3370,7 @@
     <row r="50" ht="23" customHeight="1">
       <c r="A50" s="5" t="inlineStr">
         <is>
-          <t>mlkem-native-1.1.0</t>
+          <t>libsodium-1.0.22</t>
         </is>
       </c>
       <c r="B50" s="13" t="inlineStr">
@@ -3318,46 +3378,42 @@
           <t>x</t>
         </is>
       </c>
-      <c r="C50" s="3" t="inlineStr">
-        <is>
-          <t>Apache-2.0 OR MIT OR ISC</t>
+      <c r="C50" s="5" t="inlineStr">
+        <is>
+          <t>ISC</t>
         </is>
       </c>
       <c r="D50" s="3" t="inlineStr">
         <is>
-          <t>1.1.0</t>
+          <t>1.0.22</t>
         </is>
       </c>
       <c r="E50" s="3" t="inlineStr">
         <is>
-          <t>https://github.com/pq-code-package/mlkem-native</t>
-        </is>
-      </c>
-      <c r="F50" s="3" t="inlineStr">
-        <is>
-          <t>https://github.com/pq-code-package/mlkem-native/archive/refs/tags/v1.1.0.tar.gz</t>
+          <t>https://github.com/jedisct1/libsodium</t>
+        </is>
+      </c>
+      <c r="F50" s="5" t="inlineStr">
+        <is>
+          <t>https://github.com/jedisct1/libsodium/archive/refs/tags/1.0.22-RELEASE.tar.gz</t>
         </is>
       </c>
       <c r="G50" s="5" t="inlineStr">
         <is>
-          <t>mlkem-native — ML-KEM FIPS 203, C90 + AArch64/AVX2 asm, CBMC-verified</t>
+          <t>libsodium — modern crypto primitives (C); X25519, Ed25519, ChaCha20-Poly1305; no PQC</t>
         </is>
       </c>
       <c r="H50" s="5" t="n"/>
-      <c r="I50" s="5" t="inlineStr">
-        <is>
-          <t>stable</t>
-        </is>
-      </c>
+      <c r="I50" s="5" t="n"/>
       <c r="J50" s="5" t="inlineStr">
         <is>
-          <t>ML-KEM-[512|768|1024]</t>
+          <t>ECDH-[Curve25519|X25519], EdDSA-Ed25519, ChaCha20-Poly1305, HMAC-SHA-512, Argon2id-*, scrypt-*, ML-KEM-768</t>
         </is>
       </c>
       <c r="K50" s="5" t="n"/>
       <c r="L50" s="5" t="inlineStr">
         <is>
-          <t>ML-KEM: NIST secured patent license agreements (freely available to all implementers). No known unencumbered patents.</t>
+          <t>EdDSA/Ed25519, X25519, ChaCha20-Poly1305, Argon2, scrypt: no known patents.</t>
         </is>
       </c>
       <c r="M50" s="2" t="inlineStr">
@@ -3369,50 +3425,54 @@
     <row r="51" ht="23" customHeight="1">
       <c r="A51" s="5" t="inlineStr">
         <is>
-          <t>mqom-v2</t>
-        </is>
-      </c>
-      <c r="B51" s="13" t="n"/>
-      <c r="C51" s="3" t="inlineStr">
-        <is>
-          <t>MIT</t>
-        </is>
-      </c>
-      <c r="D51" s="11" t="inlineStr">
-        <is>
-          <t>2.1.0</t>
+          <t>libsrtp-2.8.0</t>
+        </is>
+      </c>
+      <c r="B51" s="13" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="C51" s="5" t="inlineStr">
+        <is>
+          <t>BSD-3-Clause</t>
+        </is>
+      </c>
+      <c r="D51" s="3" t="inlineStr">
+        <is>
+          <t>2.8.0</t>
         </is>
       </c>
       <c r="E51" s="3" t="inlineStr">
         <is>
-          <t>https://github.com/mqom/mqom-v2</t>
-        </is>
-      </c>
-      <c r="F51" s="3" t="inlineStr">
-        <is>
-          <t>https://github.com/mqom/mqom-v2/archive/refs/heads/main.tar.gz</t>
+          <t>https://github.com/cisco/libsrtp</t>
+        </is>
+      </c>
+      <c r="F51" s="5" t="inlineStr">
+        <is>
+          <t>https://github.com/cisco/libsrtp/archive/refs/tags/v2.8.0.tar.gz</t>
         </is>
       </c>
       <c r="G51" s="5" t="inlineStr">
         <is>
-          <t>MQOM-v2 — MQ on my Mind v2 (spec v2.1, 2025)</t>
+          <t>Cisco SRTP implementation (RFC 3711)</t>
         </is>
       </c>
       <c r="H51" s="5" t="inlineStr">
         <is>
-          <t>v2.1.0</t>
+          <t>Stable release</t>
         </is>
       </c>
       <c r="I51" s="5" t="n"/>
       <c r="J51" s="5" t="inlineStr">
         <is>
-          <t>MQOM-*</t>
+          <t>SRTP-*</t>
         </is>
       </c>
       <c r="K51" s="5" t="n"/>
       <c r="L51" s="5" t="inlineStr">
         <is>
-          <t>No known patents (NIST Round 2 submission requirement: patent-free).</t>
+          <t>No known patents.</t>
         </is>
       </c>
       <c r="M51" s="2" t="inlineStr">
@@ -3424,56 +3484,60 @@
     <row r="52" ht="23" customHeight="1">
       <c r="A52" s="5" t="inlineStr">
         <is>
-          <t>mt19937-stdlibs</t>
-        </is>
-      </c>
-      <c r="B52" s="13" t="n"/>
-      <c r="C52" s="11" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="D52" s="11" t="inlineStr">
-        <is>
-          <t>N/A</t>
+          <t>libtomcrypt-1.18.2</t>
+        </is>
+      </c>
+      <c r="B52" s="13" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="C52" s="10" t="inlineStr">
+        <is>
+          <t>Unlicense</t>
+        </is>
+      </c>
+      <c r="D52" s="3" t="inlineStr">
+        <is>
+          <t>1.18.2</t>
         </is>
       </c>
       <c r="E52" s="3" t="inlineStr">
         <is>
-          <t>https://en.wikipedia.org/wiki/Mersenne_Twister</t>
-        </is>
-      </c>
-      <c r="F52" s="7" t="inlineStr">
-        <is>
-          <t>https://github.com/stdlib-js/stdlib/archive/refs/heads/develop.zip</t>
+          <t>https://github.com/libtom/libtomcrypt</t>
+        </is>
+      </c>
+      <c r="F52" s="5" t="inlineStr">
+        <is>
+          <t>https://github.com/libtom/libtomcrypt/archive/refs/tags/v1.18.2.tar.gz</t>
         </is>
       </c>
       <c r="G52" s="5" t="inlineStr">
         <is>
-          <t>MT19937 Mersenne Twister (C++ &lt;random&gt;, Python random module)</t>
+          <t>LibTomCrypt — modular, portable cryptographic toolkit in C</t>
         </is>
       </c>
       <c r="H52" s="5" t="inlineStr">
         <is>
-          <t>Standard library built-in</t>
-        </is>
-      </c>
-      <c r="I52" s="5" t="n"/>
+          <t>v1.18.2 (2018-07-02)</t>
+        </is>
+      </c>
+      <c r="I52" s="5" t="inlineStr">
+        <is>
+          <t>outdated code</t>
+        </is>
+      </c>
       <c r="J52" s="5" t="inlineStr">
         <is>
-          <t>MT19937</t>
+          <t>AES-[128|192|256]-[CBC|CTR|GCM|CCM|EAX|OCB], Twofish-*, Serpent-*, Blowfish-*, 3DES, DES, SHA-[1|256|384|512], SHA3-*, MD5, HMAC-*, RSASSA-PKCS1-*, RSAES-OAEP-*, DSA, ECDSA-*, ECDH-*, Fortuna, Yarrow</t>
         </is>
       </c>
       <c r="K52" s="5" t="inlineStr">
         <is>
-          <t>Different implementations exist under different licenses; need to cover these</t>
-        </is>
-      </c>
-      <c r="L52" s="5" t="inlineStr">
-        <is>
-          <t>No known patents.</t>
-        </is>
-      </c>
+          <t>Big-integer math via pluggable provider (libtommath/TomsFastMath/GMP). Project dormant since 2018.</t>
+        </is>
+      </c>
+      <c r="L52" s="5" t="n"/>
       <c r="M52" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve"> </t>
@@ -3483,58 +3547,50 @@
     <row r="53" ht="23" customHeight="1">
       <c r="A53" s="5" t="inlineStr">
         <is>
-          <t>nettle-4.0.0</t>
-        </is>
-      </c>
-      <c r="B53" s="13" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
-      <c r="C53" s="3" t="inlineStr">
-        <is>
-          <t>LGPL-3.0-or-later OR GPL-2.0-or-later</t>
-        </is>
-      </c>
-      <c r="D53" s="3" t="inlineStr">
-        <is>
-          <t>4.0.0</t>
+          <t>linux-dev-random</t>
+        </is>
+      </c>
+      <c r="B53" s="13" t="n"/>
+      <c r="C53" s="5" t="inlineStr">
+        <is>
+          <t>GPL-2.0-only</t>
+        </is>
+      </c>
+      <c r="D53" s="11" t="inlineStr">
+        <is>
+          <t>N/A</t>
         </is>
       </c>
       <c r="E53" s="3" t="inlineStr">
         <is>
-          <t>https://git.lysator.liu.se/nettle/nettle</t>
-        </is>
-      </c>
-      <c r="F53" s="3" t="inlineStr">
-        <is>
-          <t>https://ftp.gnu.org/gnu/nettle/nettle-4.0.tar.gz</t>
+          <t>https://www.kernel.org/</t>
+        </is>
+      </c>
+      <c r="F53" s="8" t="inlineStr">
+        <is>
+          <t>https://github.com/torvalds/linux/blob/master/drivers/char/random.c</t>
         </is>
       </c>
       <c r="G53" s="5" t="inlineStr">
         <is>
-          <t>Nettle — low-level crypto library (C) used by GnuTLS; AES, ChaCha20, SHA-3; no PQC</t>
+          <t>Linux kernel /dev/random and /dev/urandom (CSPRNG)</t>
         </is>
       </c>
       <c r="H53" s="5" t="inlineStr">
         <is>
-          <t>4.0.0</t>
-        </is>
-      </c>
-      <c r="I53" s="5" t="inlineStr">
-        <is>
-          <t>stable</t>
-        </is>
-      </c>
+          <t>OS kernel facility</t>
+        </is>
+      </c>
+      <c r="I53" s="5" t="n"/>
       <c r="J53" s="5" t="inlineStr">
         <is>
-          <t>AES-[128|192|256]-[GCM|CBC|CTR|CCM], ChaCha20-Poly1305, SHA-[256|384|512], SHA3-[256|384|512], HMAC-[SHA-256|SHA-384|SHA-512], ECDH-[P-256|P-384|P-521], ECDH-[Curve25519|X25519], ECDSA-[P-256|P-384|P-521]-*, EdDSA-Ed25519, RSASSA-PSS-[2048|3072|4096]-*, RSAES-OAEP-[2048|3072|4096]-*</t>
+          <t>dev-random, dev-urandom</t>
         </is>
       </c>
       <c r="K53" s="5" t="n"/>
       <c r="L53" s="5" t="inlineStr">
         <is>
-          <t>RSA: expired 2000; DH: expired 1997; ECC: Certicom/BlackBerry largely expired 2017–2022; AES, ChaCha20, SHA, HMAC: no known patents. LGPL-3.0-or-later OR GPL-2.0-or-later.</t>
+          <t>No known patents.</t>
         </is>
       </c>
       <c r="M53" s="2" t="inlineStr">
@@ -3546,56 +3602,50 @@
     <row r="54" ht="23" customHeight="1">
       <c r="A54" s="5" t="inlineStr">
         <is>
-          <t>nss-3.123</t>
-        </is>
-      </c>
-      <c r="B54" s="13" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
-      <c r="C54" s="3" t="inlineStr">
-        <is>
-          <t>MPL-2.0</t>
-        </is>
-      </c>
-      <c r="D54" s="3" t="n">
-        <v>3123</v>
+          <t>linux-getrandom</t>
+        </is>
+      </c>
+      <c r="B54" s="13" t="n"/>
+      <c r="C54" s="5" t="inlineStr">
+        <is>
+          <t>GPL-2.0-only</t>
+        </is>
+      </c>
+      <c r="D54" s="11" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
       </c>
       <c r="E54" s="3" t="inlineStr">
         <is>
-          <t>https://github.com/nss-dev/nss</t>
-        </is>
-      </c>
-      <c r="F54" s="3" t="inlineStr">
-        <is>
-          <t>https://github.com/nss-dev/nss/archive/refs/tags/NSS_3_123_RTM.tar.gz</t>
+          <t>https://www.kernel.org/</t>
+        </is>
+      </c>
+      <c r="F54" s="8" t="inlineStr">
+        <is>
+          <t>https://github.com/bminor/glibc/blob/master/sysdeps/unix/sysv/linux/getrandom.c</t>
         </is>
       </c>
       <c r="G54" s="5" t="inlineStr">
         <is>
-          <t>Mozilla NSS — TLS/crypto library (C); ML-KEM, ML-DSA; used by Firefox, many Linux distributions</t>
+          <t>Linux kernel getrandom() syscall</t>
         </is>
       </c>
       <c r="H54" s="5" t="inlineStr">
         <is>
-          <t>NSS_3_122_RTM</t>
-        </is>
-      </c>
-      <c r="I54" s="5" t="inlineStr">
-        <is>
-          <t>stable</t>
-        </is>
-      </c>
+          <t>OS kernel facility</t>
+        </is>
+      </c>
+      <c r="I54" s="5" t="n"/>
       <c r="J54" s="5" t="inlineStr">
         <is>
-          <t>AES-[128|192|256]-[GCM|CCM|CBC|CTR], ChaCha20-Poly1305, SHA-[256|384|512], SHA3-[256|384|512], HMAC-[SHA-256|SHA-384|SHA-512], AES-[128|192|256]-CMAC, RSAES-OAEP-[2048|3072|4096]-*, ECDH-[P-256|P-384|P-521], ECDH-[Curve25519|X25519], ECDSA-[P-256|P-384|P-521]-*, EdDSA-[Ed25519|Ed448], RSASSA-PSS-[2048|3072|4096]-*, HKDF-[SHA-256|SHA-384|SHA-512], PBKDF2-HMAC-[SHA-256|SHA-384|SHA-512]-*, ML-KEM-[512|768|1024], ML-DSA-[44|65|87]-*</t>
+          <t>getrandom</t>
         </is>
       </c>
       <c r="K54" s="5" t="n"/>
       <c r="L54" s="5" t="inlineStr">
         <is>
-          <t>RSA: expired 2000; DH: expired 1997; ECC: Certicom/BlackBerry largely expired 2017–2022; ML-KEM: NIST patent licenses secured; ML-DSA: no known patents; AES, ChaCha20, SHA, HMAC: no known patents. MPL-2.0 includes patent grant.</t>
+          <t>No known patents.</t>
         </is>
       </c>
       <c r="M54" s="2" t="inlineStr">
@@ -3607,54 +3657,50 @@
     <row r="55" ht="23" customHeight="1">
       <c r="A55" s="5" t="inlineStr">
         <is>
-          <t>opaque-ke-4.0.1</t>
-        </is>
-      </c>
-      <c r="B55" s="13" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
+          <t>mayo-c</t>
+        </is>
+      </c>
+      <c r="B55" s="13" t="n"/>
       <c r="C55" s="3" t="inlineStr">
         <is>
-          <t>MIT</t>
-        </is>
-      </c>
-      <c r="D55" s="3" t="inlineStr">
-        <is>
-          <t>4.0.1</t>
+          <t>Apache-2.0</t>
+        </is>
+      </c>
+      <c r="D55" s="11" t="inlineStr">
+        <is>
+          <t>round2</t>
         </is>
       </c>
       <c r="E55" s="3" t="inlineStr">
         <is>
-          <t>https://github.com/facebook/opaque-ke</t>
+          <t>https://github.com/PQCMayo/MAYO-C</t>
         </is>
       </c>
       <c r="F55" s="3" t="inlineStr">
         <is>
-          <t>https://github.com/facebook/opaque-ke/archive/refs/tags/v4.0.1.zip</t>
+          <t>https://github.com/PQCMayo/MAYO-C/archive/refs/heads/main.tar.gz</t>
         </is>
       </c>
       <c r="G55" s="5" t="inlineStr">
         <is>
-          <t>opaque-ke — Rust OPAQUE-3DH implementation (Meta; IETF draft-irtf-cfrg-opaque)</t>
-        </is>
-      </c>
-      <c r="H55" s="5" t="n"/>
-      <c r="I55" s="5" t="inlineStr">
-        <is>
-          <t>stable</t>
-        </is>
-      </c>
+          <t>MAYO-C — official C implementation (multivariate UOV-based)</t>
+        </is>
+      </c>
+      <c r="H55" s="5" t="inlineStr">
+        <is>
+          <t>NIST Round 2 submission</t>
+        </is>
+      </c>
+      <c r="I55" s="5" t="n"/>
       <c r="J55" s="5" t="inlineStr">
         <is>
-          <t>OPAQUE-3DH-*</t>
+          <t>MAYO-[1|2|3|5]</t>
         </is>
       </c>
       <c r="K55" s="5" t="n"/>
       <c r="L55" s="5" t="inlineStr">
         <is>
-          <t>No known patents.</t>
+          <t>No known patents (NIST Round 2 submission requirement: patent-free).</t>
         </is>
       </c>
       <c r="M55" s="2" t="inlineStr">
@@ -3666,58 +3712,58 @@
     <row r="56" ht="23" customHeight="1">
       <c r="A56" s="5" t="inlineStr">
         <is>
-          <t>open5gs-2.7.7</t>
+          <t>mbedtls-3.6.6</t>
         </is>
       </c>
       <c r="B56" s="13" t="inlineStr">
         <is>
-          <t>x</t>
+          <t>-</t>
         </is>
       </c>
       <c r="C56" s="3" t="inlineStr">
         <is>
-          <t>AGPL-3.0-only</t>
+          <t>Apache-2.0</t>
         </is>
       </c>
       <c r="D56" s="3" t="inlineStr">
         <is>
-          <t>2.7.7</t>
+          <t>3.6.6</t>
         </is>
       </c>
       <c r="E56" s="3" t="inlineStr">
         <is>
-          <t>https://github.com/open5gs/open5gs</t>
+          <t>https://github.com/Mbed-TLS/mbedtls</t>
         </is>
       </c>
       <c r="F56" s="3" t="inlineStr">
         <is>
-          <t>https://github.com/open5gs/open5gs/archive/refs/tags/v2.7.7.tar.gz</t>
+          <t>https://github.com/Mbed-TLS/mbedtls/archive/refs/tags/mbedtls-3.6.6.tar.gz</t>
         </is>
       </c>
       <c r="G56" s="5" t="inlineStr">
         <is>
-          <t>Open5GS — open-source 5G/4G core network (C); MILENAGE, TUAK, 128-EEA1/3, 128-EIA1/3</t>
+          <t>Mbed-TLS — embedded TLS/crypto (C); LTS 3.6.x branch; no PQC (ML-DSA added in 4.x roadmap Q2 2026)</t>
         </is>
       </c>
       <c r="H56" s="5" t="inlineStr">
         <is>
-          <t>v2.7.6 — 2025; 5G SA core with full 3GPP AKA authentication support</t>
+          <t>3.6.6 LTS (2025)</t>
         </is>
       </c>
       <c r="I56" s="5" t="inlineStr">
         <is>
-          <t>stable</t>
+          <t>previous</t>
         </is>
       </c>
       <c r="J56" s="5" t="inlineStr">
         <is>
-          <t>MILENAGE, TUAK, 128-EEA1, 128-EEA3, 128-EIA1, 128-EIA3</t>
+          <t>AES-*, ChaCha20-Poly1305, SHA-*, HMAC-*, AES-CMAC, RSAES-OAEP-*, ECDH-*, ECDSA-*, EdDSA-*, RSASSA-PSS-*, HKDF-*, PBKDF2-*</t>
         </is>
       </c>
       <c r="K56" s="5" t="n"/>
       <c r="L56" s="5" t="inlineStr">
         <is>
-          <t>No known patents on MILENAGE/TUAK implementations. TUAK uses Keccak; Keccak patent-free.</t>
+          <t>RSA: expired 2000; DH: expired 1997; ECC: Certicom/BlackBerry largely expired 2017–2022; AES, ChaCha20, SHA, HMAC: no known patents (no PQC). Apache-2.0 license includes patent grant.</t>
         </is>
       </c>
       <c r="M56" s="2" t="inlineStr">
@@ -3729,54 +3775,56 @@
     <row r="57" ht="23" customHeight="1">
       <c r="A57" s="5" t="inlineStr">
         <is>
-          <t>openjdk-17</t>
+          <t>mbedtls-4.1.0</t>
         </is>
       </c>
       <c r="B57" s="13" t="inlineStr">
         <is>
-          <t xml:space="preserve">(c) </t>
+          <t>x</t>
         </is>
       </c>
       <c r="C57" s="3" t="inlineStr">
         <is>
-          <t>GPL-2.0-only WITH Classpath-exception-2.0</t>
-        </is>
-      </c>
-      <c r="D57" s="3" t="n">
-        <v>17</v>
+          <t>Apache-2.0</t>
+        </is>
+      </c>
+      <c r="D57" s="3" t="inlineStr">
+        <is>
+          <t>4.1.0</t>
+        </is>
       </c>
       <c r="E57" s="3" t="inlineStr">
         <is>
-          <t>https://github.com/openjdk/jdk</t>
+          <t>https://github.com/Mbed-TLS/mbedtls</t>
         </is>
       </c>
       <c r="F57" s="3" t="inlineStr">
         <is>
-          <t>https://github.com/openjdk/jdk/archive/refs/tags/jdk-17+35.zip</t>
+          <t>https://github.com/Mbed-TLS/mbedtls/archive/refs/tags/v4.1.0.tar.gz</t>
         </is>
       </c>
       <c r="G57" s="5" t="inlineStr">
         <is>
-          <t>OpenJDK — JCA/JCE crypto framework (Java); ML-KEM/ML-DSA APIs in incubating preview in JDK 25; HPKE API not yet GA</t>
-        </is>
-      </c>
-      <c r="H57" s="5" t="inlineStr">
-        <is>
-          <t>LTS</t>
-        </is>
-      </c>
+          <t>Mbed-TLS — embedded TLS/crypto (C); PQC (ML-DSA) on roadmap Q2 2026; LTS 3.6.x branch parallel</t>
+        </is>
+      </c>
+      <c r="H57" s="5" t="n"/>
       <c r="I57" s="5" t="inlineStr">
         <is>
-          <t>lts</t>
+          <t>stable</t>
         </is>
       </c>
       <c r="J57" s="5" t="inlineStr">
         <is>
-          <t>AES-[128|192|256]-*, SHA-[1|224|256|384|512], SHA3-*, HMAC-*, ECDSA-*, EdDSA-Ed25519, EdDSA-Ed448, RSASSA-PSS-*, RSASSA-PKCS1-*, RSAES-OAEP-*, ECDH-*, FFDH-*, HKDF-*, ChaCha20-Poly1305, Poly1305</t>
+          <t>AES-[128|192|256]-[GCM|CCM|CBC|CTR|OFB|CFB128|XTS], ChaCha20-Poly1305, SHA-[256|384|512], SHA3-[256|384|512], HMAC-[SHA-256|SHA-384|SHA-512], AES-[128|192|256]-CMAC, RSAES-OAEP-[2048|3072|4096]-*, ECDH-[P-256|P-384|P-521], ECDH-[Curve25519|X25519], ECDH-[Curve448|X448], ECDSA-[P-256|P-384|P-521]-*, EdDSA-[Ed25519|Ed448], RSASSA-PSS-[2048|3072|4096]-*, HKDF-[SHA-256|SHA-384|SHA-512], PBKDF2-HMAC-[SHA-256|SHA-384|SHA-512]-*, ML-KEM-[512|768|1024]</t>
         </is>
       </c>
       <c r="K57" s="5" t="n"/>
-      <c r="L57" s="5" t="n"/>
+      <c r="L57" s="5" t="inlineStr">
+        <is>
+          <t>RSA: expired 2000; DH: expired 1997; ECC: Certicom/BlackBerry largely expired 2017–2022; ML-KEM: NIST patent licenses secured; AES, ChaCha20, SHA, HMAC: no known patents. Apache-2.0 license includes patent grant.</t>
+        </is>
+      </c>
       <c r="M57" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve"> </t>
@@ -3786,54 +3834,56 @@
     <row r="58" ht="23" customHeight="1">
       <c r="A58" s="5" t="inlineStr">
         <is>
-          <t>openjdk-21</t>
+          <t>mirith-nist-submission</t>
         </is>
       </c>
       <c r="B58" s="13" t="inlineStr">
         <is>
-          <t xml:space="preserve">(c) </t>
+          <t>x</t>
         </is>
       </c>
       <c r="C58" s="3" t="inlineStr">
         <is>
-          <t>GPL-2.0-only WITH Classpath-exception-2.0</t>
-        </is>
-      </c>
-      <c r="D58" s="3" t="n">
-        <v>21</v>
+          <t>Apache-2.0</t>
+        </is>
+      </c>
+      <c r="D58" s="11" t="inlineStr">
+        <is>
+          <t>1.1.0</t>
+        </is>
       </c>
       <c r="E58" s="3" t="inlineStr">
         <is>
-          <t>https://github.com/openjdk/jdk</t>
+          <t>https://github.com/Crypto-TII/mirith_nist_submission</t>
         </is>
       </c>
       <c r="F58" s="3" t="inlineStr">
         <is>
-          <t>https://github.com/openjdk/jdk/archive/refs/tags/jdk-21+35.zip</t>
+          <t>https://github.com/Crypto-TII/mirith_nist_submission/archive/refs/heads/main.tar.gz</t>
         </is>
       </c>
       <c r="G58" s="5" t="inlineStr">
         <is>
-          <t>OpenJDK — JCA/JCE crypto framework (Java); ML-KEM/ML-DSA APIs in incubating preview in JDK 25; HPKE API not yet GA</t>
+          <t>Mirath — merger of MIRA + MiRitH (MinRank in the Head)</t>
         </is>
       </c>
       <c r="H58" s="5" t="inlineStr">
         <is>
-          <t>LTS</t>
-        </is>
-      </c>
-      <c r="I58" s="5" t="inlineStr">
-        <is>
-          <t>lts</t>
-        </is>
-      </c>
+          <t>v1.1.0</t>
+        </is>
+      </c>
+      <c r="I58" s="5" t="n"/>
       <c r="J58" s="5" t="inlineStr">
         <is>
-          <t>AES-[128|192|256]-*, SHA-[1|224|256|384|512], SHA3-*, HMAC-*, ECDSA-*, EdDSA-Ed25519, EdDSA-Ed448, RSASSA-PSS-*, RSASSA-PKCS1-*, RSAES-OAEP-*, ECDH-*, FFDH-*, HKDF-*, ChaCha20-Poly1305, Poly1305</t>
+          <t>Mirath-*</t>
         </is>
       </c>
       <c r="K58" s="5" t="n"/>
-      <c r="L58" s="5" t="n"/>
+      <c r="L58" s="5" t="inlineStr">
+        <is>
+          <t>No known patents (NIST Round 2 submission requirement: patent-free).</t>
+        </is>
+      </c>
       <c r="M58" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve"> </t>
@@ -3843,54 +3893,52 @@
     <row r="59" ht="23" customHeight="1">
       <c r="A59" s="5" t="inlineStr">
         <is>
-          <t>openjdk-27</t>
-        </is>
-      </c>
-      <c r="B59" s="13" t="inlineStr">
-        <is>
-          <t xml:space="preserve">(c) </t>
-        </is>
-      </c>
+          <t>mldsa-native</t>
+        </is>
+      </c>
+      <c r="B59" s="13" t="n"/>
       <c r="C59" s="3" t="inlineStr">
         <is>
-          <t>GPL-2.0-only WITH Classpath-exception-2.0</t>
-        </is>
-      </c>
-      <c r="D59" s="3" t="n">
-        <v>27</v>
+          <t>Apache-2.0 OR MIT OR ISC</t>
+        </is>
+      </c>
+      <c r="D59" s="11" t="inlineStr">
+        <is>
+          <t>1.0.0-beta2</t>
+        </is>
       </c>
       <c r="E59" s="3" t="inlineStr">
         <is>
-          <t>https://github.com/openjdk/jdk</t>
+          <t>https://github.com/pq-code-package/mldsa-native</t>
         </is>
       </c>
       <c r="F59" s="3" t="inlineStr">
         <is>
-          <t>https://github.com/openjdk/jdk/archive/refs/tags/jdk-27+18.zip</t>
+          <t>https://github.com/pq-code-package/mldsa-native/archive/refs/tags/v1.0.0-beta2.tar.gz</t>
         </is>
       </c>
       <c r="G59" s="5" t="inlineStr">
         <is>
-          <t>OpenJDK — JCA/JCE crypto framework (Java); ML-KEM/ML-DSA APIs in incubating preview in JDK 25; HPKE API not yet GA</t>
+          <t>mldsa-native — ML-DSA FIPS 204, C90, CBMC-verified (alpha)</t>
         </is>
       </c>
       <c r="H59" s="5" t="inlineStr">
         <is>
-          <t>LTS</t>
-        </is>
-      </c>
-      <c r="I59" s="5" t="inlineStr">
-        <is>
-          <t>lts</t>
-        </is>
-      </c>
+          <t>v1.0.0-beta2 (2026-05-23)</t>
+        </is>
+      </c>
+      <c r="I59" s="5" t="n"/>
       <c r="J59" s="5" t="inlineStr">
         <is>
-          <t>AES-[128|192|256]-*, SHA-[1|224|256|384|512], SHA3-*, HMAC-*, ECDSA-*, EdDSA-Ed25519, EdDSA-Ed448, RSASSA-PSS-*, RSASSA-PKCS1-*, RSAES-OAEP-*, ECDH-*, FFDH-*, HKDF-*, ChaCha20-Poly1305, Poly1305, HPKE-*, ML-KEM-[512|768|1024], ML-DSA-[44|65|87]-*</t>
+          <t>ML-DSA-[44|65|87]-(hedged), HashML-DSA-[44|65|87]</t>
         </is>
       </c>
       <c r="K59" s="5" t="n"/>
-      <c r="L59" s="5" t="n"/>
+      <c r="L59" s="5" t="inlineStr">
+        <is>
+          <t>No known patents.</t>
+        </is>
+      </c>
       <c r="M59" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve"> </t>
@@ -3900,7 +3948,7 @@
     <row r="60" ht="23" customHeight="1">
       <c r="A60" s="5" t="inlineStr">
         <is>
-          <t>openmls-0.8.1</t>
+          <t>mlkem-libjade</t>
         </is>
       </c>
       <c r="B60" s="13" t="inlineStr">
@@ -3908,46 +3956,46 @@
           <t>x</t>
         </is>
       </c>
-      <c r="C60" s="5" t="inlineStr">
-        <is>
-          <t>MIT</t>
-        </is>
-      </c>
-      <c r="D60" s="3" t="inlineStr">
-        <is>
-          <t>0.8.1</t>
+      <c r="C60" s="3" t="inlineStr">
+        <is>
+          <t>Apache-2.0</t>
+        </is>
+      </c>
+      <c r="D60" s="11" t="inlineStr">
+        <is>
+          <t>2025.12.1</t>
         </is>
       </c>
       <c r="E60" s="3" t="inlineStr">
         <is>
-          <t>https://github.com/openmls/openmls</t>
-        </is>
-      </c>
-      <c r="F60" s="5" t="inlineStr">
-        <is>
-          <t>https://github.com/openmls/openmls/archive/refs/tags/openmls-v0.8.1.zip</t>
+          <t>https://github.com/pq-code-package/mlkem-libjade</t>
+        </is>
+      </c>
+      <c r="F60" s="3" t="inlineStr">
+        <is>
+          <t>https://github.com/pq-code-package/mlkem-libjade/archive/refs/heads/main.tar.gz</t>
         </is>
       </c>
       <c r="G60" s="5" t="inlineStr">
         <is>
-          <t>OpenMLS — Messaging Layer Security (RFC 9420) in Rust</t>
+          <t>mlkem-libjade — ML-KEM libjade formally-verified Jasmin</t>
         </is>
       </c>
       <c r="H60" s="5" t="inlineStr">
         <is>
-          <t>Stable release</t>
+          <t>v2025.12.1</t>
         </is>
       </c>
       <c r="I60" s="5" t="n"/>
       <c r="J60" s="5" t="inlineStr">
         <is>
-          <t>MLS-*</t>
+          <t>ML-KEM-[512|768|1024]</t>
         </is>
       </c>
       <c r="K60" s="5" t="n"/>
       <c r="L60" s="5" t="inlineStr">
         <is>
-          <t>No known patents.</t>
+          <t>ML-KEM: NIST secured patent license agreements (freely available). No known unencumbered patents.</t>
         </is>
       </c>
       <c r="M60" s="2" t="inlineStr">
@@ -3959,7 +4007,7 @@
     <row r="61" ht="23" customHeight="1">
       <c r="A61" s="5" t="inlineStr">
         <is>
-          <t>openssl-3.6.1</t>
+          <t>mlkem-native-1.1.0</t>
         </is>
       </c>
       <c r="B61" s="13" t="inlineStr">
@@ -3969,34 +4017,30 @@
       </c>
       <c r="C61" s="3" t="inlineStr">
         <is>
-          <t>Apache-2.0</t>
+          <t>Apache-2.0 OR MIT OR ISC</t>
         </is>
       </c>
       <c r="D61" s="3" t="inlineStr">
         <is>
-          <t>3.6.1</t>
+          <t>1.1.0</t>
         </is>
       </c>
       <c r="E61" s="3" t="inlineStr">
         <is>
-          <t>https://github.com/openssl/openssl</t>
+          <t>https://github.com/pq-code-package/mlkem-native</t>
         </is>
       </c>
       <c r="F61" s="3" t="inlineStr">
         <is>
-          <t>https://github.com/openssl/openssl/archive/refs/tags/openssl-3.6.1.tar.gz</t>
+          <t>https://github.com/pq-code-package/mlkem-native/archive/refs/tags/v1.1.0.tar.gz</t>
         </is>
       </c>
       <c r="G61" s="5" t="inlineStr">
         <is>
-          <t>OpenSSL — TLS/crypto library (C); ML-KEM, ML-DSA, SLH-DSA since 3.5.0 (FIPS provider); default TLS 1.3 key-share X25519+ML-KEM-768</t>
-        </is>
-      </c>
-      <c r="H61" s="5" t="inlineStr">
-        <is>
-          <t>openssl-3.6.1</t>
-        </is>
-      </c>
+          <t>mlkem-native — ML-KEM FIPS 203, C90 + AArch64/AVX2 asm, CBMC-verified</t>
+        </is>
+      </c>
+      <c r="H61" s="5" t="n"/>
       <c r="I61" s="5" t="inlineStr">
         <is>
           <t>stable</t>
@@ -4004,13 +4048,13 @@
       </c>
       <c r="J61" s="5" t="inlineStr">
         <is>
-          <t>AES-[128|192|256]-[GCM|CCM|GCM-SIV|CBC|CTR|OFB|CFB128|XTS|KW], ChaCha20-Poly1305, 3DES-*, SHA-[256|384|512], SHA3-[256|384|512], SHAKE128, SHAKE256, HMAC-[SHA-256|SHA-384|SHA-512], AES-[128|192|256]-CMAC, KMAC128, KMAC256, RSAES-OAEP-[2048|3072|4096]-*, ECDH-[P-256|P-384|P-521], ECDH-[Curve25519|X25519], ECDH-[Curve448|X448], FFDH-*, ECDSA-[P-256|P-384|P-521]-[SHA-256|SHA-384|SHA-512], EdDSA-[Ed25519|Ed448], RSASSA-PSS-[2048|3072|4096]-*, RSASSA-PKCS1-[2048|3072|4096]-*, HKDF-[SHA-256|SHA-384|SHA-512], PBKDF2-HMAC-[SHA-256|SHA-384|SHA-512]-*, SP800-108-*, ML-KEM-[512|768|1024], ML-DSA-[44|65|87]-*, SLH-DSA-*, HMAC_DRBG-[SHA-256|SHA-384|SHA-512], CTR_DRBG-AES-256</t>
+          <t>ML-KEM-[512|768|1024]</t>
         </is>
       </c>
       <c r="K61" s="5" t="n"/>
       <c r="L61" s="5" t="inlineStr">
         <is>
-          <t>RSA: US 4,405,829 expired 2000; DH: US 4,200,770 expired 1997; ECC (ECDH/ECDSA): Certicom/BlackBerry portfolio largely expired 2017–2022; AES, ChaCha20-Poly1305, SHA, HMAC: no known patents; ML-KEM: NIST patent licenses secured; FN-DSA: NTRU patents in public domain (Security Innovation, 2017). Apache-2.0 license includes patent grant.</t>
+          <t>ML-KEM: NIST secured patent license agreements (freely available to all implementers). No known unencumbered patents.</t>
         </is>
       </c>
       <c r="M61" s="2" t="inlineStr">
@@ -4022,56 +4066,60 @@
     <row r="62" ht="23" customHeight="1">
       <c r="A62" s="5" t="inlineStr">
         <is>
-          <t>openssl-des-ede</t>
+          <t>monocypher-4.0.3</t>
         </is>
       </c>
       <c r="B62" s="13" t="inlineStr">
         <is>
-          <t>(x)</t>
-        </is>
-      </c>
-      <c r="C62" s="3" t="inlineStr">
-        <is>
-          <t>Apache-2.0</t>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="C62" s="10" t="inlineStr">
+        <is>
+          <t>CC0-1.0</t>
         </is>
       </c>
       <c r="D62" s="3" t="inlineStr">
         <is>
-          <t>3.6.1</t>
+          <t>4.0.3</t>
         </is>
       </c>
       <c r="E62" s="3" t="inlineStr">
         <is>
-          <t>https://github.com/openssl/openssl</t>
-        </is>
-      </c>
-      <c r="F62" s="3" t="inlineStr">
-        <is>
-          <t>https://github.com/openssl/openssl/archive/refs/tags/openssl-3.6.1.tar.gz</t>
+          <t>https://github.com/LoupVaillant/Monocypher</t>
+        </is>
+      </c>
+      <c r="F62" s="5" t="inlineStr">
+        <is>
+          <t>https://github.com/LoupVaillant/Monocypher/archive/refs/tags/4.0.3.tar.gz</t>
         </is>
       </c>
       <c r="G62" s="5" t="inlineStr">
         <is>
-          <t>OpenSSL des-ede (2TDEA / 2-key Triple DES)</t>
+          <t>Monocypher — small, dependency-free cryptographic library in C (C99)</t>
         </is>
       </c>
       <c r="H62" s="5" t="inlineStr">
         <is>
-          <t>Stable release</t>
-        </is>
-      </c>
-      <c r="I62" s="5" t="n"/>
+          <t>4.0.3 (2026-06-15)</t>
+        </is>
+      </c>
+      <c r="I62" s="5" t="inlineStr">
+        <is>
+          <t>stable</t>
+        </is>
+      </c>
       <c r="J62" s="5" t="inlineStr">
         <is>
-          <t>2TDEA, 3DES, DES</t>
-        </is>
-      </c>
-      <c r="K62" s="5" t="n"/>
-      <c r="L62" s="5" t="inlineStr">
-        <is>
-          <t>No known patents.</t>
-        </is>
-      </c>
+          <t>XChaCha20-Poly1305, ChaCha20, BLAKE2b-*, Argon2i-*, ECDH-[Curve25519|X25519], EdDSA-Ed25519</t>
+        </is>
+      </c>
+      <c r="K62" s="5" t="inlineStr">
+        <is>
+          <t>Dependency-free; Elligator 2 support. Dual-licensed CC0-1.0 / BSD-2-Clause.</t>
+        </is>
+      </c>
+      <c r="L62" s="5" t="n"/>
       <c r="M62" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve"> </t>
@@ -4081,7 +4129,7 @@
     <row r="63" ht="23" customHeight="1">
       <c r="A63" s="5" t="inlineStr">
         <is>
-          <t>oqs-provider-0.11.0</t>
+          <t>mqom-v2</t>
         </is>
       </c>
       <c r="B63" s="13" t="inlineStr">
@@ -4094,37 +4142,41 @@
           <t>MIT</t>
         </is>
       </c>
-      <c r="D63" s="3" t="inlineStr">
-        <is>
-          <t>0.11.0</t>
+      <c r="D63" s="11" t="inlineStr">
+        <is>
+          <t>2.1.1</t>
         </is>
       </c>
       <c r="E63" s="3" t="inlineStr">
         <is>
-          <t>https://github.com/open-quantum-safe/oqs-provider</t>
+          <t>https://github.com/mqom/mqom-v2</t>
         </is>
       </c>
       <c r="F63" s="3" t="inlineStr">
         <is>
-          <t>https://github.com/open-quantum-safe/oqs-provider/archive/refs/tags/0.11.0.gz</t>
+          <t>https://github.com/mqom/mqom-v2/archive/refs/tags/v2.1.1.tar.gz</t>
         </is>
       </c>
       <c r="G63" s="5" t="inlineStr">
         <is>
-          <t>oqs-provider — OpenSSL 3 provider backed by liboqs (ML-KEM/DSA disabled vs. OpenSSL ≥ 3.5)</t>
-        </is>
-      </c>
-      <c r="H63" s="5" t="n"/>
+          <t>MQOM-v2 — MQ on my Mind v2 (spec v2.1, 2025)</t>
+        </is>
+      </c>
+      <c r="H63" s="5" t="inlineStr">
+        <is>
+          <t>v2.1.1 (2026-05-04)</t>
+        </is>
+      </c>
       <c r="I63" s="5" t="n"/>
       <c r="J63" s="5" t="inlineStr">
         <is>
-          <t>ML-KEM-[512|768|1024], ML-DSA-[44|65|87]-*, SLH-DSA-*, FN-DSA-[512|1024], HQC-[128|192|256], MAYO-*, CROSS-*, UOV-*, SNOVA-*</t>
+          <t>MQOM-*</t>
         </is>
       </c>
       <c r="K63" s="5" t="n"/>
       <c r="L63" s="5" t="inlineStr">
         <is>
-          <t>Inherits algorithm patent status from liboqs backend. No provider-level patents.</t>
+          <t>No known patents (NIST Round 2 submission requirement: patent-free).</t>
         </is>
       </c>
       <c r="M63" s="2" t="inlineStr">
@@ -4136,47 +4188,51 @@
     <row r="64" ht="23" customHeight="1">
       <c r="A64" s="5" t="inlineStr">
         <is>
-          <t>pcg-reference</t>
+          <t>mt19937-stdlibs</t>
         </is>
       </c>
       <c r="B64" s="13" t="n"/>
-      <c r="C64" s="3" t="inlineStr">
-        <is>
-          <t>Apache-2.0 OR MIT</t>
+      <c r="C64" s="11" t="inlineStr">
+        <is>
+          <t>N/A</t>
         </is>
       </c>
       <c r="D64" s="11" t="inlineStr">
         <is>
-          <t>UNRELEASED</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="E64" s="3" t="inlineStr">
         <is>
-          <t>https://www.pcg-random.org/</t>
-        </is>
-      </c>
-      <c r="F64" s="3" t="inlineStr">
-        <is>
-          <t>https://github.com/imneme/pcg-c/archive/refs/heads/master.tar.gz</t>
+          <t>https://en.wikipedia.org/wiki/Mersenne_Twister</t>
+        </is>
+      </c>
+      <c r="F64" s="7" t="inlineStr">
+        <is>
+          <t>https://github.com/stdlib-js/stdlib/archive/refs/heads/develop.zip</t>
         </is>
       </c>
       <c r="G64" s="5" t="inlineStr">
         <is>
-          <t>PCG (Permuted Congruential Generator) reference implementation</t>
+          <t>MT19937 Mersenne Twister (C++ &lt;random&gt;, Python random module)</t>
         </is>
       </c>
       <c r="H64" s="5" t="inlineStr">
         <is>
-          <t>No formal releases</t>
+          <t>Standard library built-in</t>
         </is>
       </c>
       <c r="I64" s="5" t="n"/>
       <c r="J64" s="5" t="inlineStr">
         <is>
-          <t>PCG</t>
-        </is>
-      </c>
-      <c r="K64" s="5" t="n"/>
+          <t>MT19937</t>
+        </is>
+      </c>
+      <c r="K64" s="5" t="inlineStr">
+        <is>
+          <t>Different implementations exist under different licenses; need to cover these</t>
+        </is>
+      </c>
       <c r="L64" s="5" t="inlineStr">
         <is>
           <t>No known patents.</t>
@@ -4191,50 +4247,58 @@
     <row r="65" ht="23" customHeight="1">
       <c r="A65" s="5" t="inlineStr">
         <is>
-          <t>perk</t>
+          <t>nettle-3.10.2</t>
         </is>
       </c>
       <c r="B65" s="13" t="n"/>
-      <c r="C65" s="11" t="inlineStr">
-        <is>
-          <t>UNKNOWN</t>
-        </is>
-      </c>
-      <c r="D65" s="11" t="inlineStr">
-        <is>
-          <t>UNRELEASED</t>
+      <c r="C65" s="10" t="inlineStr">
+        <is>
+          <t>LGPL-3.0-or-later OR GPL-2.0-or-later</t>
+        </is>
+      </c>
+      <c r="D65" s="3" t="inlineStr">
+        <is>
+          <t>3.10.2</t>
         </is>
       </c>
       <c r="E65" s="3" t="inlineStr">
         <is>
-          <t>https://github.com/Crypto-TII/perk-on-resource-constrained-devices</t>
-        </is>
-      </c>
-      <c r="F65" s="3" t="inlineStr">
-        <is>
-          <t>https://github.com/Crypto-TII/perk-on-resource-constrained-devices/archive/refs/heads/main.zip</t>
+          <t>https://git.lysator.liu.se/nettle/nettle</t>
+        </is>
+      </c>
+      <c r="F65" s="5" t="inlineStr">
+        <is>
+          <t>https://ftp.gnu.org/gnu/nettle/nettle-3.10.2.tar.gz</t>
         </is>
       </c>
       <c r="G65" s="5" t="inlineStr">
         <is>
-          <t>PERK — Permuted Kernels signature</t>
+          <t>Nettle — low-level crypto library (C) used by GnuTLS; AES, ChaCha20, SHA-3; no PQC</t>
         </is>
       </c>
       <c r="H65" s="5" t="inlineStr">
         <is>
-          <t>Round 2 submission update (2025); no semantic tag</t>
-        </is>
-      </c>
-      <c r="I65" s="5" t="n"/>
+          <t>nettle-3.10.2 (2025-06-26)</t>
+        </is>
+      </c>
+      <c r="I65" s="5" t="inlineStr">
+        <is>
+          <t>previous</t>
+        </is>
+      </c>
       <c r="J65" s="5" t="inlineStr">
         <is>
-          <t>PERK-*</t>
-        </is>
-      </c>
-      <c r="K65" s="5" t="n"/>
+          <t>AES-[128|192|256]-[GCM|CBC|CTR|CCM], ChaCha20-Poly1305, SHA-[256|384|512], SHA3-[256|384|512], HMAC-[SHA-256|SHA-384|SHA-512], ECDH-[P-256|P-384|P-521], ECDH-[Curve25519|X25519], ECDSA-[P-256|P-384|P-521]-*, EdDSA-Ed25519, RSASSA-PSS-[2048|3072|4096]-*, RSAES-OAEP-[2048|3072|4096]-*</t>
+        </is>
+      </c>
+      <c r="K65" s="5" t="inlineStr">
+        <is>
+          <t>Previous major line.</t>
+        </is>
+      </c>
       <c r="L65" s="5" t="inlineStr">
         <is>
-          <t>No known patents (NIST Round 2 submission requirement: patent-free).</t>
+          <t>RSA: expired 2000; DH: expired 1997; ECC: Certicom/BlackBerry largely expired 2017–2022; AES, ChaCha20, SHA, HMAC: no known patents. LGPL-3.0-or-later OR GPL-2.0-or-later.</t>
         </is>
       </c>
       <c r="M65" s="2" t="inlineStr">
@@ -4246,54 +4310,58 @@
     <row r="66" ht="23" customHeight="1">
       <c r="A66" s="5" t="inlineStr">
         <is>
-          <t>pqclean</t>
-        </is>
-      </c>
-      <c r="B66" s="13" t="n"/>
+          <t>nettle-4.0.0</t>
+        </is>
+      </c>
+      <c r="B66" s="13" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="C66" s="3" t="inlineStr">
         <is>
-          <t>CC0-1.0 (per-impl LICENSE files vary)</t>
-        </is>
-      </c>
-      <c r="D66" s="11" t="inlineStr">
-        <is>
-          <t>UNRELEASED</t>
+          <t>LGPL-3.0-or-later OR GPL-2.0-or-later</t>
+        </is>
+      </c>
+      <c r="D66" s="3" t="inlineStr">
+        <is>
+          <t>4.0.0</t>
         </is>
       </c>
       <c r="E66" s="3" t="inlineStr">
         <is>
-          <t>https://github.com/PQClean/PQClean</t>
+          <t>https://git.lysator.liu.se/nettle/nettle</t>
         </is>
       </c>
       <c r="F66" s="3" t="inlineStr">
         <is>
-          <t>https://github.com/PQClean/PQClean/archive/refs/heads/master.tar.gz</t>
+          <t>https://ftp.gnu.org/gnu/nettle/nettle-4.0.tar.gz</t>
         </is>
       </c>
       <c r="G66" s="5" t="inlineStr">
         <is>
-          <t>PQClean — clean portable C implementations ⚠ RETIRED January 2026</t>
+          <t>Nettle — low-level crypto library (C) used by GnuTLS; AES, ChaCha20, SHA-3; no PQC</t>
         </is>
       </c>
       <c r="H66" s="5" t="inlineStr">
         <is>
-          <t>RETIRED — last active 2019–2025</t>
+          <t>4.0.0</t>
         </is>
       </c>
       <c r="I66" s="5" t="inlineStr">
         <is>
-          <t>retired</t>
+          <t>stable</t>
         </is>
       </c>
       <c r="J66" s="5" t="inlineStr">
         <is>
-          <t>ML-KEM-[512|768|1024], ML-DSA-[44|65|87]-*, SLH-DSA-*, FN-DSA-[512|1024]</t>
+          <t>AES-[128|192|256]-[GCM|CBC|CTR|CCM], ChaCha20-Poly1305, SHA-[256|384|512], SHA3-[256|384|512], HMAC-[SHA-256|SHA-384|SHA-512], ECDH-[P-256|P-384|P-521], ECDH-[Curve25519|X25519], ECDSA-[P-256|P-384|P-521]-*, EdDSA-Ed25519, RSASSA-PSS-[2048|3072|4096]-*, RSAES-OAEP-[2048|3072|4096]-*</t>
         </is>
       </c>
       <c r="K66" s="5" t="n"/>
       <c r="L66" s="5" t="inlineStr">
         <is>
-          <t>ML-KEM: NIST patent licenses secured; FN-DSA: NTRU patents placed in public domain (Security Innovation, 2017). No library-level patents.</t>
+          <t>RSA: expired 2000; DH: expired 1997; ECC: Certicom/BlackBerry largely expired 2017–2022; AES, ChaCha20, SHA, HMAC: no known patents. LGPL-3.0-or-later OR GPL-2.0-or-later.</t>
         </is>
       </c>
       <c r="M66" s="2" t="inlineStr">
@@ -4305,50 +4373,58 @@
     <row r="67" ht="23" customHeight="1">
       <c r="A67" s="5" t="inlineStr">
         <is>
-          <t>pqm4</t>
-        </is>
-      </c>
-      <c r="B67" s="13" t="n"/>
+          <t>nss-3.125</t>
+        </is>
+      </c>
+      <c r="B67" s="13" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="C67" s="3" t="inlineStr">
         <is>
-          <t>CC0-1.0 (per-impl licenses vary)</t>
-        </is>
-      </c>
-      <c r="D67" s="11" t="inlineStr">
-        <is>
-          <t>UNRELEASED</t>
+          <t>MPL-2.0</t>
+        </is>
+      </c>
+      <c r="D67" s="3" t="inlineStr">
+        <is>
+          <t>3.125</t>
         </is>
       </c>
       <c r="E67" s="3" t="inlineStr">
         <is>
-          <t>https://github.com/mupq/pqm4</t>
+          <t>https://github.com/nss-dev/nss</t>
         </is>
       </c>
       <c r="F67" s="3" t="inlineStr">
         <is>
-          <t>https://github.com/mupq/pqm4/archive/refs/tags/SignatureRound1.zip</t>
+          <t>https://github.com/nss-dev/nss/archive/refs/tags/NSS_3_125_RTM.tar.gz</t>
         </is>
       </c>
       <c r="G67" s="5" t="inlineStr">
         <is>
-          <t>pqm4 — ARM Cortex-M4 PQC benchmarking framework</t>
+          <t>Mozilla NSS — TLS/crypto library (C); ML-KEM, ML-DSA; used by Firefox, many Linux distributions</t>
         </is>
       </c>
       <c r="H67" s="5" t="inlineStr">
         <is>
-          <t>No formal releases — rolling</t>
-        </is>
-      </c>
-      <c r="I67" s="5" t="n"/>
+          <t>NSS_3_125_RTM (2026-06-11)</t>
+        </is>
+      </c>
+      <c r="I67" s="5" t="inlineStr">
+        <is>
+          <t>stable</t>
+        </is>
+      </c>
       <c r="J67" s="5" t="inlineStr">
         <is>
-          <t>ML-KEM-[512|768|1024], ML-DSA-[44|65|87]-*, SLH-DSA-*, FN-DSA-[512|1024]</t>
+          <t>AES-[128|192|256]-[GCM|CCM|CBC|CTR], ChaCha20-Poly1305, SHA-[256|384|512], SHA3-[256|384|512], HMAC-[SHA-256|SHA-384|SHA-512], AES-[128|192|256]-CMAC, RSAES-OAEP-[2048|3072|4096]-*, ECDH-[P-256|P-384|P-521], ECDH-[Curve25519|X25519], ECDSA-[P-256|P-384|P-521]-*, EdDSA-[Ed25519|Ed448], RSASSA-PSS-[2048|3072|4096]-*, HKDF-[SHA-256|SHA-384|SHA-512], PBKDF2-HMAC-[SHA-256|SHA-384|SHA-512]-*, ML-KEM-[512|768|1024], ML-DSA-[44|65|87]-*</t>
         </is>
       </c>
       <c r="K67" s="5" t="n"/>
       <c r="L67" s="5" t="inlineStr">
         <is>
-          <t>Benchmarking framework; inherits algorithm patent status. No framework-level patents.</t>
+          <t>RSA: expired 2000; DH: expired 1997; ECC: Certicom/BlackBerry largely expired 2017–2022; ML-KEM: NIST patent licenses secured; ML-DSA: no known patents; AES, ChaCha20, SHA, HMAC: no known patents. MPL-2.0 includes patent grant.</t>
         </is>
       </c>
       <c r="M67" s="2" t="inlineStr">
@@ -4360,50 +4436,58 @@
     <row r="68" ht="23" customHeight="1">
       <c r="A68" s="5" t="inlineStr">
         <is>
-          <t>pqov</t>
+          <t>opaque-ke-3.0.0</t>
         </is>
       </c>
       <c r="B68" s="13" t="n"/>
-      <c r="C68" s="3" t="inlineStr">
-        <is>
-          <t>CC0-1.0</t>
-        </is>
-      </c>
-      <c r="D68" s="11" t="inlineStr">
-        <is>
-          <t>UNRELEASED</t>
+      <c r="C68" s="10" t="inlineStr">
+        <is>
+          <t>MIT</t>
+        </is>
+      </c>
+      <c r="D68" s="3" t="inlineStr">
+        <is>
+          <t>3.0.0</t>
         </is>
       </c>
       <c r="E68" s="3" t="inlineStr">
         <is>
-          <t>https://github.com/pqov/pqov</t>
-        </is>
-      </c>
-      <c r="F68" s="3" t="inlineStr">
-        <is>
-          <t>https://github.com/pqov/pqov/archive/refs/heads/main.tar.gz</t>
+          <t>https://github.com/facebook/opaque-ke</t>
+        </is>
+      </c>
+      <c r="F68" s="5" t="inlineStr">
+        <is>
+          <t>https://github.com/facebook/opaque-ke/archive/refs/tags/v3.0.0.zip</t>
         </is>
       </c>
       <c r="G68" s="5" t="inlineStr">
         <is>
-          <t>UOV / pqov — official C reference (Unbalanced Oil and Vinegar)</t>
+          <t>opaque-ke — Rust OPAQUE-3DH implementation (Meta; IETF draft-irtf-cfrg-opaque)</t>
         </is>
       </c>
       <c r="H68" s="5" t="inlineStr">
         <is>
-          <t>Round 2 submission update (Jan 2025); no semantic tag</t>
-        </is>
-      </c>
-      <c r="I68" s="5" t="n"/>
+          <t>v3.0.0 (2023-10-10)</t>
+        </is>
+      </c>
+      <c r="I68" s="5" t="inlineStr">
+        <is>
+          <t>previous</t>
+        </is>
+      </c>
       <c r="J68" s="5" t="inlineStr">
         <is>
-          <t>UOV-*</t>
-        </is>
-      </c>
-      <c r="K68" s="5" t="n"/>
+          <t>OPAQUE-3DH-*</t>
+        </is>
+      </c>
+      <c r="K68" s="5" t="inlineStr">
+        <is>
+          <t>Previous major line.</t>
+        </is>
+      </c>
       <c r="L68" s="5" t="inlineStr">
         <is>
-          <t>No known patents (NIST Round 2 submission requirement: patent-free).</t>
+          <t>No known patents.</t>
         </is>
       </c>
       <c r="M68" s="2" t="inlineStr">
@@ -4415,44 +4499,48 @@
     <row r="69" ht="23" customHeight="1">
       <c r="A69" s="5" t="inlineStr">
         <is>
-          <t>pyascon</t>
-        </is>
-      </c>
-      <c r="B69" s="13" t="n"/>
+          <t>opaque-ke-4.0.1</t>
+        </is>
+      </c>
+      <c r="B69" s="13" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="C69" s="3" t="inlineStr">
         <is>
           <t>MIT</t>
         </is>
       </c>
-      <c r="D69" s="11" t="inlineStr">
-        <is>
-          <t>UNRELEASED</t>
+      <c r="D69" s="3" t="inlineStr">
+        <is>
+          <t>4.0.1</t>
         </is>
       </c>
       <c r="E69" s="3" t="inlineStr">
         <is>
-          <t>https://github.com/meichlseder/pyascon</t>
+          <t>https://github.com/facebook/opaque-ke</t>
         </is>
       </c>
       <c r="F69" s="3" t="inlineStr">
         <is>
-          <t>https://github.com/meichlseder/pyascon/archive/refs/heads/master.zip</t>
+          <t>https://github.com/facebook/opaque-ke/archive/refs/tags/v4.0.1.zip</t>
         </is>
       </c>
       <c r="G69" s="5" t="inlineStr">
         <is>
-          <t>Ascon Python reference implementation (Eichlseder et al.; NIST SP 800-232 test vectors)</t>
-        </is>
-      </c>
-      <c r="H69" s="5" t="inlineStr">
-        <is>
-          <t>No formal releases — rolling commits</t>
-        </is>
-      </c>
-      <c r="I69" s="5" t="n"/>
+          <t>opaque-ke — Rust OPAQUE-3DH implementation (Meta; IETF draft-irtf-cfrg-opaque)</t>
+        </is>
+      </c>
+      <c r="H69" s="5" t="n"/>
+      <c r="I69" s="5" t="inlineStr">
+        <is>
+          <t>stable</t>
+        </is>
+      </c>
       <c r="J69" s="5" t="inlineStr">
         <is>
-          <t>Ascon-AEAD128, Ascon-Hash256, Ascon-XOF128, Ascon-CXOF128</t>
+          <t>OPAQUE-3DH-*</t>
         </is>
       </c>
       <c r="K69" s="5" t="n"/>
@@ -4470,7 +4558,7 @@
     <row r="70" ht="23" customHeight="1">
       <c r="A70" s="5" t="inlineStr">
         <is>
-          <t>pyca-cryptography-46.0.7</t>
+          <t>open5gs-2.7.7</t>
         </is>
       </c>
       <c r="B70" s="13" t="inlineStr">
@@ -4480,30 +4568,34 @@
       </c>
       <c r="C70" s="3" t="inlineStr">
         <is>
-          <t>Apache-2.0 OR BSD-3-Clause</t>
+          <t>AGPL-3.0-only</t>
         </is>
       </c>
       <c r="D70" s="3" t="inlineStr">
         <is>
-          <t>46.0.7</t>
+          <t>2.7.7</t>
         </is>
       </c>
       <c r="E70" s="3" t="inlineStr">
         <is>
-          <t>https://github.com/pyca/cryptography</t>
+          <t>https://github.com/open5gs/open5gs</t>
         </is>
       </c>
       <c r="F70" s="3" t="inlineStr">
         <is>
-          <t>https://github.com/pyca/cryptography/archive/refs/tags/46.0.7.tar.gz</t>
+          <t>https://github.com/open5gs/open5gs/archive/refs/tags/v2.7.7.tar.gz</t>
         </is>
       </c>
       <c r="G70" s="5" t="inlineStr">
         <is>
-          <t>pyca/cryptography — Python crypto library (OpenSSL backend); PQC via OpenSSL 3.5+ backend (ML-KEM, ML-DSA)</t>
-        </is>
-      </c>
-      <c r="H70" s="5" t="n"/>
+          <t>Open5GS — open-source 5G/4G core network (C); MILENAGE, TUAK, 128-EEA1/3, 128-EIA1/3</t>
+        </is>
+      </c>
+      <c r="H70" s="5" t="inlineStr">
+        <is>
+          <t>v2.7.6 — 2025; 5G SA core with full 3GPP AKA authentication support</t>
+        </is>
+      </c>
       <c r="I70" s="5" t="inlineStr">
         <is>
           <t>stable</t>
@@ -4511,13 +4603,13 @@
       </c>
       <c r="J70" s="5" t="inlineStr">
         <is>
-          <t>AES-[128|192|256]-[GCM|CCM|GCM-SIV|CBC|CTR|OFB|CFB128|XTS|KW], ChaCha20-Poly1305, SHA-[256|384|512], SHA3-[256|384|512], SHAKE128, SHAKE256, HMAC-[SHA-256|SHA-384|SHA-512], AES-[128|192|256]-CMAC, RSAES-OAEP-[2048|3072|4096]-*, ECDH-[P-256|P-384|P-521], ECDH-[Curve25519|X25519], ECDH-[Curve448|X448], ECDSA-[P-256|P-384|P-521]-*, EdDSA-[Ed25519|Ed448], RSASSA-PSS-[2048|3072|4096]-*, HKDF-[SHA-256|SHA-384|SHA-512], PBKDF2-HMAC-[SHA-256|SHA-384|SHA-512]-*, ML-KEM-[512|768|1024], ML-DSA-[44|65|87]-*, SLH-DSA-*</t>
+          <t>MILENAGE, TUAK, 128-EEA1, 128-EEA3, 128-EIA1, 128-EIA3, SNOW-3G, KASUMI, f8</t>
         </is>
       </c>
       <c r="K70" s="5" t="n"/>
       <c r="L70" s="5" t="inlineStr">
         <is>
-          <t>Delegates to OpenSSL backend; inherits OpenSSL algorithm patent status. RSA: expired 2000; ECC: largely expired; ML-KEM: NIST licenses secured; AES, ChaCha20, SHA: no known patents. Apache-2.0 OR BSD-3-Clause.</t>
+          <t>No known patents on MILENAGE/TUAK implementations. TUAK uses Keccak; Keccak patent-free.</t>
         </is>
       </c>
       <c r="M70" s="2" t="inlineStr">
@@ -4529,60 +4621,50 @@
     <row r="71" ht="23" customHeight="1">
       <c r="A71" s="5" t="inlineStr">
         <is>
-          <t>pycryptodome-3.23.0</t>
-        </is>
-      </c>
-      <c r="B71" s="13" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
+          <t>openjdk-17</t>
+        </is>
+      </c>
+      <c r="B71" s="13" t="n"/>
       <c r="C71" s="3" t="inlineStr">
         <is>
-          <t>BSD-2-Clause</t>
-        </is>
-      </c>
-      <c r="D71" s="3" t="inlineStr">
-        <is>
-          <t>3.23.0</t>
-        </is>
+          <t>GPL-2.0-only WITH Classpath-exception-2.0</t>
+        </is>
+      </c>
+      <c r="D71" s="3" t="n">
+        <v>17</v>
       </c>
       <c r="E71" s="3" t="inlineStr">
         <is>
-          <t>https://github.com/Legrandin/pycryptodome</t>
+          <t>https://github.com/openjdk/jdk</t>
         </is>
       </c>
       <c r="F71" s="3" t="inlineStr">
         <is>
-          <t>https://github.com/Legrandin/pycryptodome/archive/refs/tags/v3.23.0.tar.gz</t>
+          <t>https://github.com/openjdk/jdk/archive/refs/tags/jdk-17+35.zip</t>
         </is>
       </c>
       <c r="G71" s="5" t="inlineStr">
         <is>
-          <t>PyCryptodome — Python crypto library; classical algorithms only (AES, RSA, ECC, etc.); no PQC</t>
+          <t>OpenJDK — JCA/JCE crypto framework (Java); ML-KEM/ML-DSA APIs in incubating preview in JDK 25; HPKE API not yet GA</t>
         </is>
       </c>
       <c r="H71" s="5" t="inlineStr">
         <is>
-          <t>v3.23.0 (2025-05-17)</t>
+          <t>LTS</t>
         </is>
       </c>
       <c r="I71" s="5" t="inlineStr">
         <is>
-          <t>stable</t>
+          <t>lts</t>
         </is>
       </c>
       <c r="J71" s="5" t="inlineStr">
         <is>
-          <t>AES-[128|192|256]-[GCM|CCM|GCM-SIV|CBC|CTR|OFB|CFB128|XTS|ECB], ChaCha20-*, SHA-[256|384|512], SHA3-[256|384|512], HMAC-[SHA-256|SHA-384|SHA-512], AES-[128|192|256]-CMAC, RSAES-OAEP-[2048|3072|4096]-*, ECDH-[P-256|P-384|P-521], ECDSA-[P-256|P-384|P-521]-*, RSASSA-PSS-[2048|3072|4096]-*, HKDF-[SHA-256|SHA-384|SHA-512], PBKDF2-HMAC-[SHA-256|SHA-384|SHA-512]-*, bcrypt-*, scrypt-*</t>
+          <t>AES-[128|192|256]-*, SHA-[1|224|256|384|512], SHA3-*, HMAC-*, ECDSA-*, EdDSA-Ed25519, EdDSA-Ed448, RSASSA-PSS-*, RSASSA-PKCS1-*, RSAES-OAEP-*, ECDH-*, FFDH-*, HKDF-*, ChaCha20-Poly1305, Poly1305</t>
         </is>
       </c>
       <c r="K71" s="5" t="n"/>
-      <c r="L71" s="5" t="inlineStr">
-        <is>
-          <t>RSA: expired 2000; DH: expired 1997; ECC: Certicom/BlackBerry largely expired 2017–2022; AES, ChaCha20, SHA, HMAC: no known patents. BSD-2-Clause.</t>
-        </is>
-      </c>
+      <c r="L71" s="5" t="n"/>
       <c r="M71" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve"> </t>
@@ -4592,7 +4674,7 @@
     <row r="72" ht="23" customHeight="1">
       <c r="A72" s="5" t="inlineStr">
         <is>
-          <t>pynacl-1.6.2</t>
+          <t>openjdk-21</t>
         </is>
       </c>
       <c r="B72" s="13" t="inlineStr">
@@ -4602,50 +4684,44 @@
       </c>
       <c r="C72" s="3" t="inlineStr">
         <is>
-          <t>Apache-2.0</t>
-        </is>
-      </c>
-      <c r="D72" s="3" t="inlineStr">
-        <is>
-          <t>1.6.2</t>
-        </is>
+          <t>GPL-2.0-only WITH Classpath-exception-2.0</t>
+        </is>
+      </c>
+      <c r="D72" s="3" t="n">
+        <v>21</v>
       </c>
       <c r="E72" s="3" t="inlineStr">
         <is>
-          <t>https://github.com/pyca/pynacl</t>
+          <t>https://github.com/openjdk/jdk</t>
         </is>
       </c>
       <c r="F72" s="3" t="inlineStr">
         <is>
-          <t>https://github.com/pyca/pynacl/archive/refs/tags/1.6.2.tar.gz</t>
+          <t>https://github.com/openjdk/jdk/archive/refs/tags/jdk-21+35.zip</t>
         </is>
       </c>
       <c r="G72" s="5" t="inlineStr">
         <is>
-          <t>PyNaCl — Python libsodium bindings; X25519, Ed25519, ChaCha20-Poly1305; no PQC</t>
+          <t>OpenJDK — JCA/JCE crypto framework (Java); ML-KEM/ML-DSA APIs in incubating preview in JDK 25; HPKE API not yet GA</t>
         </is>
       </c>
       <c r="H72" s="5" t="inlineStr">
         <is>
-          <t>1.6.2</t>
+          <t>LTS</t>
         </is>
       </c>
       <c r="I72" s="5" t="inlineStr">
         <is>
-          <t>stable</t>
+          <t>lts</t>
         </is>
       </c>
       <c r="J72" s="5" t="inlineStr">
         <is>
-          <t>ECDH-[Curve25519|X25519], EdDSA-Ed25519, ChaCha20-Poly1305, HMAC-SHA-512, Argon2id-*, scrypt-*</t>
+          <t>AES-[128|192|256]-*, SHA-[1|224|256|384|512], SHA3-*, HMAC-*, ECDSA-*, EdDSA-Ed25519, EdDSA-Ed448, RSASSA-PSS-*, RSASSA-PKCS1-*, RSAES-OAEP-*, ECDH-*, FFDH-*, HKDF-*, ChaCha20-Poly1305, Poly1305</t>
         </is>
       </c>
       <c r="K72" s="5" t="n"/>
-      <c r="L72" s="5" t="inlineStr">
-        <is>
-          <t>EdDSA/Ed25519, X25519, ChaCha20-Poly1305, Argon2, scrypt: no known patents. Apache-2.0.</t>
-        </is>
-      </c>
+      <c r="L72" s="5" t="n"/>
       <c r="M72" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve"> </t>
@@ -4655,7 +4731,7 @@
     <row r="73" ht="23" customHeight="1">
       <c r="A73" s="5" t="inlineStr">
         <is>
-          <t>python-spake2-0.9.0</t>
+          <t>openjdk-27</t>
         </is>
       </c>
       <c r="B73" s="13" t="inlineStr">
@@ -4665,50 +4741,44 @@
       </c>
       <c r="C73" s="3" t="inlineStr">
         <is>
-          <t>MIT</t>
-        </is>
-      </c>
-      <c r="D73" s="3" t="inlineStr">
-        <is>
-          <t>0.9.0</t>
-        </is>
+          <t>GPL-2.0-only WITH Classpath-exception-2.0</t>
+        </is>
+      </c>
+      <c r="D73" s="3" t="n">
+        <v>27</v>
       </c>
       <c r="E73" s="3" t="inlineStr">
         <is>
-          <t>https://github.com/warner/python-spake2</t>
+          <t>https://github.com/openjdk/jdk</t>
         </is>
       </c>
       <c r="F73" s="3" t="inlineStr">
         <is>
-          <t>https://github.com/warner/python-spake2/archive/refs/tags/v0.9.zip</t>
+          <t>https://github.com/openjdk/jdk/archive/refs/tags/jdk-27+18.zip</t>
         </is>
       </c>
       <c r="G73" s="5" t="inlineStr">
         <is>
-          <t>python-spake2 — Python SPAKE2 and SPAKE2+ implementation (Warner; RFC 9382)</t>
+          <t>OpenJDK — JCA/JCE crypto framework (Java); ML-KEM/ML-DSA APIs in incubating preview in JDK 25; HPKE API not yet GA</t>
         </is>
       </c>
       <c r="H73" s="5" t="inlineStr">
         <is>
-          <t>v0.9.0 — 2022</t>
+          <t>LTS</t>
         </is>
       </c>
       <c r="I73" s="5" t="inlineStr">
         <is>
-          <t>stable</t>
+          <t>lts</t>
         </is>
       </c>
       <c r="J73" s="5" t="inlineStr">
         <is>
-          <t>SPAKE2-*, SPAKE2+-*</t>
+          <t>AES-[128|192|256]-*, SHA-[1|224|256|384|512], SHA3-*, HMAC-*, ECDSA-*, EdDSA-Ed25519, EdDSA-Ed448, RSASSA-PSS-*, RSASSA-PKCS1-*, RSAES-OAEP-*, ECDH-*, FFDH-*, HKDF-*, ChaCha20-Poly1305, Poly1305, HPKE-*, ML-KEM-[512|768|1024], ML-DSA-[44|65|87]-*</t>
         </is>
       </c>
       <c r="K73" s="5" t="n"/>
-      <c r="L73" s="5" t="inlineStr">
-        <is>
-          <t>No known patents. RFC 9382 explicitly addresses patent concerns.</t>
-        </is>
-      </c>
+      <c r="L73" s="5" t="n"/>
       <c r="M73" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve"> </t>
@@ -4718,50 +4788,54 @@
     <row r="74" ht="23" customHeight="1">
       <c r="A74" s="5" t="inlineStr">
         <is>
-          <t>qr-uov</t>
-        </is>
-      </c>
-      <c r="B74" s="13" t="n"/>
-      <c r="C74" s="11" t="inlineStr">
-        <is>
-          <t>UNKNOWN</t>
-        </is>
-      </c>
-      <c r="D74" s="11" t="inlineStr">
-        <is>
-          <t>UNRELEASED</t>
+          <t>openmls-0.8.1</t>
+        </is>
+      </c>
+      <c r="B74" s="13" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="C74" s="5" t="inlineStr">
+        <is>
+          <t>MIT</t>
+        </is>
+      </c>
+      <c r="D74" s="3" t="inlineStr">
+        <is>
+          <t>0.8.1</t>
         </is>
       </c>
       <c r="E74" s="3" t="inlineStr">
         <is>
-          <t>https://www.qr-uov.com/</t>
-        </is>
-      </c>
-      <c r="F74" s="3" t="inlineStr">
-        <is>
-          <t>https://github.com/qruov/round2/archive/refs/heads/main.zip</t>
+          <t>https://github.com/openmls/openmls</t>
+        </is>
+      </c>
+      <c r="F74" s="5" t="inlineStr">
+        <is>
+          <t>https://github.com/openmls/openmls/archive/refs/tags/openmls-v0.8.1.zip</t>
         </is>
       </c>
       <c r="G74" s="5" t="inlineStr">
         <is>
-          <t>QR-UOV — Quotient Ring UOV</t>
+          <t>OpenMLS — Messaging Layer Security (RFC 9420) in Rust</t>
         </is>
       </c>
       <c r="H74" s="5" t="inlineStr">
         <is>
-          <t>Round 2 submission; distributed via algorithm website (no GitHub)</t>
+          <t>Stable release</t>
         </is>
       </c>
       <c r="I74" s="5" t="n"/>
       <c r="J74" s="5" t="inlineStr">
         <is>
-          <t>QR-UOV-*</t>
+          <t>MLS-*</t>
         </is>
       </c>
       <c r="K74" s="5" t="n"/>
       <c r="L74" s="5" t="inlineStr">
         <is>
-          <t>No known patents (NIST Round 2 submission requirement: patent-free).</t>
+          <t>No known patents.</t>
         </is>
       </c>
       <c r="M74" s="2" t="inlineStr">
@@ -4773,50 +4847,58 @@
     <row r="75" ht="23" customHeight="1">
       <c r="A75" s="5" t="inlineStr">
         <is>
-          <t>rustcrypto-kems</t>
+          <t>openssl-3.6.3</t>
         </is>
       </c>
       <c r="B75" s="13" t="n"/>
-      <c r="C75" s="3" t="inlineStr">
-        <is>
-          <t>Apache-2.0 OR MIT</t>
-        </is>
-      </c>
-      <c r="D75" s="11" t="inlineStr">
-        <is>
-          <t>UNRELEASED</t>
+      <c r="C75" s="10" t="inlineStr">
+        <is>
+          <t>Apache-2.0</t>
+        </is>
+      </c>
+      <c r="D75" s="3" t="inlineStr">
+        <is>
+          <t>3.6.3</t>
         </is>
       </c>
       <c r="E75" s="3" t="inlineStr">
         <is>
-          <t>https://github.com/RustCrypto/KEMs</t>
-        </is>
-      </c>
-      <c r="F75" s="3" t="inlineStr">
-        <is>
-          <t>https://github.com/RustCrypto/KEMs/archive/refs/heads/master.tar.gz</t>
+          <t>https://github.com/openssl/openssl</t>
+        </is>
+      </c>
+      <c r="F75" s="5" t="inlineStr">
+        <is>
+          <t>https://github.com/openssl/openssl/archive/refs/tags/openssl-3.6.3.tar.gz</t>
         </is>
       </c>
       <c r="G75" s="5" t="inlineStr">
         <is>
-          <t>RustCrypto/KEMs — Rust KEM implementations; ml-kem 0.2.3 (FIPS 203); per-crate crates.io releases</t>
+          <t>OpenSSL — TLS/crypto library (C); ML-KEM, ML-DSA, SLH-DSA since 3.5.0 (FIPS provider); default TLS 1.3 key-share X25519+ML-KEM-768</t>
         </is>
       </c>
       <c r="H75" s="5" t="inlineStr">
         <is>
-          <t>per-crate (crates.io); ml-kem 0.2.3</t>
-        </is>
-      </c>
-      <c r="I75" s="5" t="n"/>
+          <t>openssl-3.6.3 (2026-06-09)</t>
+        </is>
+      </c>
+      <c r="I75" s="5" t="inlineStr">
+        <is>
+          <t>previous</t>
+        </is>
+      </c>
       <c r="J75" s="5" t="inlineStr">
         <is>
-          <t>ML-KEM-[512|768|1024]</t>
-        </is>
-      </c>
-      <c r="K75" s="5" t="n"/>
+          <t>AES-[128|192|256]-[GCM|CCM|GCM-SIV|CBC|CTR|OFB|CFB128|XTS|KW], ChaCha20-Poly1305, 3DES-*, SHA-[256|384|512], SHA3-[256|384|512], SHAKE128, SHAKE256, HMAC-[SHA-256|SHA-384|SHA-512], AES-[128|192|256]-CMAC, KMAC128, KMAC256, RSAES-OAEP-[2048|3072|4096]-*, ECDH-[P-256|P-384|P-521], ECDH-[Curve25519|X25519], ECDH-[Curve448|X448], FFDH-*, ECDSA-[P-256|P-384|P-521]-[SHA-256|SHA-384|SHA-512], EdDSA-[Ed25519|Ed448], RSASSA-PSS-[2048|3072|4096]-*, RSASSA-PKCS1-[2048|3072|4096]-*, HKDF-[SHA-256|SHA-384|SHA-512], PBKDF2-HMAC-[SHA-256|SHA-384|SHA-512]-*, SP800-108-*, ML-KEM-[512|768|1024], ML-DSA-[44|65|87]-*, SLH-DSA-*, HMAC_DRBG-[SHA-256|SHA-384|SHA-512], CTR_DRBG-AES-256, MDC-2, RSAES-PKCS1-*, SSH-KDF, TLS12-PRF, TLS13-HKDF, ANSI-KDF-X9.63, SP800-56C, MGF1, GMAC</t>
+        </is>
+      </c>
+      <c r="K75" s="5" t="inlineStr">
+        <is>
+          <t>Previous major line (3.x; current LTS). PQC native since 3.5.</t>
+        </is>
+      </c>
       <c r="L75" s="5" t="inlineStr">
         <is>
-          <t>ML-KEM: NIST patent licenses secured. No known unencumbered patents. Apache-2.0 OR MIT.</t>
+          <t>RSA: US 4,405,829 expired 2000; DH: US 4,200,770 expired 1997; ECC (ECDH/ECDSA): Certicom/BlackBerry portfolio largely expired 2017–2022; AES, ChaCha20-Poly1305, SHA, HMAC: no known patents; ML-KEM: NIST patent licenses secured; FN-DSA: NTRU patents in public domain (Security Innovation, 2017). Apache-2.0 license includes patent grant.</t>
         </is>
       </c>
       <c r="M75" s="2" t="inlineStr">
@@ -4828,50 +4910,58 @@
     <row r="76" ht="23" customHeight="1">
       <c r="A76" s="5" t="inlineStr">
         <is>
-          <t>rustcrypto-traits</t>
-        </is>
-      </c>
-      <c r="B76" s="13" t="n"/>
+          <t>openssl-4.0.1</t>
+        </is>
+      </c>
+      <c r="B76" s="13" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="C76" s="3" t="inlineStr">
         <is>
-          <t>Apache-2.0 OR MIT</t>
-        </is>
-      </c>
-      <c r="D76" s="11" t="inlineStr">
-        <is>
-          <t>UNRELEASED</t>
+          <t>Apache-2.0</t>
+        </is>
+      </c>
+      <c r="D76" s="3" t="inlineStr">
+        <is>
+          <t>4.0.1</t>
         </is>
       </c>
       <c r="E76" s="3" t="inlineStr">
         <is>
-          <t>https://github.com/RustCrypto/traits</t>
+          <t>https://github.com/openssl/openssl</t>
         </is>
       </c>
       <c r="F76" s="3" t="inlineStr">
         <is>
-          <t>https://github.com/RustCrypto/traits/archive/refs/heads/master.tar.gz</t>
+          <t>https://github.com/openssl/openssl/archive/refs/tags/openssl-4.0.1.tar.gz</t>
         </is>
       </c>
       <c r="G76" s="5" t="inlineStr">
         <is>
-          <t>RustCrypto/traits — Rust crypto trait definitions; individual crates on crates.io (ml-kem 0.2.3, ml-dsa, slh-dsa via RustCrypto/KEMs and /signatures)</t>
+          <t>OpenSSL — TLS/crypto library (C); ML-KEM, ML-DSA, SLH-DSA since 3.5.0 (FIPS provider); default TLS 1.3 key-share X25519+ML-KEM-768</t>
         </is>
       </c>
       <c r="H76" s="5" t="inlineStr">
         <is>
-          <t>per-crate (crates.io)</t>
-        </is>
-      </c>
-      <c r="I76" s="5" t="n"/>
+          <t>openssl-4.0.1 (2026-06-09)</t>
+        </is>
+      </c>
+      <c r="I76" s="5" t="inlineStr">
+        <is>
+          <t>stable</t>
+        </is>
+      </c>
       <c r="J76" s="5" t="inlineStr">
         <is>
-          <t>AES-[128|192|256]-[GCM|CCM|CBC|CTR|GCM-SIV|XTS], ChaCha20-Poly1305, SHA-[256|384|512], SHA3-[256|384|512], HMAC-[SHA-256|SHA-384|SHA-512], ECDH-[P-256|P-384|P-521], ECDH-[Curve25519|X25519], EdDSA-[Ed25519|Ed448], ECDSA-[P-256|P-384|P-521]-*, HKDF-[SHA-256|SHA-384|SHA-512], ML-KEM-[512|768|1024], ML-DSA-[44|65|87]-*, SLH-DSA-*</t>
+          <t>AES-[128|192|256]-[GCM|CCM|GCM-SIV|CBC|CTR|OFB|CFB128|XTS|KW], ChaCha20-Poly1305, 3DES-*, SHA-[256|384|512], SHA3-[256|384|512], SHAKE128, SHAKE256, HMAC-[SHA-256|SHA-384|SHA-512], AES-[128|192|256]-CMAC, KMAC128, KMAC256, RSAES-OAEP-[2048|3072|4096]-*, ECDH-[P-256|P-384|P-521], ECDH-[Curve25519|X25519], ECDH-[Curve448|X448], FFDH-*, ECDSA-[P-256|P-384|P-521]-[SHA-256|SHA-384|SHA-512], EdDSA-[Ed25519|Ed448], RSASSA-PSS-[2048|3072|4096]-*, RSASSA-PKCS1-[2048|3072|4096]-*, HKDF-[SHA-256|SHA-384|SHA-512], PBKDF2-HMAC-[SHA-256|SHA-384|SHA-512]-*, SP800-108-*, ML-KEM-[512|768|1024], ML-DSA-[44|65|87]-*, SLH-DSA-*, HMAC_DRBG-[SHA-256|SHA-384|SHA-512], CTR_DRBG-AES-256, MDC-2, RSAES-PKCS1-*, SSH-KDF, TLS12-PRF, TLS13-HKDF, ANSI-KDF-X9.63, SP800-56C, MGF1, GMAC</t>
         </is>
       </c>
       <c r="K76" s="5" t="n"/>
       <c r="L76" s="5" t="inlineStr">
         <is>
-          <t>AES, ChaCha20, SHA, HMAC: no known patents; ECC: Certicom/BlackBerry largely expired; ML-KEM: NIST patent licenses secured; ML-DSA, SLH-DSA: no known patents. Apache-2.0 OR MIT.</t>
+          <t>RSA: US 4,405,829 expired 2000; DH: US 4,200,770 expired 1997; ECC (ECDH/ECDSA): Certicom/BlackBerry portfolio largely expired 2017–2022; AES, ChaCha20-Poly1305, SHA, HMAC: no known patents; ML-KEM: NIST patent licenses secured; FN-DSA: NTRU patents in public domain (Security Innovation, 2017). Apache-2.0 license includes patent grant.</t>
         </is>
       </c>
       <c r="M76" s="2" t="inlineStr">
@@ -4883,50 +4973,54 @@
     <row r="77" ht="23" customHeight="1">
       <c r="A77" s="5" t="inlineStr">
         <is>
-          <t>ryde</t>
-        </is>
-      </c>
-      <c r="B77" s="13" t="n"/>
-      <c r="C77" s="11" t="inlineStr">
-        <is>
-          <t>UNKNOWN</t>
-        </is>
-      </c>
-      <c r="D77" s="11" t="inlineStr">
-        <is>
-          <t>UNRELEASED</t>
+          <t>openssl-des-ede</t>
+        </is>
+      </c>
+      <c r="B77" s="13" t="inlineStr">
+        <is>
+          <t>(x)</t>
+        </is>
+      </c>
+      <c r="C77" s="3" t="inlineStr">
+        <is>
+          <t>Apache-2.0</t>
+        </is>
+      </c>
+      <c r="D77" s="3" t="inlineStr">
+        <is>
+          <t>4.0.1</t>
         </is>
       </c>
       <c r="E77" s="3" t="inlineStr">
         <is>
-          <t>https://pqc-ryde.org/</t>
+          <t>https://github.com/openssl/openssl</t>
         </is>
       </c>
       <c r="F77" s="3" t="inlineStr">
         <is>
-          <t>https://pqc-ryde.org/assets/downloads/ryde_v2.1.0.zip</t>
+          <t>https://github.com/openssl/openssl/archive/refs/tags/openssl-4.0.1.tar.gz</t>
         </is>
       </c>
       <c r="G77" s="5" t="inlineStr">
         <is>
-          <t>RYDE — Rank Syndrome Decoding Equivalence</t>
+          <t>OpenSSL des-ede (2TDEA / 2-key Triple DES)</t>
         </is>
       </c>
       <c r="H77" s="5" t="inlineStr">
         <is>
-          <t>Round 2 submission update (2025); no semantic tag</t>
+          <t>openssl-4.0.1 (2026-06-09)</t>
         </is>
       </c>
       <c r="I77" s="5" t="n"/>
       <c r="J77" s="5" t="inlineStr">
         <is>
-          <t>RYDE-*</t>
+          <t>2TDEA, 3DES, DES</t>
         </is>
       </c>
       <c r="K77" s="5" t="n"/>
       <c r="L77" s="5" t="inlineStr">
         <is>
-          <t>No known patents (NIST Round 2 submission requirement: patent-free).</t>
+          <t>No known patents.</t>
         </is>
       </c>
       <c r="M77" s="2" t="inlineStr">
@@ -4938,50 +5032,50 @@
     <row r="78" ht="23" customHeight="1">
       <c r="A78" s="5" t="inlineStr">
         <is>
-          <t>sdith</t>
-        </is>
-      </c>
-      <c r="B78" s="13" t="n"/>
+          <t>oqs-provider-0.11.0</t>
+        </is>
+      </c>
+      <c r="B78" s="13" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="C78" s="3" t="inlineStr">
         <is>
-          <t>CeCILL-2.1</t>
-        </is>
-      </c>
-      <c r="D78" s="11" t="inlineStr">
-        <is>
-          <t>1.1.0</t>
+          <t>MIT</t>
+        </is>
+      </c>
+      <c r="D78" s="3" t="inlineStr">
+        <is>
+          <t>0.11.0</t>
         </is>
       </c>
       <c r="E78" s="3" t="inlineStr">
         <is>
-          <t>https://github.com/sdith/sdith</t>
+          <t>https://github.com/open-quantum-safe/oqs-provider</t>
         </is>
       </c>
       <c r="F78" s="3" t="inlineStr">
         <is>
-          <t>https://github.com/sdith/sdith/archive/refs/heads/main.tar.gz</t>
+          <t>https://github.com/open-quantum-safe/oqs-provider/archive/refs/tags/0.11.0.gz</t>
         </is>
       </c>
       <c r="G78" s="5" t="inlineStr">
         <is>
-          <t>SDitH — Syndrome Decoding in the Head</t>
-        </is>
-      </c>
-      <c r="H78" s="5" t="inlineStr">
-        <is>
-          <t>v1.1.0</t>
-        </is>
-      </c>
+          <t>oqs-provider — OpenSSL 3 provider backed by liboqs (ML-KEM/DSA disabled vs. OpenSSL ≥ 3.5)</t>
+        </is>
+      </c>
+      <c r="H78" s="5" t="n"/>
       <c r="I78" s="5" t="n"/>
       <c r="J78" s="5" t="inlineStr">
         <is>
-          <t>SDitH-*</t>
+          <t>ML-KEM-[512|768|1024], ML-DSA-[44|65|87]-*, SLH-DSA-*, FN-DSA-[512|1024], HQC-[128|192|256], MAYO-*, CROSS-*, UOV-*, SNOVA-*</t>
         </is>
       </c>
       <c r="K78" s="5" t="n"/>
       <c r="L78" s="5" t="inlineStr">
         <is>
-          <t>No known patents (NIST Round 2 submission requirement: patent-free).</t>
+          <t>Inherits algorithm patent status from liboqs backend. No provider-level patents.</t>
         </is>
       </c>
       <c r="M78" s="2" t="inlineStr">
@@ -4993,13 +5087,13 @@
     <row r="79" ht="23" customHeight="1">
       <c r="A79" s="5" t="inlineStr">
         <is>
-          <t>sdith-parameters</t>
+          <t>pcg-reference</t>
         </is>
       </c>
       <c r="B79" s="13" t="n"/>
-      <c r="C79" s="11" t="inlineStr">
-        <is>
-          <t>UNKNOWN</t>
+      <c r="C79" s="3" t="inlineStr">
+        <is>
+          <t>Apache-2.0 OR MIT</t>
         </is>
       </c>
       <c r="D79" s="11" t="inlineStr">
@@ -5009,17 +5103,17 @@
       </c>
       <c r="E79" s="3" t="inlineStr">
         <is>
-          <t>https://github.com/sdith/sdith-parameters</t>
+          <t>https://www.pcg-random.org/</t>
         </is>
       </c>
       <c r="F79" s="3" t="inlineStr">
         <is>
-          <t>https://github.com/sdith/sdith-parameters/archive/refs/heads/main.zip</t>
+          <t>https://github.com/imneme/pcg-c/archive/refs/heads/master.tar.gz</t>
         </is>
       </c>
       <c r="G79" s="5" t="inlineStr">
         <is>
-          <t>https://github.com/sdith/sdith-parameters/archive/refs/heads/main.tar.gz</t>
+          <t>PCG (Permuted Congruential Generator) reference implementation</t>
         </is>
       </c>
       <c r="H79" s="5" t="inlineStr">
@@ -5030,13 +5124,13 @@
       <c r="I79" s="5" t="n"/>
       <c r="J79" s="5" t="inlineStr">
         <is>
-          <t>SDitH-*</t>
+          <t>PCG</t>
         </is>
       </c>
       <c r="K79" s="5" t="n"/>
       <c r="L79" s="5" t="inlineStr">
         <is>
-          <t>Parameter-generation scripts only. No known patents.</t>
+          <t>No known patents.</t>
         </is>
       </c>
       <c r="M79" s="2" t="inlineStr">
@@ -5048,13 +5142,13 @@
     <row r="80" ht="23" customHeight="1">
       <c r="A80" s="5" t="inlineStr">
         <is>
-          <t>slh-dsa-py</t>
+          <t>perk</t>
         </is>
       </c>
       <c r="B80" s="13" t="n"/>
-      <c r="C80" s="3" t="inlineStr">
-        <is>
-          <t>MIT</t>
+      <c r="C80" s="11" t="inlineStr">
+        <is>
+          <t>UNKNOWN</t>
         </is>
       </c>
       <c r="D80" s="11" t="inlineStr">
@@ -5064,34 +5158,34 @@
       </c>
       <c r="E80" s="3" t="inlineStr">
         <is>
-          <t>https://github.com/gmh5225/slh-dsa-py</t>
+          <t>https://github.com/Crypto-TII/perk-on-resource-constrained-devices</t>
         </is>
       </c>
       <c r="F80" s="3" t="inlineStr">
         <is>
-          <t>https://github.com/gmh5225/slh-dsa-py/archive/refs/heads/main.zip</t>
+          <t>https://github.com/Crypto-TII/perk-on-resource-constrained-devices/archive/refs/heads/main.zip</t>
         </is>
       </c>
       <c r="G80" s="5" t="inlineStr">
         <is>
-          <t>slh-dsa-py — SLH-DSA Python, Saarinen (FIPS 205 IPD test vectors)</t>
+          <t>PERK — Permuted Kernels signature</t>
         </is>
       </c>
       <c r="H80" s="5" t="inlineStr">
         <is>
-          <t>No formal releases</t>
+          <t>Round 2 submission update (2025); no semantic tag</t>
         </is>
       </c>
       <c r="I80" s="5" t="n"/>
       <c r="J80" s="5" t="inlineStr">
         <is>
-          <t>SLH-DSA-*</t>
+          <t>PERK-*</t>
         </is>
       </c>
       <c r="K80" s="5" t="n"/>
       <c r="L80" s="5" t="inlineStr">
         <is>
-          <t>No known patents (SLH-DSA is patent-free).</t>
+          <t>No known patents (NIST Round 2 submission requirement: patent-free).</t>
         </is>
       </c>
       <c r="M80" s="2" t="inlineStr">
@@ -5103,13 +5197,13 @@
     <row r="81" ht="23" customHeight="1">
       <c r="A81" s="5" t="inlineStr">
         <is>
-          <t>slhdsa-c</t>
+          <t>pqclean</t>
         </is>
       </c>
       <c r="B81" s="13" t="n"/>
       <c r="C81" s="3" t="inlineStr">
         <is>
-          <t>MIT OR Apache-2.0</t>
+          <t>CC0-1.0 (per-impl LICENSE files vary)</t>
         </is>
       </c>
       <c r="D81" s="11" t="inlineStr">
@@ -5119,34 +5213,38 @@
       </c>
       <c r="E81" s="3" t="inlineStr">
         <is>
-          <t>https://github.com/pq-code-package/slhdsa-c</t>
+          <t>https://github.com/PQClean/PQClean</t>
         </is>
       </c>
       <c r="F81" s="3" t="inlineStr">
         <is>
-          <t>https://github.com/pq-code-package/slhdsa-c/archive/refs/heads/main.tar.gz</t>
+          <t>https://github.com/PQClean/PQClean/archive/refs/heads/master.tar.gz</t>
         </is>
       </c>
       <c r="G81" s="5" t="inlineStr">
         <is>
-          <t>slhdsa-c — SLH-DSA FIPS 205, PQCP</t>
+          <t>PQClean — clean portable C implementations ⚠ RETIRED January 2026</t>
         </is>
       </c>
       <c r="H81" s="5" t="inlineStr">
         <is>
-          <t>No formal release — active dev (2026)</t>
-        </is>
-      </c>
-      <c r="I81" s="5" t="n"/>
+          <t>RETIRED — last active 2019–2025</t>
+        </is>
+      </c>
+      <c r="I81" s="5" t="inlineStr">
+        <is>
+          <t>retired</t>
+        </is>
+      </c>
       <c r="J81" s="5" t="inlineStr">
         <is>
-          <t>SLH-DSA-*, HashSLH-DSA-*</t>
+          <t>ML-KEM-[512|768|1024], ML-DSA-[44|65|87]-*, SLH-DSA-*, FN-DSA-[512|1024]</t>
         </is>
       </c>
       <c r="K81" s="5" t="n"/>
       <c r="L81" s="5" t="inlineStr">
         <is>
-          <t>No known patents.</t>
+          <t>ML-KEM: NIST patent licenses secured; FN-DSA: NTRU patents placed in public domain (Security Innovation, 2017). No library-level patents.</t>
         </is>
       </c>
       <c r="M81" s="2" t="inlineStr">
@@ -5158,13 +5256,13 @@
     <row r="82" ht="23" customHeight="1">
       <c r="A82" s="5" t="inlineStr">
         <is>
-          <t>snova</t>
+          <t>pqm4</t>
         </is>
       </c>
       <c r="B82" s="13" t="n"/>
-      <c r="C82" s="11" t="inlineStr">
-        <is>
-          <t>UNKNOWN</t>
+      <c r="C82" s="3" t="inlineStr">
+        <is>
+          <t>CC0-1.0 (per-impl licenses vary)</t>
         </is>
       </c>
       <c r="D82" s="11" t="inlineStr">
@@ -5174,34 +5272,34 @@
       </c>
       <c r="E82" s="3" t="inlineStr">
         <is>
-          <t>https://github.com/PQCLAB-SNOVA/SNOVA</t>
+          <t>https://github.com/mupq/pqm4</t>
         </is>
       </c>
       <c r="F82" s="3" t="inlineStr">
         <is>
-          <t>https://github.com/PQCLAB-SNOVA/SNOVA/archive/refs/heads/main.tar.gz</t>
+          <t>https://github.com/mupq/pqm4/archive/refs/tags/SignatureRound1.zip</t>
         </is>
       </c>
       <c r="G82" s="5" t="inlineStr">
         <is>
-          <t>SNOVA — official C reference + optimised + AVX2</t>
+          <t>pqm4 — ARM Cortex-M4 PQC benchmarking framework</t>
         </is>
       </c>
       <c r="H82" s="5" t="inlineStr">
         <is>
-          <t>Round 2 submission update (Jan 2025); no semantic tag</t>
+          <t>No formal releases — rolling</t>
         </is>
       </c>
       <c r="I82" s="5" t="n"/>
       <c r="J82" s="5" t="inlineStr">
         <is>
-          <t>SNOVA-*</t>
+          <t>ML-KEM-[512|768|1024], ML-DSA-[44|65|87]-*, SLH-DSA-*, FN-DSA-[512|1024]</t>
         </is>
       </c>
       <c r="K82" s="5" t="n"/>
       <c r="L82" s="5" t="inlineStr">
         <is>
-          <t>No known patents (NIST Round 2 submission requirement: patent-free).</t>
+          <t>Benchmarking framework; inherits algorithm patent status. No framework-level patents.</t>
         </is>
       </c>
       <c r="M82" s="2" t="inlineStr">
@@ -5213,7 +5311,7 @@
     <row r="83" ht="23" customHeight="1">
       <c r="A83" s="5" t="inlineStr">
         <is>
-          <t>sphincsplus</t>
+          <t>pqov</t>
         </is>
       </c>
       <c r="B83" s="13" t="n"/>
@@ -5229,34 +5327,34 @@
       </c>
       <c r="E83" s="3" t="inlineStr">
         <is>
-          <t>https://github.com/sphincs/sphincsplus</t>
+          <t>https://github.com/pqov/pqov</t>
         </is>
       </c>
       <c r="F83" s="3" t="inlineStr">
         <is>
-          <t>https://github.com/sphincs/sphincsplus/archive/refs/heads/master.tar.gz</t>
+          <t>https://github.com/pqov/pqov/archive/refs/heads/main.tar.gz</t>
         </is>
       </c>
       <c r="G83" s="5" t="inlineStr">
         <is>
-          <t>SPHINCS+ / SLH-DSA reference</t>
+          <t>UOV / pqov — official C reference (Unbalanced Oil and Vinegar)</t>
         </is>
       </c>
       <c r="H83" s="5" t="inlineStr">
         <is>
-          <t>No formal releases — rolling commits</t>
+          <t>Round 2 submission update (Jan 2025); no semantic tag</t>
         </is>
       </c>
       <c r="I83" s="5" t="n"/>
       <c r="J83" s="5" t="inlineStr">
         <is>
-          <t>SLH-DSA-*, HashSLH-DSA-*</t>
+          <t>UOV-*</t>
         </is>
       </c>
       <c r="K83" s="5" t="n"/>
       <c r="L83" s="5" t="inlineStr">
         <is>
-          <t>No known patents.</t>
+          <t>No known patents (NIST Round 2 submission requirement: patent-free).</t>
         </is>
       </c>
       <c r="M83" s="2" t="inlineStr">
@@ -5268,13 +5366,13 @@
     <row r="84" ht="23" customHeight="1">
       <c r="A84" s="5" t="inlineStr">
         <is>
-          <t>sqisign-ec23</t>
+          <t>pyascon</t>
         </is>
       </c>
       <c r="B84" s="13" t="n"/>
       <c r="C84" s="3" t="inlineStr">
         <is>
-          <t>Apache-2.0</t>
+          <t>MIT</t>
         </is>
       </c>
       <c r="D84" s="11" t="inlineStr">
@@ -5284,91 +5382,109 @@
       </c>
       <c r="E84" s="3" t="inlineStr">
         <is>
-          <t>https://github.com/SQISign/sqisign-ec23</t>
+          <t>https://github.com/meichlseder/pyascon</t>
         </is>
       </c>
       <c r="F84" s="3" t="inlineStr">
         <is>
-          <t>https://github.com/SQISign/sqisign-ec23/archive/refs/heads/main.tar.gz</t>
+          <t>https://github.com/meichlseder/pyascon/archive/refs/heads/master.zip</t>
         </is>
       </c>
       <c r="G84" s="5" t="inlineStr">
         <is>
-          <t>SQIsign ec23 — EUROCRYPT 2023 C implementation</t>
+          <t>Ascon Python reference implementation (Eichlseder et al.; NIST SP 800-232 test vectors)</t>
         </is>
       </c>
       <c r="H84" s="5" t="inlineStr">
         <is>
-          <t>No formal releases</t>
+          <t>No formal releases — rolling commits</t>
         </is>
       </c>
       <c r="I84" s="5" t="n"/>
       <c r="J84" s="5" t="inlineStr">
         <is>
-          <t>SQIsign-*</t>
+          <t>Ascon-AEAD128, Ascon-Hash256, Ascon-XOF128, Ascon-CXOF128</t>
         </is>
       </c>
       <c r="K84" s="5" t="n"/>
       <c r="L84" s="5" t="inlineStr">
         <is>
-          <t>No known patents. Isogeny-based (SQIsign variant); distinct from SIDH/SIKE (broken 2022; Microsoft patents abandoned). NIST Round 2 requirement: patent-free.</t>
+          <t>No known patents.</t>
+        </is>
+      </c>
+      <c r="M84" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
     </row>
     <row r="85" ht="23" customHeight="1">
       <c r="A85" s="5" t="inlineStr">
         <is>
-          <t>sqisign2d-west-ac24</t>
+          <t>pyca-cryptography-48.0.1</t>
         </is>
       </c>
       <c r="B85" s="13" t="n"/>
-      <c r="C85" s="3" t="inlineStr">
-        <is>
-          <t>Apache-2.0</t>
-        </is>
-      </c>
-      <c r="D85" s="11" t="inlineStr">
-        <is>
-          <t>UNRELEASED</t>
+      <c r="C85" s="10" t="inlineStr">
+        <is>
+          <t>Apache-2.0 OR BSD-3-Clause</t>
+        </is>
+      </c>
+      <c r="D85" s="3" t="inlineStr">
+        <is>
+          <t>48.0.1</t>
         </is>
       </c>
       <c r="E85" s="3" t="inlineStr">
         <is>
-          <t>https://github.com/SQISign/sqisign2d-west-ac24</t>
-        </is>
-      </c>
-      <c r="F85" s="3" t="inlineStr">
-        <is>
-          <t>https://github.com/SQISign/sqisign2d-west-ac24/archive/refs/heads/main.tar.gz</t>
+          <t>https://github.com/pyca/cryptography</t>
+        </is>
+      </c>
+      <c r="F85" s="5" t="inlineStr">
+        <is>
+          <t>https://github.com/pyca/cryptography/archive/refs/tags/48.0.1.tar.gz</t>
         </is>
       </c>
       <c r="G85" s="5" t="inlineStr">
         <is>
-          <t>SQIsign2D-West ac24 — ASIACRYPT 2024 C implementation</t>
+          <t>pyca/cryptography — Python crypto library (OpenSSL backend); PQC via OpenSSL 3.5+ backend (ML-KEM, ML-DSA)</t>
         </is>
       </c>
       <c r="H85" s="5" t="inlineStr">
         <is>
-          <t>No formal releases</t>
-        </is>
-      </c>
-      <c r="I85" s="5" t="n"/>
+          <t>48.0.1</t>
+        </is>
+      </c>
+      <c r="I85" s="5" t="inlineStr">
+        <is>
+          <t>previous</t>
+        </is>
+      </c>
       <c r="J85" s="5" t="inlineStr">
         <is>
-          <t>SQIsign2D-*</t>
-        </is>
-      </c>
-      <c r="K85" s="5" t="n"/>
+          <t>AES-[128|192|256]-[GCM|CCM|GCM-SIV|CBC|CTR|OFB|CFB128|XTS|KW], ChaCha20-Poly1305, SHA-[256|384|512], SHA3-[256|384|512], SHAKE128, SHAKE256, HMAC-[SHA-256|SHA-384|SHA-512], AES-[128|192|256]-CMAC, RSAES-OAEP-[2048|3072|4096]-*, ECDH-[P-256|P-384|P-521], ECDH-[Curve25519|X25519], ECDH-[Curve448|X448], ECDSA-[P-256|P-384|P-521]-*, EdDSA-[Ed25519|Ed448], RSASSA-PSS-[2048|3072|4096]-*, HKDF-[SHA-256|SHA-384|SHA-512], PBKDF2-HMAC-[SHA-256|SHA-384|SHA-512]-*, ML-KEM-[512|768|1024], ML-DSA-[44|65|87]-*, SLH-DSA-*</t>
+        </is>
+      </c>
+      <c r="K85" s="5" t="inlineStr">
+        <is>
+          <t>Previous major line.</t>
+        </is>
+      </c>
       <c r="L85" s="5" t="inlineStr">
         <is>
-          <t>No known patents. Isogeny-based (SQIsign2D); distinct from SIDH/SIKE. NIST Round 2 requirement: patent-free.</t>
+          <t>Delegates to OpenSSL backend; inherits OpenSSL algorithm patent status. RSA: expired 2000; ECC: largely expired; ML-KEM: NIST licenses secured; AES, ChaCha20, SHA: no known patents. Apache-2.0 OR BSD-3-Clause.</t>
+        </is>
+      </c>
+      <c r="M85" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
     </row>
     <row r="86" ht="23" customHeight="1">
       <c r="A86" s="5" t="inlineStr">
         <is>
-          <t>tink-go-2.6.0</t>
+          <t>pyca-cryptography-49.0.0</t>
         </is>
       </c>
       <c r="B86" s="13" t="inlineStr">
@@ -5378,32 +5494,32 @@
       </c>
       <c r="C86" s="3" t="inlineStr">
         <is>
-          <t>Apache-2.0</t>
+          <t>Apache-2.0 OR BSD-3-Clause</t>
         </is>
       </c>
       <c r="D86" s="3" t="inlineStr">
         <is>
-          <t>2.6.0</t>
+          <t>49.0.0</t>
         </is>
       </c>
       <c r="E86" s="3" t="inlineStr">
         <is>
-          <t>https://github.com/tink-crypto/tink-go</t>
+          <t>https://github.com/pyca/cryptography</t>
         </is>
       </c>
       <c r="F86" s="3" t="inlineStr">
         <is>
-          <t>https://github.com/tink-crypto/tink-go/archive/refs/tags/v2.6.0.tar.gz</t>
+          <t>https://github.com/pyca/cryptography/archive/refs/tags/49.0.0.tar.gz</t>
         </is>
       </c>
       <c r="G86" s="5" t="inlineStr">
         <is>
-          <t>Google Tink Go — opinionated crypto API (Go); ML-KEM-768/1024, ML-DSA-87</t>
+          <t>pyca/cryptography — Python crypto library (OpenSSL backend); PQC via OpenSSL 3.5+ backend (ML-KEM, ML-DSA)</t>
         </is>
       </c>
       <c r="H86" s="5" t="inlineStr">
         <is>
-          <t>v2.6.0</t>
+          <t>49.0.0 (2026-06-12)</t>
         </is>
       </c>
       <c r="I86" s="5" t="inlineStr">
@@ -5413,20 +5529,25 @@
       </c>
       <c r="J86" s="5" t="inlineStr">
         <is>
-          <t>AES-[128|256]-GCM, ChaCha20-Poly1305, HMAC-[SHA-256|SHA-512], ECDH-[P-256|P-384], ECDH-[Curve25519|X25519], ECDSA-[P-256|P-384|P-521]-[SHA-256|SHA-384|SHA-512], EdDSA-Ed25519, RSASSA-PSS-[2048|3072|4096]-*, HKDF-[SHA-256|SHA-384|SHA-512], ML-KEM-[768|1024], ML-DSA-87</t>
+          <t>AES-[128|192|256]-[GCM|CCM|GCM-SIV|CBC|CTR|OFB|CFB128|XTS|KW], ChaCha20-Poly1305, SHA-[256|384|512], SHA3-[256|384|512], SHAKE128, SHAKE256, HMAC-[SHA-256|SHA-384|SHA-512], AES-[128|192|256]-CMAC, RSAES-OAEP-[2048|3072|4096]-*, ECDH-[P-256|P-384|P-521], ECDH-[Curve25519|X25519], ECDH-[Curve448|X448], ECDSA-[P-256|P-384|P-521]-*, EdDSA-[Ed25519|Ed448], RSASSA-PSS-[2048|3072|4096]-*, HKDF-[SHA-256|SHA-384|SHA-512], PBKDF2-HMAC-[SHA-256|SHA-384|SHA-512]-*, ML-KEM-[512|768|1024], ML-DSA-[44|65|87]-*, SLH-DSA-*</t>
         </is>
       </c>
       <c r="K86" s="5" t="n"/>
       <c r="L86" s="5" t="inlineStr">
         <is>
-          <t>AES, ChaCha20-Poly1305, HMAC: no known patents; ECC: Certicom/BlackBerry largely expired; ML-KEM: NIST patent licenses secured; ML-DSA: no known patents. Apache-2.0 license includes patent grant.</t>
+          <t>Delegates to OpenSSL backend; inherits OpenSSL algorithm patent status. RSA: expired 2000; ECC: largely expired; ML-KEM: NIST licenses secured; AES, ChaCha20, SHA: no known patents. Apache-2.0 OR BSD-3-Clause.</t>
+        </is>
+      </c>
+      <c r="M86" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
     </row>
     <row r="87" ht="23" customHeight="1">
       <c r="A87" s="5" t="inlineStr">
         <is>
-          <t>tink-java-1.21.0</t>
+          <t>pycryptodome-3.23.0</t>
         </is>
       </c>
       <c r="B87" s="13" t="inlineStr">
@@ -5436,32 +5557,32 @@
       </c>
       <c r="C87" s="3" t="inlineStr">
         <is>
-          <t>Apache-2.0</t>
+          <t>BSD-2-Clause</t>
         </is>
       </c>
       <c r="D87" s="3" t="inlineStr">
         <is>
-          <t>1.21.0</t>
+          <t>3.23.0</t>
         </is>
       </c>
       <c r="E87" s="3" t="inlineStr">
         <is>
-          <t>https://github.com/tink-crypto/tink-java</t>
+          <t>https://github.com/Legrandin/pycryptodome</t>
         </is>
       </c>
       <c r="F87" s="3" t="inlineStr">
         <is>
-          <t>https://github.com/tink-crypto/tink-java/archive/refs/tags/v1.21.0.tar.gz</t>
+          <t>https://github.com/Legrandin/pycryptodome/archive/refs/tags/v3.23.0.tar.gz</t>
         </is>
       </c>
       <c r="G87" s="5" t="inlineStr">
         <is>
-          <t>Google Tink Java — opinionated crypto API (Java); ML-DSA-87, ML-KEM, hybrid KEM (DHKEM+ML-KEM)</t>
+          <t>PyCryptodome — Python crypto library; classical algorithms only (AES, RSA, ECC, etc.); no PQC</t>
         </is>
       </c>
       <c r="H87" s="5" t="inlineStr">
         <is>
-          <t>v1.21.0 (2025-03-24)</t>
+          <t>v3.23.0 (2025-05-17)</t>
         </is>
       </c>
       <c r="I87" s="5" t="inlineStr">
@@ -5471,20 +5592,25 @@
       </c>
       <c r="J87" s="5" t="inlineStr">
         <is>
-          <t>AES-[128|256]-GCM, AES-[128|256]-CTR, ChaCha20-Poly1305, HMAC-[SHA-256|SHA-512], ECDH-[P-256|P-384|P-521], ECDH-[Curve25519|X25519], ECDSA-[P-256|P-384|P-521]-[SHA-256|SHA-384|SHA-512], EdDSA-[Ed25519|Ed448], RSASSA-PSS-[2048|3072|4096]-*, HKDF-[SHA-256|SHA-384|SHA-512], ML-KEM-[768|1024], ML-DSA-87</t>
+          <t>AES-[128|192|256]-[GCM|CCM|GCM-SIV|CBC|CTR|OFB|CFB128|XTS|ECB], ChaCha20-*, SHA-[256|384|512], SHA3-[256|384|512], HMAC-[SHA-256|SHA-384|SHA-512], AES-[128|192|256]-CMAC, RSAES-OAEP-[2048|3072|4096]-*, ECDH-[P-256|P-384|P-521], ECDSA-[P-256|P-384|P-521]-*, RSASSA-PSS-[2048|3072|4096]-*, HKDF-[SHA-256|SHA-384|SHA-512], PBKDF2-HMAC-[SHA-256|SHA-384|SHA-512]-*, bcrypt-*, scrypt-*</t>
         </is>
       </c>
       <c r="K87" s="5" t="n"/>
       <c r="L87" s="5" t="inlineStr">
         <is>
-          <t>AES, ChaCha20-Poly1305, HMAC: no known patents; ECC: Certicom/BlackBerry largely expired; ML-KEM: NIST patent licenses secured; ML-DSA: no known patents. Apache-2.0 license includes patent grant.</t>
+          <t>RSA: expired 2000; DH: expired 1997; ECC: Certicom/BlackBerry largely expired 2017–2022; AES, ChaCha20, SHA, HMAC: no known patents. BSD-2-Clause.</t>
+        </is>
+      </c>
+      <c r="M87" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
     </row>
     <row r="88" ht="23" customHeight="1">
       <c r="A88" s="5" t="inlineStr">
         <is>
-          <t>wolfssl-5.9.1</t>
+          <t>pynacl-1.6.2</t>
         </is>
       </c>
       <c r="B88" s="13" t="inlineStr">
@@ -5492,34 +5618,34 @@
           <t>x</t>
         </is>
       </c>
-      <c r="C88" s="9" t="inlineStr">
-        <is>
-          <t>GPL-2.0-only</t>
+      <c r="C88" s="3" t="inlineStr">
+        <is>
+          <t>Apache-2.0</t>
         </is>
       </c>
       <c r="D88" s="3" t="inlineStr">
         <is>
-          <t>5.9.1</t>
+          <t>1.6.2</t>
         </is>
       </c>
       <c r="E88" s="3" t="inlineStr">
         <is>
-          <t>https://github.com/wolfSSL/wolfssl</t>
-        </is>
-      </c>
-      <c r="F88" s="6" t="inlineStr">
-        <is>
-          <t>https://github.com/wolfSSL/wolfssl/archive/refs/tags/v5.9.1-stable.tar.gz</t>
+          <t>https://github.com/pyca/pynacl</t>
+        </is>
+      </c>
+      <c r="F88" s="3" t="inlineStr">
+        <is>
+          <t>https://github.com/pyca/pynacl/archive/refs/tags/1.6.2.tar.gz</t>
         </is>
       </c>
       <c r="G88" s="5" t="inlineStr">
         <is>
-          <t>wolfSSL — embedded TLS/crypto (C); ML-KEM, ML-DSA, SLH-DSA (FIPS 203/204/205); CNSA 2.0 compliant</t>
+          <t>PyNaCl — Python libsodium bindings; X25519, Ed25519, ChaCha20-Poly1305; no PQC</t>
         </is>
       </c>
       <c r="H88" s="5" t="inlineStr">
         <is>
-          <t>v5.9.0-stable</t>
+          <t>1.6.2</t>
         </is>
       </c>
       <c r="I88" s="5" t="inlineStr">
@@ -5529,80 +5655,94 @@
       </c>
       <c r="J88" s="5" t="inlineStr">
         <is>
-          <t>AES-[128|192|256]-[GCM|CCM|CBC|CTR|OFB|CFB128|XTS], ChaCha20-Poly1305, SHA-[256|384|512], SHA3-[256|384|512], HMAC-[SHA-256|SHA-384|SHA-512], AES-[128|192|256]-CMAC, RSAES-OAEP-[2048|3072|4096]-*, ECDH-[P-256|P-384|P-521], ECDH-[Curve25519|X25519], ECDH-[Curve448|X448], ECDSA-[P-256|P-384|P-521]-*, EdDSA-[Ed25519|Ed448], RSASSA-PSS-[2048|3072|4096]-*, HKDF-[SHA-256|SHA-384|SHA-512], PBKDF2-HMAC-[SHA-256|SHA-384|SHA-512]-*, ML-KEM-[512|768|1024], ML-DSA-[44|65|87]-*, SLH-DSA-*, HMAC_DRBG-[SHA-256|SHA-384|SHA-512], CTR_DRBG-AES-[128|192|256]</t>
-        </is>
-      </c>
-      <c r="K88" s="5" t="inlineStr">
-        <is>
-          <t>GPL-3 or for some combinations GPL-2 or Commercial</t>
-        </is>
-      </c>
+          <t>ECDH-[Curve25519|X25519], EdDSA-Ed25519, ChaCha20-Poly1305, HMAC-SHA-512, Argon2id-*, scrypt-*</t>
+        </is>
+      </c>
+      <c r="K88" s="5" t="n"/>
       <c r="L88" s="5" t="inlineStr">
         <is>
-          <t>RSA: expired 2000; DH: expired 1997; ECC: Certicom/BlackBerry largely expired 2017–2022; ML-KEM: NIST patent licenses secured; ML-DSA, SLH-DSA: no known patents; AES, ChaCha20, SHA, HMAC: no known patents. GPL-2.0-only.</t>
+          <t>EdDSA/Ed25519, X25519, ChaCha20-Poly1305, Argon2, scrypt: no known patents. Apache-2.0.</t>
+        </is>
+      </c>
+      <c r="M88" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
     </row>
     <row r="89" ht="23" customHeight="1">
       <c r="A89" s="5" t="inlineStr">
         <is>
-          <t>xkcp</t>
-        </is>
-      </c>
-      <c r="B89" s="13" t="n"/>
+          <t>python-spake2-0.9.0</t>
+        </is>
+      </c>
+      <c r="B89" s="13" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="C89" s="3" t="inlineStr">
         <is>
-          <t>CC0-1.0 OR Apache-2.0</t>
-        </is>
-      </c>
-      <c r="D89" s="11" t="inlineStr">
-        <is>
-          <t>UNRELEASED</t>
+          <t>MIT</t>
+        </is>
+      </c>
+      <c r="D89" s="3" t="inlineStr">
+        <is>
+          <t>0.9.0</t>
         </is>
       </c>
       <c r="E89" s="3" t="inlineStr">
         <is>
-          <t>https://github.com/XKCP/XKCP</t>
+          <t>https://github.com/warner/python-spake2</t>
         </is>
       </c>
       <c r="F89" s="3" t="inlineStr">
         <is>
-          <t>https://github.com/XKCP/XKCP/archive/refs/heads/master.tar.gz</t>
+          <t>https://github.com/warner/python-spake2/archive/refs/tags/v0.9.zip</t>
         </is>
       </c>
       <c r="G89" s="5" t="inlineStr">
         <is>
-          <t>XKCP — eXtended Keccak Code Package (C/ASM); SHA-3, SHAKE, cSHAKE, KMAC, Ascon, TurboSHAKE</t>
+          <t>python-spake2 — Python SPAKE2 and SPAKE2+ implementation (Warner; RFC 9382)</t>
         </is>
       </c>
       <c r="H89" s="5" t="inlineStr">
         <is>
-          <t>No formal releases — rolling commits; reference implementation used by NIST</t>
-        </is>
-      </c>
-      <c r="I89" s="5" t="n"/>
+          <t>v0.9.0 — 2022</t>
+        </is>
+      </c>
+      <c r="I89" s="5" t="inlineStr">
+        <is>
+          <t>stable</t>
+        </is>
+      </c>
       <c r="J89" s="5" t="inlineStr">
         <is>
-          <t>SHA3-[224|256|384|512], SHAKE128, SHAKE256, cSHAKE128, SHAKE256, KMAC128, KMAC256, Ascon-AEAD128, Ascon-Hash256, Ascon-XOF128, Ascon-CXOF128, TupleHash128, TupleHash256, ParallelHash128, ParallelHash256</t>
+          <t>SPAKE2-*, SPAKE2+-*</t>
         </is>
       </c>
       <c r="K89" s="5" t="n"/>
       <c r="L89" s="5" t="inlineStr">
         <is>
-          <t>Keccak / SHA-3: patent-free per NIST agreement. Ascon: no known patents.</t>
+          <t>No known patents. RFC 9382 explicitly addresses patent concerns.</t>
+        </is>
+      </c>
+      <c r="M89" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
     </row>
     <row r="90" ht="23" customHeight="1">
       <c r="A90" s="5" t="inlineStr">
         <is>
-          <t>xoshiro-reference</t>
+          <t>qr-uov</t>
         </is>
       </c>
       <c r="B90" s="13" t="n"/>
-      <c r="C90" s="3" t="inlineStr">
-        <is>
-          <t>CC0-1.0</t>
+      <c r="C90" s="11" t="inlineStr">
+        <is>
+          <t>UNKNOWN</t>
         </is>
       </c>
       <c r="D90" s="11" t="inlineStr">
@@ -5612,119 +5752,1229 @@
       </c>
       <c r="E90" s="3" t="inlineStr">
         <is>
-          <t>https://prng.di.unimi.it/</t>
+          <t>https://www.qr-uov.com/</t>
         </is>
       </c>
       <c r="F90" s="3" t="inlineStr">
         <is>
-          <t>https://github.com/hpenne/smallrand/archive/refs/tags/v1.0.1.zip</t>
+          <t>https://github.com/qruov/round2/archive/refs/heads/main.zip</t>
         </is>
       </c>
       <c r="G90" s="5" t="inlineStr">
         <is>
-          <t>Xoshiro / Xoroshiro reference implementation (Vigna, Blackman)</t>
+          <t>QR-UOV — Quotient Ring UOV</t>
         </is>
       </c>
       <c r="H90" s="5" t="inlineStr">
         <is>
-          <t>No formal releases</t>
+          <t>Round 2 submission; distributed via algorithm website (no GitHub)</t>
         </is>
       </c>
       <c r="I90" s="5" t="n"/>
       <c r="J90" s="5" t="inlineStr">
         <is>
-          <t>Xoshiro, Xoroshiro</t>
-        </is>
-      </c>
-      <c r="K90" s="5" t="inlineStr">
-        <is>
-          <t>Different implementations exist under different licenses; research required</t>
-        </is>
-      </c>
+          <t>QR-UOV-*</t>
+        </is>
+      </c>
+      <c r="K90" s="5" t="n"/>
       <c r="L90" s="5" t="inlineStr">
         <is>
-          <t>No known patents.</t>
+          <t>No known patents (NIST Round 2 submission requirement: patent-free).</t>
+        </is>
+      </c>
+      <c r="M90" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
     </row>
     <row r="91" ht="23" customHeight="1">
       <c r="A91" s="5" t="inlineStr">
         <is>
+          <t>ring-0.17.14</t>
+        </is>
+      </c>
+      <c r="B91" s="13" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="C91" s="10" t="inlineStr">
+        <is>
+          <t>Apache-2.0 AND ISC</t>
+        </is>
+      </c>
+      <c r="D91" s="3" t="inlineStr">
+        <is>
+          <t>0.17.14</t>
+        </is>
+      </c>
+      <c r="E91" s="3" t="inlineStr">
+        <is>
+          <t>https://github.com/briansmith/ring</t>
+        </is>
+      </c>
+      <c r="F91" s="5" t="inlineStr">
+        <is>
+          <t>https://static.crates.io/crates/ring/ring-0.17.14.crate</t>
+        </is>
+      </c>
+      <c r="G91" s="5" t="inlineStr">
+        <is>
+          <t>ring — Rust cryptography library exposing a curated BoringSSL-derived primitive set (Rust + vendored C/asm)</t>
+        </is>
+      </c>
+      <c r="H91" s="5" t="inlineStr">
+        <is>
+          <t>0.17.14 (2025-03-11)</t>
+        </is>
+      </c>
+      <c r="I91" s="5" t="inlineStr">
+        <is>
+          <t>stable</t>
+        </is>
+      </c>
+      <c r="J91" s="5" t="inlineStr">
+        <is>
+          <t>AES-[128|256]-GCM, ChaCha20-Poly1305, SHA-[1|256|384|512], HMAC-*, HKDF, PBKDF2-*, ECDH-[P-256|P-384|X25519], EdDSA-Ed25519, ECDSA-[P-256|P-384]-*, RSASSA-PKCS1-*, RSASSA-PSS-*</t>
+        </is>
+      </c>
+      <c r="K91" s="5" t="inlineStr">
+        <is>
+          <t>Widely used by rustls; primitives derived from BoringSSL. Pre-1.0 crate.</t>
+        </is>
+      </c>
+      <c r="L91" s="5" t="n"/>
+      <c r="M91" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> </t>
+        </is>
+      </c>
+    </row>
+    <row r="92" ht="23" customHeight="1">
+      <c r="A92" s="5" t="inlineStr">
+        <is>
+          <t>rustcrypto-kems</t>
+        </is>
+      </c>
+      <c r="B92" s="13" t="n"/>
+      <c r="C92" s="3" t="inlineStr">
+        <is>
+          <t>Apache-2.0 OR MIT</t>
+        </is>
+      </c>
+      <c r="D92" s="11" t="inlineStr">
+        <is>
+          <t>UNRELEASED</t>
+        </is>
+      </c>
+      <c r="E92" s="3" t="inlineStr">
+        <is>
+          <t>https://github.com/RustCrypto/KEMs</t>
+        </is>
+      </c>
+      <c r="F92" s="3" t="inlineStr">
+        <is>
+          <t>https://github.com/RustCrypto/KEMs/archive/refs/heads/master.tar.gz</t>
+        </is>
+      </c>
+      <c r="G92" s="5" t="inlineStr">
+        <is>
+          <t>RustCrypto/KEMs — Rust KEM implementations; ml-kem 0.2.3 (FIPS 203); per-crate crates.io releases</t>
+        </is>
+      </c>
+      <c r="H92" s="5" t="inlineStr">
+        <is>
+          <t>per-crate (crates.io); ml-kem 0.2.3</t>
+        </is>
+      </c>
+      <c r="I92" s="5" t="n"/>
+      <c r="J92" s="5" t="inlineStr">
+        <is>
+          <t>ML-KEM-[512|768|1024]</t>
+        </is>
+      </c>
+      <c r="K92" s="5" t="n"/>
+      <c r="L92" s="5" t="inlineStr">
+        <is>
+          <t>ML-KEM: NIST patent licenses secured. No known unencumbered patents. Apache-2.0 OR MIT.</t>
+        </is>
+      </c>
+      <c r="M92" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> </t>
+        </is>
+      </c>
+    </row>
+    <row r="93" ht="23" customHeight="1">
+      <c r="A93" s="5" t="inlineStr">
+        <is>
+          <t>rustcrypto-traits</t>
+        </is>
+      </c>
+      <c r="B93" s="13" t="n"/>
+      <c r="C93" s="3" t="inlineStr">
+        <is>
+          <t>Apache-2.0 OR MIT</t>
+        </is>
+      </c>
+      <c r="D93" s="11" t="inlineStr">
+        <is>
+          <t>UNRELEASED</t>
+        </is>
+      </c>
+      <c r="E93" s="3" t="inlineStr">
+        <is>
+          <t>https://github.com/RustCrypto/traits</t>
+        </is>
+      </c>
+      <c r="F93" s="3" t="inlineStr">
+        <is>
+          <t>https://github.com/RustCrypto/traits/archive/refs/heads/master.tar.gz</t>
+        </is>
+      </c>
+      <c r="G93" s="5" t="inlineStr">
+        <is>
+          <t>RustCrypto/traits — Rust crypto trait definitions; individual crates on crates.io (ml-kem 0.2.3, ml-dsa, slh-dsa via RustCrypto/KEMs and /signatures)</t>
+        </is>
+      </c>
+      <c r="H93" s="5" t="inlineStr">
+        <is>
+          <t>per-crate (crates.io)</t>
+        </is>
+      </c>
+      <c r="I93" s="5" t="n"/>
+      <c r="J93" s="5" t="inlineStr">
+        <is>
+          <t>AES-[128|192|256]-[GCM|CCM|CBC|CTR|GCM-SIV|XTS], ChaCha20-Poly1305, SHA-[256|384|512], SHA3-[256|384|512], HMAC-[SHA-256|SHA-384|SHA-512], ECDH-[P-256|P-384|P-521], ECDH-[Curve25519|X25519], EdDSA-[Ed25519|Ed448], ECDSA-[P-256|P-384|P-521]-*, HKDF-[SHA-256|SHA-384|SHA-512], ML-KEM-[512|768|1024], ML-DSA-[44|65|87]-*, SLH-DSA-*</t>
+        </is>
+      </c>
+      <c r="K93" s="5" t="n"/>
+      <c r="L93" s="5" t="inlineStr">
+        <is>
+          <t>AES, ChaCha20, SHA, HMAC: no known patents; ECC: Certicom/BlackBerry largely expired; ML-KEM: NIST patent licenses secured; ML-DSA, SLH-DSA: no known patents. Apache-2.0 OR MIT.</t>
+        </is>
+      </c>
+      <c r="M93" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> </t>
+        </is>
+      </c>
+    </row>
+    <row r="94" ht="23" customHeight="1">
+      <c r="A94" s="5" t="inlineStr">
+        <is>
+          <t>ryde</t>
+        </is>
+      </c>
+      <c r="B94" s="13" t="n"/>
+      <c r="C94" s="11" t="inlineStr">
+        <is>
+          <t>UNKNOWN</t>
+        </is>
+      </c>
+      <c r="D94" s="11" t="inlineStr">
+        <is>
+          <t>UNRELEASED</t>
+        </is>
+      </c>
+      <c r="E94" s="3" t="inlineStr">
+        <is>
+          <t>https://pqc-ryde.org/</t>
+        </is>
+      </c>
+      <c r="F94" s="3" t="inlineStr">
+        <is>
+          <t>https://pqc-ryde.org/assets/downloads/ryde_v2.1.0.zip</t>
+        </is>
+      </c>
+      <c r="G94" s="5" t="inlineStr">
+        <is>
+          <t>RYDE — Rank Syndrome Decoding Equivalence</t>
+        </is>
+      </c>
+      <c r="H94" s="5" t="inlineStr">
+        <is>
+          <t>Round 2 submission update (2025); no semantic tag</t>
+        </is>
+      </c>
+      <c r="I94" s="5" t="n"/>
+      <c r="J94" s="5" t="inlineStr">
+        <is>
+          <t>RYDE-*</t>
+        </is>
+      </c>
+      <c r="K94" s="5" t="n"/>
+      <c r="L94" s="5" t="inlineStr">
+        <is>
+          <t>No known patents (NIST Round 2 submission requirement: patent-free).</t>
+        </is>
+      </c>
+      <c r="M94" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> </t>
+        </is>
+      </c>
+    </row>
+    <row r="95" ht="23" customHeight="1">
+      <c r="A95" s="5" t="inlineStr">
+        <is>
+          <t>sdith</t>
+        </is>
+      </c>
+      <c r="B95" s="13" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="C95" s="3" t="inlineStr">
+        <is>
+          <t>CeCILL-2.1</t>
+        </is>
+      </c>
+      <c r="D95" s="11" t="inlineStr">
+        <is>
+          <t>1.1.0</t>
+        </is>
+      </c>
+      <c r="E95" s="3" t="inlineStr">
+        <is>
+          <t>https://github.com/sdith/sdith</t>
+        </is>
+      </c>
+      <c r="F95" s="3" t="inlineStr">
+        <is>
+          <t>https://github.com/sdith/sdith/archive/refs/heads/main.tar.gz</t>
+        </is>
+      </c>
+      <c r="G95" s="5" t="inlineStr">
+        <is>
+          <t>SDitH — Syndrome Decoding in the Head</t>
+        </is>
+      </c>
+      <c r="H95" s="5" t="inlineStr">
+        <is>
+          <t>v1.1.0</t>
+        </is>
+      </c>
+      <c r="I95" s="5" t="n"/>
+      <c r="J95" s="5" t="inlineStr">
+        <is>
+          <t>SDitH-*</t>
+        </is>
+      </c>
+      <c r="K95" s="5" t="n"/>
+      <c r="L95" s="5" t="inlineStr">
+        <is>
+          <t>No known patents (NIST Round 2 submission requirement: patent-free).</t>
+        </is>
+      </c>
+      <c r="M95" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> </t>
+        </is>
+      </c>
+    </row>
+    <row r="96" ht="23" customHeight="1">
+      <c r="A96" s="5" t="inlineStr">
+        <is>
+          <t>sdith-parameters</t>
+        </is>
+      </c>
+      <c r="B96" s="13" t="n"/>
+      <c r="C96" s="11" t="inlineStr">
+        <is>
+          <t>UNKNOWN</t>
+        </is>
+      </c>
+      <c r="D96" s="11" t="inlineStr">
+        <is>
+          <t>UNRELEASED</t>
+        </is>
+      </c>
+      <c r="E96" s="3" t="inlineStr">
+        <is>
+          <t>https://github.com/sdith/sdith-parameters</t>
+        </is>
+      </c>
+      <c r="F96" s="3" t="inlineStr">
+        <is>
+          <t>https://github.com/sdith/sdith-parameters/archive/refs/heads/main.zip</t>
+        </is>
+      </c>
+      <c r="G96" s="5" t="inlineStr">
+        <is>
+          <t>https://github.com/sdith/sdith-parameters/archive/refs/heads/main.tar.gz</t>
+        </is>
+      </c>
+      <c r="H96" s="5" t="inlineStr">
+        <is>
+          <t>No formal releases</t>
+        </is>
+      </c>
+      <c r="I96" s="5" t="n"/>
+      <c r="J96" s="5" t="inlineStr">
+        <is>
+          <t>SDitH-*</t>
+        </is>
+      </c>
+      <c r="K96" s="5" t="n"/>
+      <c r="L96" s="5" t="inlineStr">
+        <is>
+          <t>Parameter-generation scripts only. No known patents.</t>
+        </is>
+      </c>
+      <c r="M96" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> </t>
+        </is>
+      </c>
+    </row>
+    <row r="97" ht="23" customHeight="1">
+      <c r="A97" s="5" t="inlineStr">
+        <is>
+          <t>slh-dsa-py</t>
+        </is>
+      </c>
+      <c r="B97" s="13" t="n"/>
+      <c r="C97" s="3" t="inlineStr">
+        <is>
+          <t>MIT</t>
+        </is>
+      </c>
+      <c r="D97" s="11" t="inlineStr">
+        <is>
+          <t>UNRELEASED</t>
+        </is>
+      </c>
+      <c r="E97" s="3" t="inlineStr">
+        <is>
+          <t>https://github.com/gmh5225/slh-dsa-py</t>
+        </is>
+      </c>
+      <c r="F97" s="3" t="inlineStr">
+        <is>
+          <t>https://github.com/gmh5225/slh-dsa-py/archive/refs/heads/main.zip</t>
+        </is>
+      </c>
+      <c r="G97" s="5" t="inlineStr">
+        <is>
+          <t>slh-dsa-py — SLH-DSA Python, Saarinen (FIPS 205 IPD test vectors)</t>
+        </is>
+      </c>
+      <c r="H97" s="5" t="inlineStr">
+        <is>
+          <t>No formal releases</t>
+        </is>
+      </c>
+      <c r="I97" s="5" t="n"/>
+      <c r="J97" s="5" t="inlineStr">
+        <is>
+          <t>SLH-DSA-*</t>
+        </is>
+      </c>
+      <c r="K97" s="5" t="n"/>
+      <c r="L97" s="5" t="inlineStr">
+        <is>
+          <t>No known patents (SLH-DSA is patent-free).</t>
+        </is>
+      </c>
+      <c r="M97" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> </t>
+        </is>
+      </c>
+    </row>
+    <row r="98" ht="23" customHeight="1">
+      <c r="A98" s="5" t="inlineStr">
+        <is>
+          <t>slhdsa-c</t>
+        </is>
+      </c>
+      <c r="B98" s="13" t="n"/>
+      <c r="C98" s="3" t="inlineStr">
+        <is>
+          <t>MIT OR Apache-2.0</t>
+        </is>
+      </c>
+      <c r="D98" s="11" t="inlineStr">
+        <is>
+          <t>UNRELEASED</t>
+        </is>
+      </c>
+      <c r="E98" s="3" t="inlineStr">
+        <is>
+          <t>https://github.com/pq-code-package/slhdsa-c</t>
+        </is>
+      </c>
+      <c r="F98" s="3" t="inlineStr">
+        <is>
+          <t>https://github.com/pq-code-package/slhdsa-c/archive/refs/heads/main.tar.gz</t>
+        </is>
+      </c>
+      <c r="G98" s="5" t="inlineStr">
+        <is>
+          <t>slhdsa-c — SLH-DSA FIPS 205, PQCP</t>
+        </is>
+      </c>
+      <c r="H98" s="5" t="inlineStr">
+        <is>
+          <t>No formal release — active dev (2026)</t>
+        </is>
+      </c>
+      <c r="I98" s="5" t="n"/>
+      <c r="J98" s="5" t="inlineStr">
+        <is>
+          <t>SLH-DSA-*, HashSLH-DSA-*</t>
+        </is>
+      </c>
+      <c r="K98" s="5" t="n"/>
+      <c r="L98" s="5" t="inlineStr">
+        <is>
+          <t>No known patents.</t>
+        </is>
+      </c>
+      <c r="M98" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> </t>
+        </is>
+      </c>
+    </row>
+    <row r="99" ht="23" customHeight="1">
+      <c r="A99" s="5" t="inlineStr">
+        <is>
+          <t>snova</t>
+        </is>
+      </c>
+      <c r="B99" s="13" t="n"/>
+      <c r="C99" s="11" t="inlineStr">
+        <is>
+          <t>UNKNOWN</t>
+        </is>
+      </c>
+      <c r="D99" s="11" t="inlineStr">
+        <is>
+          <t>UNRELEASED</t>
+        </is>
+      </c>
+      <c r="E99" s="3" t="inlineStr">
+        <is>
+          <t>https://github.com/PQCLAB-SNOVA/SNOVA</t>
+        </is>
+      </c>
+      <c r="F99" s="3" t="inlineStr">
+        <is>
+          <t>https://github.com/PQCLAB-SNOVA/SNOVA/archive/refs/heads/main.tar.gz</t>
+        </is>
+      </c>
+      <c r="G99" s="5" t="inlineStr">
+        <is>
+          <t>SNOVA — official C reference + optimised + AVX2</t>
+        </is>
+      </c>
+      <c r="H99" s="5" t="inlineStr">
+        <is>
+          <t>Round 2 submission update (Jan 2025); no semantic tag</t>
+        </is>
+      </c>
+      <c r="I99" s="5" t="n"/>
+      <c r="J99" s="5" t="inlineStr">
+        <is>
+          <t>SNOVA-*</t>
+        </is>
+      </c>
+      <c r="K99" s="5" t="n"/>
+      <c r="L99" s="5" t="inlineStr">
+        <is>
+          <t>No known patents (NIST Round 2 submission requirement: patent-free).</t>
+        </is>
+      </c>
+      <c r="M99" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> </t>
+        </is>
+      </c>
+    </row>
+    <row r="100" ht="23" customHeight="1">
+      <c r="A100" s="5" t="inlineStr">
+        <is>
+          <t>sphincsplus</t>
+        </is>
+      </c>
+      <c r="B100" s="13" t="n"/>
+      <c r="C100" s="3" t="inlineStr">
+        <is>
+          <t>CC0-1.0</t>
+        </is>
+      </c>
+      <c r="D100" s="11" t="inlineStr">
+        <is>
+          <t>UNRELEASED</t>
+        </is>
+      </c>
+      <c r="E100" s="3" t="inlineStr">
+        <is>
+          <t>https://github.com/sphincs/sphincsplus</t>
+        </is>
+      </c>
+      <c r="F100" s="3" t="inlineStr">
+        <is>
+          <t>https://github.com/sphincs/sphincsplus/archive/refs/heads/master.tar.gz</t>
+        </is>
+      </c>
+      <c r="G100" s="5" t="inlineStr">
+        <is>
+          <t>SPHINCS+ / SLH-DSA reference</t>
+        </is>
+      </c>
+      <c r="H100" s="5" t="inlineStr">
+        <is>
+          <t>No formal releases — rolling commits</t>
+        </is>
+      </c>
+      <c r="I100" s="5" t="n"/>
+      <c r="J100" s="5" t="inlineStr">
+        <is>
+          <t>SLH-DSA-*, HashSLH-DSA-*</t>
+        </is>
+      </c>
+      <c r="K100" s="5" t="n"/>
+      <c r="L100" s="5" t="inlineStr">
+        <is>
+          <t>No known patents.</t>
+        </is>
+      </c>
+      <c r="M100" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> </t>
+        </is>
+      </c>
+    </row>
+    <row r="101" ht="23" customHeight="1">
+      <c r="A101" s="5" t="inlineStr">
+        <is>
+          <t>sqisign-ec23</t>
+        </is>
+      </c>
+      <c r="B101" s="13" t="n"/>
+      <c r="C101" s="3" t="inlineStr">
+        <is>
+          <t>Apache-2.0</t>
+        </is>
+      </c>
+      <c r="D101" s="11" t="inlineStr">
+        <is>
+          <t>UNRELEASED</t>
+        </is>
+      </c>
+      <c r="E101" s="3" t="inlineStr">
+        <is>
+          <t>https://github.com/SQISign/sqisign-ec23</t>
+        </is>
+      </c>
+      <c r="F101" s="3" t="inlineStr">
+        <is>
+          <t>https://github.com/SQISign/sqisign-ec23/archive/refs/heads/main.tar.gz</t>
+        </is>
+      </c>
+      <c r="G101" s="5" t="inlineStr">
+        <is>
+          <t>SQIsign ec23 — EUROCRYPT 2023 C implementation</t>
+        </is>
+      </c>
+      <c r="H101" s="5" t="inlineStr">
+        <is>
+          <t>No formal releases</t>
+        </is>
+      </c>
+      <c r="I101" s="5" t="n"/>
+      <c r="J101" s="5" t="inlineStr">
+        <is>
+          <t>SQIsign-*</t>
+        </is>
+      </c>
+      <c r="K101" s="5" t="n"/>
+      <c r="L101" s="5" t="inlineStr">
+        <is>
+          <t>No known patents. Isogeny-based (SQIsign variant); distinct from SIDH/SIKE (broken 2022; Microsoft patents abandoned). NIST Round 2 requirement: patent-free.</t>
+        </is>
+      </c>
+    </row>
+    <row r="102" ht="23" customHeight="1">
+      <c r="A102" s="5" t="inlineStr">
+        <is>
+          <t>sqisign2d-west-ac24</t>
+        </is>
+      </c>
+      <c r="B102" s="13" t="n"/>
+      <c r="C102" s="3" t="inlineStr">
+        <is>
+          <t>Apache-2.0</t>
+        </is>
+      </c>
+      <c r="D102" s="11" t="inlineStr">
+        <is>
+          <t>UNRELEASED</t>
+        </is>
+      </c>
+      <c r="E102" s="3" t="inlineStr">
+        <is>
+          <t>https://github.com/SQISign/sqisign2d-west-ac24</t>
+        </is>
+      </c>
+      <c r="F102" s="3" t="inlineStr">
+        <is>
+          <t>https://github.com/SQISign/sqisign2d-west-ac24/archive/refs/heads/main.tar.gz</t>
+        </is>
+      </c>
+      <c r="G102" s="5" t="inlineStr">
+        <is>
+          <t>SQIsign2D-West ac24 — ASIACRYPT 2024 C implementation</t>
+        </is>
+      </c>
+      <c r="H102" s="5" t="inlineStr">
+        <is>
+          <t>No formal releases</t>
+        </is>
+      </c>
+      <c r="I102" s="5" t="n"/>
+      <c r="J102" s="5" t="inlineStr">
+        <is>
+          <t>SQIsign2D-*</t>
+        </is>
+      </c>
+      <c r="K102" s="5" t="n"/>
+      <c r="L102" s="5" t="inlineStr">
+        <is>
+          <t>No known patents. Isogeny-based (SQIsign2D); distinct from SIDH/SIKE. NIST Round 2 requirement: patent-free.</t>
+        </is>
+      </c>
+    </row>
+    <row r="103" ht="23" customHeight="1">
+      <c r="A103" s="5" t="inlineStr">
+        <is>
+          <t>swift-crypto-3.15.1</t>
+        </is>
+      </c>
+      <c r="B103" s="13" t="n"/>
+      <c r="C103" s="10" t="inlineStr">
+        <is>
+          <t>Apache-2.0</t>
+        </is>
+      </c>
+      <c r="D103" s="3" t="inlineStr">
+        <is>
+          <t>3.15.1</t>
+        </is>
+      </c>
+      <c r="E103" s="3" t="inlineStr">
+        <is>
+          <t>https://github.com/apple/swift-crypto</t>
+        </is>
+      </c>
+      <c r="F103" s="5" t="inlineStr">
+        <is>
+          <t>https://github.com/apple/swift-crypto/archive/refs/tags/3.15.1.tar.gz</t>
+        </is>
+      </c>
+      <c r="G103" s="5" t="inlineStr">
+        <is>
+          <t>swift-crypto — Swift CryptoKit-compatible crypto API (wraps CryptoKit on Apple, vendored BoringSSL off-Apple)</t>
+        </is>
+      </c>
+      <c r="H103" s="5" t="inlineStr">
+        <is>
+          <t>3.15.1 (2025-09-22)</t>
+        </is>
+      </c>
+      <c r="I103" s="5" t="inlineStr">
+        <is>
+          <t>previous</t>
+        </is>
+      </c>
+      <c r="J103" s="5" t="inlineStr">
+        <is>
+          <t>SHA-[256|384|512], HMAC-*, AES-[128|192|256]-GCM, ChaCha20-Poly1305, ECDH-[P-256|P-384|P-521|X25519], ECDSA-[P-256|P-384|P-521]-*, EdDSA-Ed25519, HKDF</t>
+        </is>
+      </c>
+      <c r="K103" s="5" t="inlineStr">
+        <is>
+          <t>Previous major line. Wrapper (CryptoKit / BoringSSL).</t>
+        </is>
+      </c>
+      <c r="L103" s="5" t="n"/>
+      <c r="M103" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> </t>
+        </is>
+      </c>
+    </row>
+    <row r="104" ht="23" customHeight="1">
+      <c r="A104" s="5" t="inlineStr">
+        <is>
+          <t>swift-crypto-4.5.0</t>
+        </is>
+      </c>
+      <c r="B104" s="13" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="C104" s="10" t="inlineStr">
+        <is>
+          <t>Apache-2.0</t>
+        </is>
+      </c>
+      <c r="D104" s="3" t="inlineStr">
+        <is>
+          <t>4.5.0</t>
+        </is>
+      </c>
+      <c r="E104" s="3" t="inlineStr">
+        <is>
+          <t>https://github.com/apple/swift-crypto</t>
+        </is>
+      </c>
+      <c r="F104" s="5" t="inlineStr">
+        <is>
+          <t>https://github.com/apple/swift-crypto/archive/refs/tags/4.5.0.tar.gz</t>
+        </is>
+      </c>
+      <c r="G104" s="5" t="inlineStr">
+        <is>
+          <t>swift-crypto — Swift CryptoKit-compatible crypto API (wraps CryptoKit on Apple, vendored BoringSSL off-Apple)</t>
+        </is>
+      </c>
+      <c r="H104" s="5" t="inlineStr">
+        <is>
+          <t>4.5.0 (2026-04-23)</t>
+        </is>
+      </c>
+      <c r="I104" s="5" t="inlineStr">
+        <is>
+          <t>stable</t>
+        </is>
+      </c>
+      <c r="J104" s="5" t="inlineStr">
+        <is>
+          <t>SHA-[256|384|512], HMAC-*, AES-[128|192|256]-GCM, ChaCha20-Poly1305, ECDH-[P-256|P-384|P-521|X25519], ECDSA-[P-256|P-384|P-521]-*, EdDSA-Ed25519, HKDF</t>
+        </is>
+      </c>
+      <c r="K104" s="5" t="inlineStr">
+        <is>
+          <t>Wrapper: CryptoKit on Apple platforms, vendored BoringSSL elsewhere.</t>
+        </is>
+      </c>
+      <c r="L104" s="5" t="n"/>
+      <c r="M104" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> </t>
+        </is>
+      </c>
+    </row>
+    <row r="105" ht="23" customHeight="1">
+      <c r="A105" s="5" t="inlineStr">
+        <is>
+          <t>symcrypt-103.12.1</t>
+        </is>
+      </c>
+      <c r="B105" s="13" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="C105" s="10" t="inlineStr">
+        <is>
+          <t>MIT</t>
+        </is>
+      </c>
+      <c r="D105" s="3" t="inlineStr">
+        <is>
+          <t>103.12.1</t>
+        </is>
+      </c>
+      <c r="E105" s="3" t="inlineStr">
+        <is>
+          <t>https://github.com/microsoft/SymCrypt</t>
+        </is>
+      </c>
+      <c r="F105" s="5" t="inlineStr">
+        <is>
+          <t>https://github.com/microsoft/SymCrypt/archive/refs/tags/v103.12.1.tar.gz</t>
+        </is>
+      </c>
+      <c r="G105" s="5" t="inlineStr">
+        <is>
+          <t>SymCrypt — Microsoft core cryptographic library (Windows / Azure Linux); C + platform assembly</t>
+        </is>
+      </c>
+      <c r="H105" s="5" t="inlineStr">
+        <is>
+          <t>v103.12.1 (2026-06-01)</t>
+        </is>
+      </c>
+      <c r="I105" s="5" t="inlineStr">
+        <is>
+          <t>stable</t>
+        </is>
+      </c>
+      <c r="J105" s="5" t="inlineStr">
+        <is>
+          <t>AES-[128|192|256]-[ECB|CBC|GCM|XTS|KW], ChaCha20-Poly1305, SHA-[1|256|384|512], SHA3-*, MD5, HMAC-*, RSASSA-PSS-*, RSAES-OAEP-*, ECDSA-*, ECDH-*, ML-KEM-[512|768|1024], ML-DSA-[44|65|87]-*, XMSS-*, XMSSMT-*, LMS-*</t>
+        </is>
+      </c>
+      <c r="K105" s="5" t="inlineStr">
+        <is>
+          <t>Backs Windows CNG and the SymCrypt-OpenSSL provider.</t>
+        </is>
+      </c>
+      <c r="L105" s="5" t="n"/>
+      <c r="M105" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> </t>
+        </is>
+      </c>
+    </row>
+    <row r="106" ht="23" customHeight="1">
+      <c r="A106" s="5" t="inlineStr">
+        <is>
+          <t>tink-go-2.7.0</t>
+        </is>
+      </c>
+      <c r="B106" s="13" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="C106" s="3" t="inlineStr">
+        <is>
+          <t>Apache-2.0</t>
+        </is>
+      </c>
+      <c r="D106" s="3" t="inlineStr">
+        <is>
+          <t>2.7.0</t>
+        </is>
+      </c>
+      <c r="E106" s="3" t="inlineStr">
+        <is>
+          <t>https://github.com/tink-crypto/tink-go</t>
+        </is>
+      </c>
+      <c r="F106" s="3" t="inlineStr">
+        <is>
+          <t>https://github.com/tink-crypto/tink-go/archive/refs/tags/v2.7.0.tar.gz</t>
+        </is>
+      </c>
+      <c r="G106" s="5" t="inlineStr">
+        <is>
+          <t>Google Tink Go — opinionated crypto API (Go); ML-KEM-768/1024, ML-DSA-87</t>
+        </is>
+      </c>
+      <c r="H106" s="5" t="inlineStr">
+        <is>
+          <t>v2.7.0 (2026-06-10)</t>
+        </is>
+      </c>
+      <c r="I106" s="5" t="inlineStr">
+        <is>
+          <t>stable</t>
+        </is>
+      </c>
+      <c r="J106" s="5" t="inlineStr">
+        <is>
+          <t>AES-[128|256]-GCM, ChaCha20-Poly1305, HMAC-[SHA-256|SHA-512], ECDH-[P-256|P-384], ECDH-[Curve25519|X25519], ECDSA-[P-256|P-384|P-521]-[SHA-256|SHA-384|SHA-512], EdDSA-Ed25519, RSASSA-PSS-[2048|3072|4096]-*, HKDF-[SHA-256|SHA-384|SHA-512], ML-KEM-[768|1024], ML-DSA-87</t>
+        </is>
+      </c>
+      <c r="K106" s="5" t="n"/>
+      <c r="L106" s="5" t="inlineStr">
+        <is>
+          <t>AES, ChaCha20-Poly1305, HMAC: no known patents; ECC: Certicom/BlackBerry largely expired; ML-KEM: NIST patent licenses secured; ML-DSA: no known patents. Apache-2.0 license includes patent grant.</t>
+        </is>
+      </c>
+    </row>
+    <row r="107" ht="23" customHeight="1">
+      <c r="A107" s="5" t="inlineStr">
+        <is>
+          <t>tink-java-1.21.0</t>
+        </is>
+      </c>
+      <c r="B107" s="13" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="C107" s="3" t="inlineStr">
+        <is>
+          <t>Apache-2.0</t>
+        </is>
+      </c>
+      <c r="D107" s="3" t="inlineStr">
+        <is>
+          <t>1.21.0</t>
+        </is>
+      </c>
+      <c r="E107" s="3" t="inlineStr">
+        <is>
+          <t>https://github.com/tink-crypto/tink-java</t>
+        </is>
+      </c>
+      <c r="F107" s="3" t="inlineStr">
+        <is>
+          <t>https://github.com/tink-crypto/tink-java/archive/refs/tags/v1.21.0.tar.gz</t>
+        </is>
+      </c>
+      <c r="G107" s="5" t="inlineStr">
+        <is>
+          <t>Google Tink Java — opinionated crypto API (Java); ML-DSA-87, ML-KEM, hybrid KEM (DHKEM+ML-KEM)</t>
+        </is>
+      </c>
+      <c r="H107" s="5" t="inlineStr">
+        <is>
+          <t>v1.21.0 (2025-03-24)</t>
+        </is>
+      </c>
+      <c r="I107" s="5" t="inlineStr">
+        <is>
+          <t>stable</t>
+        </is>
+      </c>
+      <c r="J107" s="5" t="inlineStr">
+        <is>
+          <t>AES-[128|256]-GCM, AES-[128|256]-CTR, ChaCha20-Poly1305, HMAC-[SHA-256|SHA-512], ECDH-[P-256|P-384|P-521], ECDH-[Curve25519|X25519], ECDSA-[P-256|P-384|P-521]-[SHA-256|SHA-384|SHA-512], EdDSA-[Ed25519|Ed448], RSASSA-PSS-[2048|3072|4096]-*, HKDF-[SHA-256|SHA-384|SHA-512], ML-KEM-[768|1024], ML-DSA-87</t>
+        </is>
+      </c>
+      <c r="K107" s="5" t="n"/>
+      <c r="L107" s="5" t="inlineStr">
+        <is>
+          <t>AES, ChaCha20-Poly1305, HMAC: no known patents; ECC: Certicom/BlackBerry largely expired; ML-KEM: NIST patent licenses secured; ML-DSA: no known patents. Apache-2.0 license includes patent grant.</t>
+        </is>
+      </c>
+    </row>
+    <row r="108" ht="23" customHeight="1">
+      <c r="A108" s="5" t="inlineStr">
+        <is>
+          <t>wolfssl-5.9.1</t>
+        </is>
+      </c>
+      <c r="B108" s="13" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="C108" s="9" t="inlineStr">
+        <is>
+          <t>GPL-2.0-only</t>
+        </is>
+      </c>
+      <c r="D108" s="3" t="inlineStr">
+        <is>
+          <t>5.9.1</t>
+        </is>
+      </c>
+      <c r="E108" s="3" t="inlineStr">
+        <is>
+          <t>https://github.com/wolfSSL/wolfssl</t>
+        </is>
+      </c>
+      <c r="F108" s="6" t="inlineStr">
+        <is>
+          <t>https://github.com/wolfSSL/wolfssl/archive/refs/tags/v5.9.1-stable.tar.gz</t>
+        </is>
+      </c>
+      <c r="G108" s="5" t="inlineStr">
+        <is>
+          <t>wolfSSL — embedded TLS/crypto (C); ML-KEM, ML-DSA, SLH-DSA (FIPS 203/204/205); CNSA 2.0 compliant</t>
+        </is>
+      </c>
+      <c r="H108" s="5" t="inlineStr">
+        <is>
+          <t>v5.9.0-stable</t>
+        </is>
+      </c>
+      <c r="I108" s="5" t="inlineStr">
+        <is>
+          <t>stable</t>
+        </is>
+      </c>
+      <c r="J108" s="5" t="inlineStr">
+        <is>
+          <t>AES-[128|192|256]-[GCM|CCM|CBC|CTR|OFB|CFB128|XTS], ChaCha20-Poly1305, SHA-[256|384|512], SHA3-[256|384|512], HMAC-[SHA-256|SHA-384|SHA-512], AES-[128|192|256]-CMAC, RSAES-OAEP-[2048|3072|4096]-*, ECDH-[P-256|P-384|P-521], ECDH-[Curve25519|X25519], ECDH-[Curve448|X448], ECDSA-[P-256|P-384|P-521]-*, EdDSA-[Ed25519|Ed448], RSASSA-PSS-[2048|3072|4096]-*, HKDF-[SHA-256|SHA-384|SHA-512], PBKDF2-HMAC-[SHA-256|SHA-384|SHA-512]-*, ML-KEM-[512|768|1024], ML-DSA-[44|65|87]-*, SLH-DSA-*, HMAC_DRBG-[SHA-256|SHA-384|SHA-512], CTR_DRBG-AES-[128|192|256], LMS-*, XMSS-*, XMSSMT-*</t>
+        </is>
+      </c>
+      <c r="K108" s="5" t="inlineStr">
+        <is>
+          <t>GPL-3 or for some combinations GPL-2 or Commercial</t>
+        </is>
+      </c>
+      <c r="L108" s="5" t="inlineStr">
+        <is>
+          <t>RSA: expired 2000; DH: expired 1997; ECC: Certicom/BlackBerry largely expired 2017–2022; ML-KEM: NIST patent licenses secured; ML-DSA, SLH-DSA: no known patents; AES, ChaCha20, SHA, HMAC: no known patents. GPL-2.0-only.</t>
+        </is>
+      </c>
+    </row>
+    <row r="109" ht="23" customHeight="1">
+      <c r="A109" s="5" t="inlineStr">
+        <is>
+          <t>xkcp</t>
+        </is>
+      </c>
+      <c r="B109" s="13" t="n"/>
+      <c r="C109" s="3" t="inlineStr">
+        <is>
+          <t>CC0-1.0 OR Apache-2.0</t>
+        </is>
+      </c>
+      <c r="D109" s="11" t="inlineStr">
+        <is>
+          <t>UNRELEASED</t>
+        </is>
+      </c>
+      <c r="E109" s="3" t="inlineStr">
+        <is>
+          <t>https://github.com/XKCP/XKCP</t>
+        </is>
+      </c>
+      <c r="F109" s="3" t="inlineStr">
+        <is>
+          <t>https://github.com/XKCP/XKCP/archive/refs/heads/master.tar.gz</t>
+        </is>
+      </c>
+      <c r="G109" s="5" t="inlineStr">
+        <is>
+          <t>XKCP — eXtended Keccak Code Package (C/ASM); SHA-3, SHAKE, cSHAKE, KMAC, Ascon, TurboSHAKE</t>
+        </is>
+      </c>
+      <c r="H109" s="5" t="inlineStr">
+        <is>
+          <t>No formal releases — rolling commits; reference implementation used by NIST</t>
+        </is>
+      </c>
+      <c r="I109" s="5" t="n"/>
+      <c r="J109" s="5" t="inlineStr">
+        <is>
+          <t>SHA3-[224|256|384|512], SHAKE128, SHAKE256, cSHAKE128, SHAKE256, KMAC128, KMAC256, Ascon-AEAD128, Ascon-Hash256, Ascon-XOF128, Ascon-CXOF128, TupleHash128, TupleHash256, ParallelHash128, ParallelHash256, cSHAKE256, TupleHashXOF128, TupleHashXOF256, ParallelHashXOF128, ParallelHashXOF256, KMACXOF128, KMACXOF256</t>
+        </is>
+      </c>
+      <c r="K109" s="5" t="n"/>
+      <c r="L109" s="5" t="inlineStr">
+        <is>
+          <t>Keccak / SHA-3: patent-free per NIST agreement. Ascon: no known patents.</t>
+        </is>
+      </c>
+    </row>
+    <row r="110" ht="23" customHeight="1">
+      <c r="A110" s="5" t="inlineStr">
+        <is>
+          <t>xoshiro-reference</t>
+        </is>
+      </c>
+      <c r="B110" s="13" t="n"/>
+      <c r="C110" s="3" t="inlineStr">
+        <is>
+          <t>CC0-1.0</t>
+        </is>
+      </c>
+      <c r="D110" s="11" t="inlineStr">
+        <is>
+          <t>UNRELEASED</t>
+        </is>
+      </c>
+      <c r="E110" s="3" t="inlineStr">
+        <is>
+          <t>https://prng.di.unimi.it/</t>
+        </is>
+      </c>
+      <c r="F110" s="3" t="inlineStr">
+        <is>
+          <t>https://github.com/hpenne/smallrand/archive/refs/tags/v1.0.1.zip</t>
+        </is>
+      </c>
+      <c r="G110" s="5" t="inlineStr">
+        <is>
+          <t>Xoshiro / Xoroshiro reference implementation (Vigna, Blackman)</t>
+        </is>
+      </c>
+      <c r="H110" s="5" t="inlineStr">
+        <is>
+          <t>No formal releases</t>
+        </is>
+      </c>
+      <c r="I110" s="5" t="n"/>
+      <c r="J110" s="5" t="inlineStr">
+        <is>
+          <t>Xoshiro, Xoroshiro</t>
+        </is>
+      </c>
+      <c r="K110" s="5" t="inlineStr">
+        <is>
+          <t>Different implementations exist under different licenses; research required</t>
+        </is>
+      </c>
+      <c r="L110" s="5" t="inlineStr">
+        <is>
+          <t>No known patents.</t>
+        </is>
+      </c>
+    </row>
+    <row r="111" ht="23" customHeight="1">
+      <c r="A111" s="5" t="inlineStr">
+        <is>
           <t>yescrypt-1.1.0</t>
         </is>
       </c>
-      <c r="B91" s="13" t="inlineStr">
+      <c r="B111" s="13" t="inlineStr">
         <is>
           <t>x</t>
         </is>
       </c>
-      <c r="C91" s="3" t="inlineStr">
+      <c r="C111" s="3" t="inlineStr">
         <is>
           <t>BSD-2-Clause</t>
         </is>
       </c>
-      <c r="D91" s="3" t="inlineStr">
+      <c r="D111" s="3" t="inlineStr">
         <is>
           <t>1.1.0</t>
         </is>
       </c>
-      <c r="E91" s="3" t="inlineStr">
+      <c r="E111" s="3" t="inlineStr">
         <is>
           <t>https://github.com/openwall/yescrypt</t>
         </is>
       </c>
-      <c r="F91" s="3" t="inlineStr">
+      <c r="F111" s="3" t="inlineStr">
         <is>
           <t>https://www.openwall.com/yescrypt/yescrypt-1.1.0.tar.gz</t>
         </is>
       </c>
-      <c r="G91" s="5" t="inlineStr">
+      <c r="G111" s="5" t="inlineStr">
         <is>
           <t>yescrypt reference implementation (Openwall)</t>
         </is>
       </c>
-      <c r="H91" s="5" t="inlineStr">
+      <c r="H111" s="5" t="inlineStr">
         <is>
           <t>Outdated last release dates back to june 2019</t>
         </is>
       </c>
-      <c r="I91" s="5" t="inlineStr">
+      <c r="I111" s="5" t="inlineStr">
         <is>
           <t>outdated code</t>
         </is>
       </c>
-      <c r="J91" s="5" t="inlineStr">
+      <c r="J111" s="5" t="inlineStr">
         <is>
           <t>yescrypt-*</t>
         </is>
       </c>
-      <c r="K91" s="5" t="n"/>
-      <c r="L91" s="5" t="inlineStr">
+      <c r="K111" s="5" t="n"/>
+      <c r="L111" s="5" t="inlineStr">
         <is>
           <t>No known patents.</t>
         </is>
       </c>
     </row>
-    <row r="92" ht="23" customHeight="1"/>
-    <row r="93" ht="23" customHeight="1"/>
-    <row r="94" ht="23" customHeight="1"/>
-    <row r="95" ht="23" customHeight="1"/>
-    <row r="96" ht="23" customHeight="1"/>
-    <row r="97" ht="23" customHeight="1"/>
-    <row r="98" ht="23" customHeight="1"/>
-    <row r="99" ht="23" customHeight="1"/>
-    <row r="100" ht="23" customHeight="1"/>
-    <row r="101" ht="23" customHeight="1"/>
-    <row r="102" ht="23" customHeight="1"/>
-    <row r="103" ht="23" customHeight="1"/>
-    <row r="104" ht="23" customHeight="1"/>
-    <row r="105" ht="23" customHeight="1"/>
-    <row r="106" ht="23" customHeight="1"/>
-    <row r="107" ht="23" customHeight="1"/>
-    <row r="108" ht="23" customHeight="1"/>
-    <row r="109" ht="23" customHeight="1"/>
-    <row r="110" ht="23" customHeight="1"/>
-    <row r="111" ht="23" customHeight="1"/>
     <row r="112" ht="23" customHeight="1"/>
     <row r="113" ht="23" customHeight="1"/>
     <row r="114" ht="23" customHeight="1"/>
